--- a/output/2024-05-25.xlsx
+++ b/output/2024-05-25.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>1.91</v>
+        <v>2.09</v>
       </c>
       <c r="F14" t="n">
-        <v>7.3</v>
+        <v>7.7</v>
       </c>
       <c r="G14" t="n">
-        <v>229.3</v>
+        <v>233.6</v>
       </c>
       <c r="H14" t="n">
-        <v>19.2</v>
+        <v>17</v>
       </c>
       <c r="I14" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J14" t="n">
-        <v>4.69</v>
+        <v>-41.38</v>
       </c>
       <c r="K14" t="n">
-        <v>30.19</v>
+        <v>-38.12</v>
       </c>
       <c r="L14" t="n">
-        <v>30.55</v>
+        <v>56.26</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:46:25</t>
+          <t>04:46:34</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2.77</v>
+        <v>2.36</v>
       </c>
       <c r="F15" t="n">
-        <v>7.07</v>
+        <v>8.15</v>
       </c>
       <c r="G15" t="n">
-        <v>233.3</v>
+        <v>238.7</v>
       </c>
       <c r="H15" t="n">
-        <v>19.6</v>
+        <v>11.6</v>
       </c>
       <c r="I15" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J15" t="n">
-        <v>-2.29</v>
+        <v>73.8</v>
       </c>
       <c r="K15" t="n">
-        <v>-71.39</v>
+        <v>-146.89</v>
       </c>
       <c r="L15" t="n">
-        <v>71.42</v>
+        <v>164.39</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:48:46</t>
+          <t>04:48:09</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>2.28</v>
+        <v>3.23</v>
       </c>
       <c r="F16" t="n">
-        <v>7.45</v>
+        <v>8.18</v>
       </c>
       <c r="G16" t="n">
-        <v>235.7</v>
+        <v>236.9</v>
       </c>
       <c r="H16" t="n">
-        <v>8.6</v>
+        <v>5.7</v>
       </c>
       <c r="I16" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J16" t="n">
-        <v>19.41</v>
+        <v>-31.68</v>
       </c>
       <c r="K16" t="n">
-        <v>-41.93</v>
+        <v>43.37</v>
       </c>
       <c r="L16" t="n">
-        <v>46.2</v>
+        <v>53.71</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04:52:51</t>
+          <t>04:52:00</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>1.91</v>
+        <v>2.35</v>
       </c>
       <c r="F17" t="n">
-        <v>8.4</v>
+        <v>7.3</v>
       </c>
       <c r="G17" t="n">
-        <v>252.8</v>
+        <v>234.8</v>
       </c>
       <c r="H17" t="n">
-        <v>20.9</v>
+        <v>18.8</v>
       </c>
       <c r="I17" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J17" t="n">
-        <v>54.77</v>
+        <v>-120.85</v>
       </c>
       <c r="K17" t="n">
-        <v>-21.77</v>
+        <v>47.7</v>
       </c>
       <c r="L17" t="n">
-        <v>58.94</v>
+        <v>129.92</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:54:56</t>
+          <t>04:54:33</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,28 +793,28 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.62</v>
+        <v>2.22</v>
       </c>
       <c r="F18" t="n">
-        <v>7.86</v>
+        <v>7.91</v>
       </c>
       <c r="G18" t="n">
-        <v>225.4</v>
+        <v>228.6</v>
       </c>
       <c r="H18" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="I18" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J18" t="n">
-        <v>19.46</v>
+        <v>109.81</v>
       </c>
       <c r="K18" t="n">
-        <v>-3.45</v>
+        <v>-39.62</v>
       </c>
       <c r="L18" t="n">
-        <v>19.76</v>
+        <v>116.74</v>
       </c>
     </row>
     <row r="19">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>2.51</v>
+        <v>2.47</v>
       </c>
       <c r="F19" t="n">
-        <v>7.07</v>
+        <v>8</v>
       </c>
       <c r="G19" t="n">
-        <v>231.2</v>
+        <v>224.4</v>
       </c>
       <c r="H19" t="n">
-        <v>15.8</v>
+        <v>13.9</v>
       </c>
       <c r="I19" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>-133.66</v>
+        <v>85.72</v>
       </c>
       <c r="K19" t="n">
-        <v>-24.63</v>
+        <v>74.59</v>
       </c>
       <c r="L19" t="n">
-        <v>135.91</v>
+        <v>113.63</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>05:00:07</t>
+          <t>05:00:51</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>2.61</v>
+        <v>2.14</v>
       </c>
       <c r="F20" t="n">
-        <v>7.92</v>
+        <v>7.97</v>
       </c>
       <c r="G20" t="n">
-        <v>246</v>
+        <v>235.3</v>
       </c>
       <c r="H20" t="n">
-        <v>12.8</v>
+        <v>16.1</v>
       </c>
       <c r="I20" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J20" t="n">
-        <v>73.08</v>
+        <v>130.54</v>
       </c>
       <c r="K20" t="n">
-        <v>376.35</v>
+        <v>52.39</v>
       </c>
       <c r="L20" t="n">
-        <v>383.38</v>
+        <v>140.66</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>05:02:25</t>
+          <t>05:02:39</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="F21" t="n">
-        <v>8.029999999999999</v>
+        <v>7.81</v>
       </c>
       <c r="G21" t="n">
-        <v>242.9</v>
+        <v>237.3</v>
       </c>
       <c r="H21" t="n">
-        <v>12.4</v>
+        <v>18.3</v>
       </c>
       <c r="I21" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J21" t="n">
-        <v>-26.33</v>
+        <v>14.28</v>
       </c>
       <c r="K21" t="n">
-        <v>-30.54</v>
+        <v>322.51</v>
       </c>
       <c r="L21" t="n">
-        <v>40.32</v>
+        <v>322.83</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05:04:27</t>
+          <t>05:04:38</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="F22" t="n">
-        <v>6.74</v>
+        <v>7.53</v>
       </c>
       <c r="G22" t="n">
-        <v>236.4</v>
+        <v>232.1</v>
       </c>
       <c r="H22" t="n">
-        <v>17.8</v>
+        <v>14.4</v>
       </c>
       <c r="I22" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J22" t="n">
-        <v>-109.85</v>
+        <v>133.42</v>
       </c>
       <c r="K22" t="n">
-        <v>-4.49</v>
+        <v>118.39</v>
       </c>
       <c r="L22" t="n">
-        <v>109.94</v>
+        <v>178.38</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05:09:25</t>
+          <t>05:10:49</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="F23" t="n">
-        <v>7.98</v>
+        <v>8.19</v>
       </c>
       <c r="G23" t="n">
-        <v>237.7</v>
+        <v>248.4</v>
       </c>
       <c r="H23" t="n">
         <v>9.6</v>
       </c>
       <c r="I23" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J23" t="n">
-        <v>153.01</v>
+        <v>105.96</v>
       </c>
       <c r="K23" t="n">
-        <v>278.74</v>
+        <v>122.88</v>
       </c>
       <c r="L23" t="n">
-        <v>317.97</v>
+        <v>162.26</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:11:00</t>
+          <t>05:12:11</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>2.45</v>
+        <v>2.69</v>
       </c>
       <c r="F24" t="n">
-        <v>7.35</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>243.3</v>
+        <v>253.8</v>
       </c>
       <c r="H24" t="n">
-        <v>11.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J24" t="n">
-        <v>228.98</v>
+        <v>-243.08</v>
       </c>
       <c r="K24" t="n">
-        <v>-36.89</v>
+        <v>103.09</v>
       </c>
       <c r="L24" t="n">
-        <v>231.93</v>
+        <v>264.04</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:12:39</t>
+          <t>05:14:19</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="F25" t="n">
-        <v>7.49</v>
+        <v>7.75</v>
       </c>
       <c r="G25" t="n">
-        <v>225.9</v>
+        <v>228.8</v>
       </c>
       <c r="H25" t="n">
-        <v>17.1</v>
+        <v>11.2</v>
       </c>
       <c r="I25" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J25" t="n">
-        <v>-300.11</v>
+        <v>13.96</v>
       </c>
       <c r="K25" t="n">
-        <v>-308.48</v>
+        <v>-236.85</v>
       </c>
       <c r="L25" t="n">
-        <v>430.38</v>
+        <v>237.26</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:16:24</t>
+          <t>05:20:02</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>2.55</v>
+        <v>2.31</v>
       </c>
       <c r="F26" t="n">
-        <v>7.9</v>
+        <v>7.13</v>
       </c>
       <c r="G26" t="n">
-        <v>240.9</v>
+        <v>231.4</v>
       </c>
       <c r="H26" t="n">
-        <v>12.7</v>
+        <v>15.9</v>
       </c>
       <c r="I26" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J26" t="n">
-        <v>222.5</v>
+        <v>135.65</v>
       </c>
       <c r="K26" t="n">
-        <v>-297.87</v>
+        <v>96.02</v>
       </c>
       <c r="L26" t="n">
-        <v>371.79</v>
+        <v>166.19</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:18:03</t>
+          <t>05:22:24</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="F27" t="n">
-        <v>8.1</v>
+        <v>7.68</v>
       </c>
       <c r="G27" t="n">
-        <v>233.3</v>
+        <v>224.6</v>
       </c>
       <c r="H27" t="n">
-        <v>13.5</v>
+        <v>14.3</v>
       </c>
       <c r="I27" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J27" t="n">
-        <v>-211.68</v>
+        <v>-356.32</v>
       </c>
       <c r="K27" t="n">
-        <v>125.88</v>
+        <v>-12.83</v>
       </c>
       <c r="L27" t="n">
-        <v>246.28</v>
+        <v>356.55</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:19:24</t>
+          <t>05:24:17</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="F28" t="n">
-        <v>7.3</v>
+        <v>7.63</v>
       </c>
       <c r="G28" t="n">
-        <v>254.4</v>
+        <v>246.8</v>
       </c>
       <c r="H28" t="n">
-        <v>15.7</v>
+        <v>14.3</v>
       </c>
       <c r="I28" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J28" t="n">
-        <v>-297.22</v>
+        <v>-72.56</v>
       </c>
       <c r="K28" t="n">
-        <v>16.61</v>
+        <v>-128.58</v>
       </c>
       <c r="L28" t="n">
-        <v>297.68</v>
+        <v>147.64</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:27:10</t>
+          <t>05:33:38</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>2.69</v>
+        <v>2.24</v>
       </c>
       <c r="F29" t="n">
-        <v>6.95</v>
+        <v>7.87</v>
       </c>
       <c r="G29" t="n">
-        <v>234.8</v>
+        <v>241.4</v>
       </c>
       <c r="H29" t="n">
-        <v>22.1</v>
+        <v>21.7</v>
       </c>
       <c r="I29" t="n">
         <v>26</v>
       </c>
       <c r="J29" t="n">
-        <v>24.63</v>
+        <v>-19.6</v>
       </c>
       <c r="K29" t="n">
-        <v>-8.199999999999999</v>
+        <v>73.97</v>
       </c>
       <c r="L29" t="n">
-        <v>25.96</v>
+        <v>76.52</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:28:16</t>
+          <t>05:36:16</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2.34</v>
+        <v>2.9</v>
       </c>
       <c r="F30" t="n">
-        <v>7.61</v>
+        <v>7.68</v>
       </c>
       <c r="G30" t="n">
-        <v>245.7</v>
+        <v>238</v>
       </c>
       <c r="H30" t="n">
-        <v>13.5</v>
+        <v>16.7</v>
       </c>
       <c r="I30" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J30" t="n">
-        <v>20.74</v>
+        <v>-131.22</v>
       </c>
       <c r="K30" t="n">
-        <v>19.12</v>
+        <v>-101.85</v>
       </c>
       <c r="L30" t="n">
-        <v>28.21</v>
+        <v>166.11</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:30:05</t>
+          <t>05:38:13</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.2</v>
+        <v>2.43</v>
       </c>
       <c r="F31" t="n">
-        <v>7.88</v>
+        <v>7.13</v>
       </c>
       <c r="G31" t="n">
-        <v>230.5</v>
+        <v>235.2</v>
       </c>
       <c r="H31" t="n">
-        <v>8</v>
+        <v>13.4</v>
       </c>
       <c r="I31" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>101.44</v>
+        <v>-29.79</v>
       </c>
       <c r="K31" t="n">
-        <v>33.2</v>
+        <v>-55.63</v>
       </c>
       <c r="L31" t="n">
-        <v>106.73</v>
+        <v>63.11</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:35:30</t>
+          <t>05:42:02</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>3.17</v>
+        <v>2.65</v>
       </c>
       <c r="F32" t="n">
-        <v>8.289999999999999</v>
+        <v>7.64</v>
       </c>
       <c r="G32" t="n">
-        <v>217.6</v>
+        <v>237.7</v>
       </c>
       <c r="H32" t="n">
-        <v>9</v>
+        <v>5.6</v>
       </c>
       <c r="I32" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J32" t="n">
-        <v>-151.38</v>
+        <v>-52.98</v>
       </c>
       <c r="K32" t="n">
-        <v>-21.23</v>
+        <v>-87.48</v>
       </c>
       <c r="L32" t="n">
-        <v>152.86</v>
+        <v>102.27</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:36:33</t>
+          <t>05:44:01</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>2.85</v>
+        <v>2.43</v>
       </c>
       <c r="F33" t="n">
-        <v>7.57</v>
+        <v>8.59</v>
       </c>
       <c r="G33" t="n">
-        <v>248.7</v>
+        <v>237.3</v>
       </c>
       <c r="H33" t="n">
-        <v>6.5</v>
+        <v>12.2</v>
       </c>
       <c r="I33" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J33" t="n">
-        <v>-11.88</v>
+        <v>56.17</v>
       </c>
       <c r="K33" t="n">
-        <v>9.26</v>
+        <v>66.66</v>
       </c>
       <c r="L33" t="n">
-        <v>15.07</v>
+        <v>87.17</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:38:29</t>
+          <t>05:45:13</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>2.29</v>
+        <v>2.61</v>
       </c>
       <c r="F34" t="n">
-        <v>7.46</v>
+        <v>7.37</v>
       </c>
       <c r="G34" t="n">
-        <v>246.2</v>
+        <v>238.5</v>
       </c>
       <c r="H34" t="n">
-        <v>13.8</v>
+        <v>14.3</v>
       </c>
       <c r="I34" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J34" t="n">
-        <v>-83.53</v>
+        <v>192.22</v>
       </c>
       <c r="K34" t="n">
-        <v>-20.33</v>
+        <v>114.67</v>
       </c>
       <c r="L34" t="n">
-        <v>85.97</v>
+        <v>223.82</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:42:02</t>
+          <t>05:50:02</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>3.14</v>
+        <v>2.51</v>
       </c>
       <c r="F35" t="n">
-        <v>7.84</v>
+        <v>8.19</v>
       </c>
       <c r="G35" t="n">
-        <v>234.6</v>
+        <v>245.3</v>
       </c>
       <c r="H35" t="n">
-        <v>8.1</v>
+        <v>12.5</v>
       </c>
       <c r="I35" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J35" t="n">
-        <v>-134.47</v>
+        <v>-67.14</v>
       </c>
       <c r="K35" t="n">
-        <v>-151.5</v>
+        <v>268.13</v>
       </c>
       <c r="L35" t="n">
-        <v>202.57</v>
+        <v>276.41</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:44:49</t>
+          <t>05:51:23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2.25</v>
+        <v>2.47</v>
       </c>
       <c r="F36" t="n">
-        <v>7.77</v>
+        <v>7.48</v>
       </c>
       <c r="G36" t="n">
-        <v>255.7</v>
+        <v>239.7</v>
       </c>
       <c r="H36" t="n">
-        <v>11.5</v>
+        <v>14.3</v>
       </c>
       <c r="I36" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J36" t="n">
-        <v>91.04000000000001</v>
+        <v>164.2</v>
       </c>
       <c r="K36" t="n">
-        <v>-196.56</v>
+        <v>-134.06</v>
       </c>
       <c r="L36" t="n">
-        <v>216.62</v>
+        <v>211.98</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:46:50</t>
+          <t>05:52:41</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>2.11</v>
+        <v>2.36</v>
       </c>
       <c r="F37" t="n">
-        <v>7.81</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="G37" t="n">
-        <v>248.7</v>
+        <v>245.8</v>
       </c>
       <c r="H37" t="n">
-        <v>18.4</v>
+        <v>11.5</v>
       </c>
       <c r="I37" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J37" t="n">
-        <v>-269.75</v>
+        <v>20.06</v>
       </c>
       <c r="K37" t="n">
-        <v>56.47</v>
+        <v>-155.11</v>
       </c>
       <c r="L37" t="n">
-        <v>275.6</v>
+        <v>156.4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05:52:23</t>
+          <t>05:58:05</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="F38" t="n">
-        <v>7.98</v>
+        <v>7.31</v>
       </c>
       <c r="G38" t="n">
-        <v>239.7</v>
+        <v>230</v>
       </c>
       <c r="H38" t="n">
-        <v>14</v>
+        <v>13.6</v>
       </c>
       <c r="I38" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J38" t="n">
-        <v>20.6</v>
+        <v>63.85</v>
       </c>
       <c r="K38" t="n">
-        <v>-111.7</v>
+        <v>-329.4</v>
       </c>
       <c r="L38" t="n">
-        <v>113.58</v>
+        <v>335.53</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>05:53:45</t>
+          <t>05:59:37</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>2.4</v>
+        <v>2.22</v>
       </c>
       <c r="F39" t="n">
-        <v>8.01</v>
+        <v>8.26</v>
       </c>
       <c r="G39" t="n">
-        <v>232.1</v>
+        <v>238</v>
       </c>
       <c r="H39" t="n">
-        <v>15.3</v>
+        <v>6.3</v>
       </c>
       <c r="I39" t="n">
         <v>27</v>
       </c>
       <c r="J39" t="n">
-        <v>194.6</v>
+        <v>-305.89</v>
       </c>
       <c r="K39" t="n">
-        <v>232.92</v>
+        <v>41.59</v>
       </c>
       <c r="L39" t="n">
-        <v>303.51</v>
+        <v>308.7</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>05:55:12</t>
+          <t>06:01:42</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>2.52</v>
+        <v>2.23</v>
       </c>
       <c r="F40" t="n">
-        <v>7.31</v>
+        <v>7.84</v>
       </c>
       <c r="G40" t="n">
-        <v>230.5</v>
+        <v>247.5</v>
       </c>
       <c r="H40" t="n">
-        <v>17.1</v>
+        <v>13</v>
       </c>
       <c r="I40" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>-232.44</v>
+        <v>103.95</v>
       </c>
       <c r="K40" t="n">
-        <v>-95.45999999999999</v>
+        <v>-376.02</v>
       </c>
       <c r="L40" t="n">
-        <v>251.28</v>
+        <v>390.12</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>05:59:01</t>
+          <t>06:06:30</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>2.41</v>
+        <v>2.29</v>
       </c>
       <c r="F41" t="n">
-        <v>7.42</v>
+        <v>7.53</v>
       </c>
       <c r="G41" t="n">
-        <v>237.2</v>
+        <v>236.6</v>
       </c>
       <c r="H41" t="n">
-        <v>13.2</v>
+        <v>12.7</v>
       </c>
       <c r="I41" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J41" t="n">
-        <v>-36.67</v>
+        <v>137.18</v>
       </c>
       <c r="K41" t="n">
-        <v>-136.29</v>
+        <v>26.84</v>
       </c>
       <c r="L41" t="n">
-        <v>141.13</v>
+        <v>139.78</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06:00:13</t>
+          <t>06:08:17</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>2.57</v>
+        <v>3.41</v>
       </c>
       <c r="F42" t="n">
-        <v>8.029999999999999</v>
+        <v>8.06</v>
       </c>
       <c r="G42" t="n">
-        <v>236.9</v>
+        <v>237.2</v>
       </c>
       <c r="H42" t="n">
-        <v>11.5</v>
+        <v>11.3</v>
       </c>
       <c r="I42" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J42" t="n">
-        <v>254.38</v>
+        <v>531.65</v>
       </c>
       <c r="K42" t="n">
-        <v>-378.75</v>
+        <v>-457.03</v>
       </c>
       <c r="L42" t="n">
-        <v>456.24</v>
+        <v>701.09</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06:01:50</t>
+          <t>06:08:57</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="F43" t="n">
-        <v>7.78</v>
+        <v>7.45</v>
       </c>
       <c r="G43" t="n">
-        <v>234.4</v>
+        <v>233.7</v>
       </c>
       <c r="H43" t="n">
-        <v>24.3</v>
+        <v>11.5</v>
       </c>
       <c r="I43" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J43" t="n">
-        <v>-143.07</v>
+        <v>-128.84</v>
       </c>
       <c r="K43" t="n">
-        <v>-3.4</v>
+        <v>-61.68</v>
       </c>
       <c r="L43" t="n">
-        <v>143.11</v>
+        <v>142.85</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:11:21</t>
+          <t>06:20:25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>2.27</v>
+        <v>1.65</v>
       </c>
       <c r="F44" t="n">
-        <v>6.63</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="G44" t="n">
-        <v>233.3</v>
+        <v>246</v>
       </c>
       <c r="H44" t="n">
-        <v>17.6</v>
+        <v>13.6</v>
       </c>
       <c r="I44" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J44" t="n">
-        <v>91.29000000000001</v>
+        <v>43.14</v>
       </c>
       <c r="K44" t="n">
-        <v>-8.880000000000001</v>
+        <v>-59.29</v>
       </c>
       <c r="L44" t="n">
-        <v>91.72</v>
+        <v>73.31999999999999</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:12:45</t>
+          <t>06:21:00</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="F45" t="n">
-        <v>7.72</v>
+        <v>7.67</v>
       </c>
       <c r="G45" t="n">
-        <v>240.6</v>
+        <v>248.9</v>
       </c>
       <c r="H45" t="n">
         <v>12.8</v>
       </c>
       <c r="I45" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J45" t="n">
-        <v>29.11</v>
+        <v>-68.14</v>
       </c>
       <c r="K45" t="n">
-        <v>4.34</v>
+        <v>92.42</v>
       </c>
       <c r="L45" t="n">
-        <v>29.44</v>
+        <v>114.82</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:14:39</t>
+          <t>06:23:29</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>2.98</v>
+        <v>2.36</v>
       </c>
       <c r="F46" t="n">
-        <v>7.47</v>
+        <v>7.7</v>
       </c>
       <c r="G46" t="n">
-        <v>237.3</v>
+        <v>243</v>
       </c>
       <c r="H46" t="n">
-        <v>9.699999999999999</v>
+        <v>14.4</v>
       </c>
       <c r="I46" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J46" t="n">
-        <v>-105.23</v>
+        <v>67.2</v>
       </c>
       <c r="K46" t="n">
-        <v>12.76</v>
+        <v>133.95</v>
       </c>
       <c r="L46" t="n">
-        <v>106</v>
+        <v>149.86</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:18:18</t>
+          <t>06:28:42</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>2.84</v>
+        <v>2.38</v>
       </c>
       <c r="F47" t="n">
-        <v>7.27</v>
+        <v>7.82</v>
       </c>
       <c r="G47" t="n">
-        <v>239.8</v>
+        <v>236.7</v>
       </c>
       <c r="H47" t="n">
-        <v>17.6</v>
+        <v>12.2</v>
       </c>
       <c r="I47" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>51.01</v>
+        <v>-42.27</v>
       </c>
       <c r="K47" t="n">
-        <v>-27.78</v>
+        <v>-16.74</v>
       </c>
       <c r="L47" t="n">
-        <v>58.09</v>
+        <v>45.46</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:19:38</t>
+          <t>06:30:28</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>2.46</v>
+        <v>2.89</v>
       </c>
       <c r="F48" t="n">
-        <v>6.66</v>
+        <v>7.66</v>
       </c>
       <c r="G48" t="n">
-        <v>247</v>
+        <v>228.1</v>
       </c>
       <c r="H48" t="n">
-        <v>13.3</v>
+        <v>8.6</v>
       </c>
       <c r="I48" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J48" t="n">
-        <v>56.73</v>
+        <v>-181.14</v>
       </c>
       <c r="K48" t="n">
-        <v>-67.73999999999999</v>
+        <v>69.75</v>
       </c>
       <c r="L48" t="n">
-        <v>88.36</v>
+        <v>194.1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:21:11</t>
+          <t>06:32:53</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>2.42</v>
+        <v>2.7</v>
       </c>
       <c r="F49" t="n">
-        <v>7.53</v>
+        <v>7.84</v>
       </c>
       <c r="G49" t="n">
-        <v>240.7</v>
+        <v>242.5</v>
       </c>
       <c r="H49" t="n">
-        <v>15.8</v>
+        <v>14.3</v>
       </c>
       <c r="I49" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J49" t="n">
-        <v>-102.59</v>
+        <v>-18.04</v>
       </c>
       <c r="K49" t="n">
-        <v>39.73</v>
+        <v>-37.24</v>
       </c>
       <c r="L49" t="n">
-        <v>110.01</v>
+        <v>41.37</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:25:23</t>
+          <t>06:38:30</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>2.51</v>
+        <v>2.67</v>
       </c>
       <c r="F50" t="n">
-        <v>7.81</v>
+        <v>7.63</v>
       </c>
       <c r="G50" t="n">
-        <v>235.5</v>
+        <v>243.7</v>
       </c>
       <c r="H50" t="n">
-        <v>15.2</v>
+        <v>13.6</v>
       </c>
       <c r="I50" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J50" t="n">
-        <v>-66.81999999999999</v>
+        <v>180.34</v>
       </c>
       <c r="K50" t="n">
-        <v>-50.72</v>
+        <v>-24.94</v>
       </c>
       <c r="L50" t="n">
-        <v>83.88</v>
+        <v>182.06</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:26:38</t>
+          <t>06:40:02</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="F51" t="n">
-        <v>7.3</v>
+        <v>7.69</v>
       </c>
       <c r="G51" t="n">
-        <v>252</v>
+        <v>226.9</v>
       </c>
       <c r="H51" t="n">
-        <v>19</v>
+        <v>12.2</v>
       </c>
       <c r="I51" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J51" t="n">
-        <v>-43.05</v>
+        <v>92.66</v>
       </c>
       <c r="K51" t="n">
-        <v>-98.12</v>
+        <v>192.84</v>
       </c>
       <c r="L51" t="n">
-        <v>107.15</v>
+        <v>213.95</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:27:32</t>
+          <t>06:41:46</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="F52" t="n">
-        <v>8.109999999999999</v>
+        <v>7.38</v>
       </c>
       <c r="G52" t="n">
-        <v>239</v>
+        <v>227.2</v>
       </c>
       <c r="H52" t="n">
-        <v>18.7</v>
+        <v>14.4</v>
       </c>
       <c r="I52" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J52" t="n">
-        <v>57.35</v>
+        <v>91.06999999999999</v>
       </c>
       <c r="K52" t="n">
-        <v>84.45999999999999</v>
+        <v>-165.08</v>
       </c>
       <c r="L52" t="n">
-        <v>102.09</v>
+        <v>188.53</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:32:50</t>
+          <t>06:46:15</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>2.78</v>
+        <v>2.49</v>
       </c>
       <c r="F53" t="n">
-        <v>7.15</v>
+        <v>8.07</v>
       </c>
       <c r="G53" t="n">
-        <v>234.6</v>
+        <v>242.8</v>
       </c>
       <c r="H53" t="n">
-        <v>15.8</v>
+        <v>16.7</v>
       </c>
       <c r="I53" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J53" t="n">
-        <v>300.58</v>
+        <v>226.53</v>
       </c>
       <c r="K53" t="n">
-        <v>-320.11</v>
+        <v>-284.19</v>
       </c>
       <c r="L53" t="n">
-        <v>439.11</v>
+        <v>363.43</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:34:15</t>
+          <t>06:47:23</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>2.39</v>
+        <v>2.23</v>
       </c>
       <c r="F54" t="n">
-        <v>7.43</v>
+        <v>7.36</v>
       </c>
       <c r="G54" t="n">
-        <v>233.5</v>
+        <v>247.3</v>
       </c>
       <c r="H54" t="n">
-        <v>16.7</v>
+        <v>13.5</v>
       </c>
       <c r="I54" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J54" t="n">
-        <v>-118.91</v>
+        <v>-57.1</v>
       </c>
       <c r="K54" t="n">
-        <v>-50.7</v>
+        <v>105.8</v>
       </c>
       <c r="L54" t="n">
-        <v>129.27</v>
+        <v>120.23</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:35:19</t>
+          <t>06:48:47</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>2.82</v>
+        <v>2.45</v>
       </c>
       <c r="F55" t="n">
-        <v>7.87</v>
+        <v>7.64</v>
       </c>
       <c r="G55" t="n">
-        <v>238.3</v>
+        <v>247.1</v>
       </c>
       <c r="H55" t="n">
-        <v>18.5</v>
+        <v>11.2</v>
       </c>
       <c r="I55" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J55" t="n">
-        <v>193.68</v>
+        <v>206.54</v>
       </c>
       <c r="K55" t="n">
-        <v>267.78</v>
+        <v>-111.15</v>
       </c>
       <c r="L55" t="n">
-        <v>330.48</v>
+        <v>234.55</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:40:20</t>
+          <t>06:53:52</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>2.82</v>
+        <v>2.93</v>
       </c>
       <c r="F56" t="n">
-        <v>7.3</v>
+        <v>8.52</v>
       </c>
       <c r="G56" t="n">
-        <v>234.8</v>
+        <v>225.7</v>
       </c>
       <c r="H56" t="n">
-        <v>18.7</v>
+        <v>13.7</v>
       </c>
       <c r="I56" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J56" t="n">
-        <v>-56.69</v>
+        <v>-131.83</v>
       </c>
       <c r="K56" t="n">
-        <v>224.87</v>
+        <v>264.01</v>
       </c>
       <c r="L56" t="n">
-        <v>231.91</v>
+        <v>295.09</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06:42:03</t>
+          <t>06:55:55</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>2.59</v>
+        <v>2.76</v>
       </c>
       <c r="F57" t="n">
-        <v>7.05</v>
+        <v>7.87</v>
       </c>
       <c r="G57" t="n">
-        <v>237</v>
+        <v>228.2</v>
       </c>
       <c r="H57" t="n">
-        <v>15.1</v>
+        <v>14.8</v>
       </c>
       <c r="I57" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J57" t="n">
-        <v>-421.64</v>
+        <v>250.49</v>
       </c>
       <c r="K57" t="n">
-        <v>-30.38</v>
+        <v>55.84</v>
       </c>
       <c r="L57" t="n">
-        <v>422.74</v>
+        <v>256.63</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06:44:58</t>
+          <t>06:57:27</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>2.39</v>
+        <v>2.55</v>
       </c>
       <c r="F58" t="n">
-        <v>7.66</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G58" t="n">
-        <v>251.9</v>
+        <v>244</v>
       </c>
       <c r="H58" t="n">
-        <v>11.6</v>
+        <v>10</v>
       </c>
       <c r="I58" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J58" t="n">
-        <v>-145.3</v>
+        <v>154.06</v>
       </c>
       <c r="K58" t="n">
-        <v>-165.81</v>
+        <v>131.85</v>
       </c>
       <c r="L58" t="n">
-        <v>220.47</v>
+        <v>202.78</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06:56:07</t>
+          <t>07:10:03</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>2.53</v>
+        <v>2.62</v>
       </c>
       <c r="F59" t="n">
-        <v>6.84</v>
+        <v>8.16</v>
       </c>
       <c r="G59" t="n">
-        <v>250.7</v>
+        <v>220.6</v>
       </c>
       <c r="H59" t="n">
-        <v>17.6</v>
+        <v>10.4</v>
       </c>
       <c r="I59" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>-73.86</v>
+        <v>-3.83</v>
       </c>
       <c r="K59" t="n">
-        <v>98.61</v>
+        <v>-198.23</v>
       </c>
       <c r="L59" t="n">
-        <v>123.2</v>
+        <v>198.27</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06:56:57</t>
+          <t>07:10:55</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="F60" t="n">
-        <v>7.76</v>
+        <v>7.95</v>
       </c>
       <c r="G60" t="n">
-        <v>237.6</v>
+        <v>232.1</v>
       </c>
       <c r="H60" t="n">
-        <v>19.9</v>
+        <v>21.4</v>
       </c>
       <c r="I60" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J60" t="n">
-        <v>102.25</v>
+        <v>2.97</v>
       </c>
       <c r="K60" t="n">
-        <v>29.03</v>
+        <v>84.05</v>
       </c>
       <c r="L60" t="n">
-        <v>106.29</v>
+        <v>84.09999999999999</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>06:58:54</t>
+          <t>07:12:38</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>2.66</v>
+        <v>2.53</v>
       </c>
       <c r="F61" t="n">
-        <v>7.38</v>
+        <v>7.33</v>
       </c>
       <c r="G61" t="n">
-        <v>225.2</v>
+        <v>246.4</v>
       </c>
       <c r="H61" t="n">
-        <v>8.1</v>
+        <v>13.7</v>
       </c>
       <c r="I61" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J61" t="n">
-        <v>-26.34</v>
+        <v>26.38</v>
       </c>
       <c r="K61" t="n">
-        <v>-75.39</v>
+        <v>43.94</v>
       </c>
       <c r="L61" t="n">
-        <v>79.86</v>
+        <v>51.25</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:03:13</t>
+          <t>07:18:10</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="F62" t="n">
-        <v>7.52</v>
+        <v>7.98</v>
       </c>
       <c r="G62" t="n">
-        <v>245</v>
+        <v>234.2</v>
       </c>
       <c r="H62" t="n">
-        <v>16.7</v>
+        <v>13.5</v>
       </c>
       <c r="I62" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="J62" t="n">
-        <v>-41.23</v>
+        <v>-144</v>
       </c>
       <c r="K62" t="n">
-        <v>36.65</v>
+        <v>-160.6</v>
       </c>
       <c r="L62" t="n">
-        <v>55.16</v>
+        <v>215.7</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:04:56</t>
+          <t>07:19:50</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>2.69</v>
+        <v>2.21</v>
       </c>
       <c r="F63" t="n">
-        <v>7.49</v>
+        <v>7.57</v>
       </c>
       <c r="G63" t="n">
-        <v>229.2</v>
+        <v>238.8</v>
       </c>
       <c r="H63" t="n">
-        <v>7.2</v>
+        <v>14.7</v>
       </c>
       <c r="I63" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J63" t="n">
-        <v>111.82</v>
+        <v>11.19</v>
       </c>
       <c r="K63" t="n">
-        <v>10.58</v>
+        <v>-225.67</v>
       </c>
       <c r="L63" t="n">
-        <v>112.32</v>
+        <v>225.94</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:06:28</t>
+          <t>07:21:08</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>2.86</v>
+        <v>2.56</v>
       </c>
       <c r="F64" t="n">
-        <v>7.89</v>
+        <v>7.05</v>
       </c>
       <c r="G64" t="n">
-        <v>238.8</v>
+        <v>251.2</v>
       </c>
       <c r="H64" t="n">
-        <v>11.4</v>
+        <v>20.1</v>
       </c>
       <c r="I64" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J64" t="n">
-        <v>-147.73</v>
+        <v>-147.48</v>
       </c>
       <c r="K64" t="n">
-        <v>-35.11</v>
+        <v>139.51</v>
       </c>
       <c r="L64" t="n">
-        <v>151.84</v>
+        <v>203.01</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:10:55</t>
+          <t>07:24:27</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>2.05</v>
+        <v>3.2</v>
       </c>
       <c r="F65" t="n">
-        <v>8.01</v>
+        <v>7.78</v>
       </c>
       <c r="G65" t="n">
-        <v>228.8</v>
+        <v>247</v>
       </c>
       <c r="H65" t="n">
-        <v>11</v>
+        <v>18.3</v>
       </c>
       <c r="I65" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J65" t="n">
-        <v>6</v>
+        <v>124.46</v>
       </c>
       <c r="K65" t="n">
-        <v>57.9</v>
+        <v>140.7</v>
       </c>
       <c r="L65" t="n">
-        <v>58.21</v>
+        <v>187.84</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:13:02</t>
+          <t>07:26:39</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>2.91</v>
+        <v>2.6</v>
       </c>
       <c r="F66" t="n">
-        <v>7.33</v>
+        <v>7.3</v>
       </c>
       <c r="G66" t="n">
-        <v>245.9</v>
+        <v>251</v>
       </c>
       <c r="H66" t="n">
-        <v>13.5</v>
+        <v>18</v>
       </c>
       <c r="I66" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J66" t="n">
-        <v>-96.73</v>
+        <v>51.89</v>
       </c>
       <c r="K66" t="n">
-        <v>-144.74</v>
+        <v>83.20999999999999</v>
       </c>
       <c r="L66" t="n">
-        <v>174.09</v>
+        <v>98.06</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:14:00</t>
+          <t>07:28:45</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="F67" t="n">
-        <v>7.28</v>
+        <v>7.42</v>
       </c>
       <c r="G67" t="n">
-        <v>227.4</v>
+        <v>251.8</v>
       </c>
       <c r="H67" t="n">
-        <v>6.6</v>
+        <v>15.6</v>
       </c>
       <c r="I67" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J67" t="n">
-        <v>79</v>
+        <v>-197.4</v>
       </c>
       <c r="K67" t="n">
-        <v>103.04</v>
+        <v>-28.84</v>
       </c>
       <c r="L67" t="n">
-        <v>129.84</v>
+        <v>199.5</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:20:15</t>
+          <t>07:32:58</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="F68" t="n">
-        <v>7.5</v>
+        <v>7.56</v>
       </c>
       <c r="G68" t="n">
-        <v>235.8</v>
+        <v>235.5</v>
       </c>
       <c r="H68" t="n">
-        <v>14.6</v>
+        <v>15.2</v>
       </c>
       <c r="I68" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J68" t="n">
-        <v>182.72</v>
+        <v>-210.07</v>
       </c>
       <c r="K68" t="n">
-        <v>228.16</v>
+        <v>27.19</v>
       </c>
       <c r="L68" t="n">
-        <v>292.31</v>
+        <v>211.82</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:21:51</t>
+          <t>07:35:41</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>2.75</v>
+        <v>2.83</v>
       </c>
       <c r="F69" t="n">
-        <v>7.72</v>
+        <v>7.13</v>
       </c>
       <c r="G69" t="n">
-        <v>258.5</v>
+        <v>236.8</v>
       </c>
       <c r="H69" t="n">
-        <v>15.4</v>
+        <v>6.8</v>
       </c>
       <c r="I69" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>-57.58</v>
+        <v>-267.15</v>
       </c>
       <c r="K69" t="n">
-        <v>67.06999999999999</v>
+        <v>-366.5</v>
       </c>
       <c r="L69" t="n">
-        <v>88.40000000000001</v>
+        <v>453.54</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:22:41</t>
+          <t>07:36:50</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="F70" t="n">
-        <v>7.47</v>
+        <v>6.8</v>
       </c>
       <c r="G70" t="n">
-        <v>234</v>
+        <v>241.9</v>
       </c>
       <c r="H70" t="n">
-        <v>14.7</v>
+        <v>7.5</v>
       </c>
       <c r="I70" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>198.25</v>
+        <v>-156.89</v>
       </c>
       <c r="K70" t="n">
-        <v>46.76</v>
+        <v>178.68</v>
       </c>
       <c r="L70" t="n">
-        <v>203.69</v>
+        <v>237.79</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:28:03</t>
+          <t>07:42:21</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>2.72</v>
+        <v>2.99</v>
       </c>
       <c r="F71" t="n">
-        <v>7.65</v>
+        <v>8.19</v>
       </c>
       <c r="G71" t="n">
-        <v>251.5</v>
+        <v>240.8</v>
       </c>
       <c r="H71" t="n">
-        <v>9.6</v>
+        <v>3.8</v>
       </c>
       <c r="I71" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J71" t="n">
-        <v>138.56</v>
+        <v>106.91</v>
       </c>
       <c r="K71" t="n">
-        <v>6.59</v>
+        <v>-403.18</v>
       </c>
       <c r="L71" t="n">
-        <v>138.71</v>
+        <v>417.11</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:28:49</t>
+          <t>07:44:23</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>2.37</v>
+        <v>2.55</v>
       </c>
       <c r="F72" t="n">
-        <v>7.47</v>
+        <v>7.98</v>
       </c>
       <c r="G72" t="n">
-        <v>233.7</v>
+        <v>228.5</v>
       </c>
       <c r="H72" t="n">
-        <v>15.9</v>
+        <v>7.8</v>
       </c>
       <c r="I72" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J72" t="n">
-        <v>176.19</v>
+        <v>-347.87</v>
       </c>
       <c r="K72" t="n">
-        <v>-101.11</v>
+        <v>393.95</v>
       </c>
       <c r="L72" t="n">
-        <v>203.14</v>
+        <v>525.5599999999999</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:30:56</t>
+          <t>07:45:18</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>2.5</v>
+        <v>2.79</v>
       </c>
       <c r="F73" t="n">
-        <v>8.039999999999999</v>
+        <v>8.16</v>
       </c>
       <c r="G73" t="n">
-        <v>239.2</v>
+        <v>237.5</v>
       </c>
       <c r="H73" t="n">
-        <v>16.4</v>
+        <v>21.7</v>
       </c>
       <c r="I73" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>120.06</v>
+        <v>-224.03</v>
       </c>
       <c r="K73" t="n">
-        <v>106.09</v>
+        <v>-206.43</v>
       </c>
       <c r="L73" t="n">
-        <v>160.22</v>
+        <v>304.64</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:39:55</t>
+          <t>07:54:48</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>2.47</v>
+        <v>3.05</v>
       </c>
       <c r="F74" t="n">
-        <v>7.72</v>
+        <v>7.55</v>
       </c>
       <c r="G74" t="n">
-        <v>238.3</v>
+        <v>242.1</v>
       </c>
       <c r="H74" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="I74" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J74" t="n">
-        <v>71.95</v>
+        <v>22.83</v>
       </c>
       <c r="K74" t="n">
-        <v>19.36</v>
+        <v>-128.43</v>
       </c>
       <c r="L74" t="n">
-        <v>74.51000000000001</v>
+        <v>130.44</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:41:24</t>
+          <t>07:55:54</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>2.41</v>
+        <v>2.59</v>
       </c>
       <c r="F75" t="n">
-        <v>7.64</v>
+        <v>8.23</v>
       </c>
       <c r="G75" t="n">
-        <v>226.2</v>
+        <v>229.6</v>
       </c>
       <c r="H75" t="n">
-        <v>11.3</v>
+        <v>13.2</v>
       </c>
       <c r="I75" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J75" t="n">
-        <v>77.05</v>
+        <v>132.96</v>
       </c>
       <c r="K75" t="n">
-        <v>-93.03</v>
+        <v>-12.88</v>
       </c>
       <c r="L75" t="n">
-        <v>120.79</v>
+        <v>133.59</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07:43:42</t>
+          <t>07:58:28</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>2.71</v>
+        <v>2.57</v>
       </c>
       <c r="F76" t="n">
-        <v>7.24</v>
+        <v>7.89</v>
       </c>
       <c r="G76" t="n">
-        <v>249.1</v>
+        <v>236.3</v>
       </c>
       <c r="H76" t="n">
-        <v>18.1</v>
+        <v>11.2</v>
       </c>
       <c r="I76" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J76" t="n">
-        <v>12.12</v>
+        <v>59.41</v>
       </c>
       <c r="K76" t="n">
-        <v>-72.73999999999999</v>
+        <v>48.93</v>
       </c>
       <c r="L76" t="n">
-        <v>73.75</v>
+        <v>76.97</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07:47:33</t>
+          <t>08:03:41</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>2.66</v>
+        <v>3.02</v>
       </c>
       <c r="F77" t="n">
-        <v>7.89</v>
+        <v>8.44</v>
       </c>
       <c r="G77" t="n">
-        <v>245.9</v>
+        <v>230.8</v>
       </c>
       <c r="H77" t="n">
-        <v>9.5</v>
+        <v>13.1</v>
       </c>
       <c r="I77" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J77" t="n">
-        <v>42.05</v>
+        <v>-165.27</v>
       </c>
       <c r="K77" t="n">
-        <v>19.96</v>
+        <v>61.51</v>
       </c>
       <c r="L77" t="n">
-        <v>46.55</v>
+        <v>176.35</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07:50:14</t>
+          <t>08:05:28</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>2.88</v>
+        <v>3.11</v>
       </c>
       <c r="F78" t="n">
-        <v>7.38</v>
+        <v>7.4</v>
       </c>
       <c r="G78" t="n">
-        <v>245.1</v>
+        <v>221.7</v>
       </c>
       <c r="H78" t="n">
-        <v>9.800000000000001</v>
+        <v>17.5</v>
       </c>
       <c r="I78" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J78" t="n">
-        <v>86.36</v>
+        <v>79.54000000000001</v>
       </c>
       <c r="K78" t="n">
-        <v>-69.34999999999999</v>
+        <v>-166.02</v>
       </c>
       <c r="L78" t="n">
-        <v>110.76</v>
+        <v>184.09</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07:52:26</t>
+          <t>08:07:05</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>2.89</v>
+        <v>2.41</v>
       </c>
       <c r="F79" t="n">
-        <v>7.13</v>
+        <v>7.82</v>
       </c>
       <c r="G79" t="n">
-        <v>251.6</v>
+        <v>242.3</v>
       </c>
       <c r="H79" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="I79" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J79" t="n">
-        <v>-31.81</v>
+        <v>-108.94</v>
       </c>
       <c r="K79" t="n">
-        <v>10.29</v>
+        <v>53.56</v>
       </c>
       <c r="L79" t="n">
-        <v>33.43</v>
+        <v>121.39</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>07:56:53</t>
+          <t>08:11:12</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>2.34</v>
+        <v>2.88</v>
       </c>
       <c r="F80" t="n">
-        <v>7.54</v>
+        <v>7.88</v>
       </c>
       <c r="G80" t="n">
-        <v>241.9</v>
+        <v>228.4</v>
       </c>
       <c r="H80" t="n">
-        <v>18.6</v>
+        <v>14.7</v>
       </c>
       <c r="I80" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J80" t="n">
-        <v>-53.29</v>
+        <v>-89.40000000000001</v>
       </c>
       <c r="K80" t="n">
-        <v>157.52</v>
+        <v>-57.02</v>
       </c>
       <c r="L80" t="n">
-        <v>166.29</v>
+        <v>106.03</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>07:58:38</t>
+          <t>08:13:37</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>3.03</v>
+        <v>2.56</v>
       </c>
       <c r="F81" t="n">
-        <v>7.62</v>
+        <v>8.25</v>
       </c>
       <c r="G81" t="n">
         <v>235.1</v>
       </c>
       <c r="H81" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="I81" t="n">
         <v>29</v>
       </c>
       <c r="J81" t="n">
-        <v>70.09</v>
+        <v>-234.16</v>
       </c>
       <c r="K81" t="n">
-        <v>-72.16</v>
+        <v>181.97</v>
       </c>
       <c r="L81" t="n">
-        <v>100.6</v>
+        <v>296.55</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>07:59:59</t>
+          <t>08:14:55</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>2.52</v>
+        <v>3.06</v>
       </c>
       <c r="F82" t="n">
-        <v>7.84</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="G82" t="n">
-        <v>241.2</v>
+        <v>237.1</v>
       </c>
       <c r="H82" t="n">
-        <v>12.9</v>
+        <v>3.4</v>
       </c>
       <c r="I82" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J82" t="n">
-        <v>-61.23</v>
+        <v>-160.86</v>
       </c>
       <c r="K82" t="n">
-        <v>-12.91</v>
+        <v>294.68</v>
       </c>
       <c r="L82" t="n">
-        <v>62.58</v>
+        <v>335.73</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:05:17</t>
+          <t>08:18:47</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>2.93</v>
+        <v>2.2</v>
       </c>
       <c r="F83" t="n">
-        <v>7.5</v>
+        <v>7.98</v>
       </c>
       <c r="G83" t="n">
-        <v>236.8</v>
+        <v>248.1</v>
       </c>
       <c r="H83" t="n">
-        <v>15.2</v>
+        <v>18.1</v>
       </c>
       <c r="I83" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J83" t="n">
-        <v>145.9</v>
+        <v>151.46</v>
       </c>
       <c r="K83" t="n">
-        <v>169.2</v>
+        <v>92.11</v>
       </c>
       <c r="L83" t="n">
-        <v>223.42</v>
+        <v>177.27</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:07:47</t>
+          <t>08:19:57</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="F84" t="n">
-        <v>7.37</v>
+        <v>7.53</v>
       </c>
       <c r="G84" t="n">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="H84" t="n">
-        <v>19.7</v>
+        <v>11.1</v>
       </c>
       <c r="I84" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J84" t="n">
-        <v>-276.23</v>
+        <v>-65.84</v>
       </c>
       <c r="K84" t="n">
-        <v>327.8</v>
+        <v>75.42</v>
       </c>
       <c r="L84" t="n">
-        <v>428.67</v>
+        <v>100.11</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:09:25</t>
+          <t>08:22:03</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>2.96</v>
+        <v>2.73</v>
       </c>
       <c r="F85" t="n">
-        <v>7.02</v>
+        <v>7.48</v>
       </c>
       <c r="G85" t="n">
-        <v>241.5</v>
+        <v>235</v>
       </c>
       <c r="H85" t="n">
-        <v>17.7</v>
+        <v>17.5</v>
       </c>
       <c r="I85" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J85" t="n">
-        <v>-112.12</v>
+        <v>-267.35</v>
       </c>
       <c r="K85" t="n">
-        <v>-192</v>
+        <v>58.42</v>
       </c>
       <c r="L85" t="n">
-        <v>222.34</v>
+        <v>273.66</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:15:20</t>
+          <t>08:27:28</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>3.17</v>
+        <v>2.43</v>
       </c>
       <c r="F86" t="n">
-        <v>8.1</v>
+        <v>8.26</v>
       </c>
       <c r="G86" t="n">
-        <v>239.7</v>
+        <v>228.8</v>
       </c>
       <c r="H86" t="n">
-        <v>19.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I86" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J86" t="n">
-        <v>478.72</v>
+        <v>30.29</v>
       </c>
       <c r="K86" t="n">
-        <v>114.33</v>
+        <v>-539.35</v>
       </c>
       <c r="L86" t="n">
-        <v>492.18</v>
+        <v>540.2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:16:59</t>
+          <t>08:29:29</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="F87" t="n">
-        <v>7.45</v>
+        <v>7.75</v>
       </c>
       <c r="G87" t="n">
-        <v>244.4</v>
+        <v>239.4</v>
       </c>
       <c r="H87" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="I87" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J87" t="n">
-        <v>166.16</v>
+        <v>-197.79</v>
       </c>
       <c r="K87" t="n">
-        <v>579.11</v>
+        <v>-595.9299999999999</v>
       </c>
       <c r="L87" t="n">
-        <v>602.48</v>
+        <v>627.9</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:18:42</t>
+          <t>08:31:30</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>2.86</v>
+        <v>2.52</v>
       </c>
       <c r="F88" t="n">
-        <v>7.98</v>
+        <v>7.42</v>
       </c>
       <c r="G88" t="n">
-        <v>227.4</v>
+        <v>216</v>
       </c>
       <c r="H88" t="n">
-        <v>14.5</v>
+        <v>16.4</v>
       </c>
       <c r="I88" t="n">
         <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>-243.8</v>
+        <v>-20.49</v>
       </c>
       <c r="K88" t="n">
-        <v>-134.43</v>
+        <v>248.24</v>
       </c>
       <c r="L88" t="n">
-        <v>278.41</v>
+        <v>249.08</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-05-25.xlsx
+++ b/output/2024-05-25.xlsx
@@ -640,13 +640,13 @@
         <v>31</v>
       </c>
       <c r="J14" t="n">
-        <v>-41.38</v>
+        <v>-28.41</v>
       </c>
       <c r="K14" t="n">
-        <v>-38.12</v>
+        <v>-26.17</v>
       </c>
       <c r="L14" t="n">
-        <v>56.26</v>
+        <v>38.62</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>26</v>
       </c>
       <c r="J15" t="n">
-        <v>73.8</v>
+        <v>49.78</v>
       </c>
       <c r="K15" t="n">
-        <v>-146.89</v>
+        <v>-99.08</v>
       </c>
       <c r="L15" t="n">
-        <v>164.39</v>
+        <v>110.88</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>28</v>
       </c>
       <c r="J16" t="n">
-        <v>-31.68</v>
+        <v>-43.05</v>
       </c>
       <c r="K16" t="n">
-        <v>43.37</v>
+        <v>58.93</v>
       </c>
       <c r="L16" t="n">
-        <v>53.71</v>
+        <v>72.97</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>27</v>
       </c>
       <c r="J17" t="n">
-        <v>-120.85</v>
+        <v>-98.27</v>
       </c>
       <c r="K17" t="n">
-        <v>47.7</v>
+        <v>38.79</v>
       </c>
       <c r="L17" t="n">
-        <v>129.92</v>
+        <v>105.64</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>28</v>
       </c>
       <c r="J18" t="n">
-        <v>109.81</v>
+        <v>85.14</v>
       </c>
       <c r="K18" t="n">
-        <v>-39.62</v>
+        <v>-30.72</v>
       </c>
       <c r="L18" t="n">
-        <v>116.74</v>
+        <v>90.51000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>85.72</v>
+        <v>79.15000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>74.59</v>
+        <v>68.88</v>
       </c>
       <c r="L19" t="n">
-        <v>113.63</v>
+        <v>104.92</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>30</v>
       </c>
       <c r="J20" t="n">
-        <v>130.54</v>
+        <v>103.1</v>
       </c>
       <c r="K20" t="n">
-        <v>52.39</v>
+        <v>41.37</v>
       </c>
       <c r="L20" t="n">
-        <v>140.66</v>
+        <v>111.09</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>26</v>
       </c>
       <c r="J21" t="n">
-        <v>14.28</v>
+        <v>11.55</v>
       </c>
       <c r="K21" t="n">
-        <v>322.51</v>
+        <v>260.89</v>
       </c>
       <c r="L21" t="n">
-        <v>322.83</v>
+        <v>261.15</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>27</v>
       </c>
       <c r="J22" t="n">
-        <v>133.42</v>
+        <v>131.36</v>
       </c>
       <c r="K22" t="n">
-        <v>118.39</v>
+        <v>116.56</v>
       </c>
       <c r="L22" t="n">
-        <v>178.38</v>
+        <v>175.61</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>31</v>
       </c>
       <c r="J23" t="n">
-        <v>105.96</v>
+        <v>90.18000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>122.88</v>
+        <v>104.58</v>
       </c>
       <c r="L23" t="n">
-        <v>162.26</v>
+        <v>138.09</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>27</v>
       </c>
       <c r="J24" t="n">
-        <v>-243.08</v>
+        <v>-249.67</v>
       </c>
       <c r="K24" t="n">
-        <v>103.09</v>
+        <v>105.88</v>
       </c>
       <c r="L24" t="n">
-        <v>264.04</v>
+        <v>271.2</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>31</v>
       </c>
       <c r="J25" t="n">
-        <v>13.96</v>
+        <v>10.91</v>
       </c>
       <c r="K25" t="n">
-        <v>-236.85</v>
+        <v>-185.05</v>
       </c>
       <c r="L25" t="n">
-        <v>237.26</v>
+        <v>185.37</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>31</v>
       </c>
       <c r="J26" t="n">
-        <v>135.65</v>
+        <v>158.69</v>
       </c>
       <c r="K26" t="n">
-        <v>96.02</v>
+        <v>112.33</v>
       </c>
       <c r="L26" t="n">
-        <v>166.19</v>
+        <v>194.42</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>29</v>
       </c>
       <c r="J27" t="n">
-        <v>-356.32</v>
+        <v>-332.29</v>
       </c>
       <c r="K27" t="n">
-        <v>-12.83</v>
+        <v>-11.96</v>
       </c>
       <c r="L27" t="n">
-        <v>356.55</v>
+        <v>332.5</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>29</v>
       </c>
       <c r="J28" t="n">
-        <v>-72.56</v>
+        <v>-102.01</v>
       </c>
       <c r="K28" t="n">
-        <v>-128.58</v>
+        <v>-180.77</v>
       </c>
       <c r="L28" t="n">
-        <v>147.64</v>
+        <v>207.56</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>26</v>
       </c>
       <c r="J29" t="n">
-        <v>-19.6</v>
+        <v>-15.79</v>
       </c>
       <c r="K29" t="n">
-        <v>73.97</v>
+        <v>59.58</v>
       </c>
       <c r="L29" t="n">
-        <v>76.52</v>
+        <v>61.63</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>26</v>
       </c>
       <c r="J30" t="n">
-        <v>-131.22</v>
+        <v>-106.62</v>
       </c>
       <c r="K30" t="n">
-        <v>-101.85</v>
+        <v>-82.76000000000001</v>
       </c>
       <c r="L30" t="n">
-        <v>166.11</v>
+        <v>134.97</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>-29.79</v>
+        <v>-29.97</v>
       </c>
       <c r="K31" t="n">
-        <v>-55.63</v>
+        <v>-55.97</v>
       </c>
       <c r="L31" t="n">
-        <v>63.11</v>
+        <v>63.49</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>30</v>
       </c>
       <c r="J32" t="n">
-        <v>-52.98</v>
+        <v>-43.87</v>
       </c>
       <c r="K32" t="n">
-        <v>-87.48</v>
+        <v>-72.43000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>102.27</v>
+        <v>84.68000000000001</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>25</v>
       </c>
       <c r="J33" t="n">
-        <v>56.17</v>
+        <v>58.21</v>
       </c>
       <c r="K33" t="n">
-        <v>66.66</v>
+        <v>69.08</v>
       </c>
       <c r="L33" t="n">
-        <v>87.17</v>
+        <v>90.34</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>26</v>
       </c>
       <c r="J34" t="n">
-        <v>192.22</v>
+        <v>147.64</v>
       </c>
       <c r="K34" t="n">
-        <v>114.67</v>
+        <v>88.08</v>
       </c>
       <c r="L34" t="n">
-        <v>223.82</v>
+        <v>171.92</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>30</v>
       </c>
       <c r="J35" t="n">
-        <v>-67.14</v>
+        <v>-48.12</v>
       </c>
       <c r="K35" t="n">
-        <v>268.13</v>
+        <v>192.17</v>
       </c>
       <c r="L35" t="n">
-        <v>276.41</v>
+        <v>198.1</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>30</v>
       </c>
       <c r="J36" t="n">
-        <v>164.2</v>
+        <v>124.94</v>
       </c>
       <c r="K36" t="n">
-        <v>-134.06</v>
+        <v>-102.01</v>
       </c>
       <c r="L36" t="n">
-        <v>211.98</v>
+        <v>161.29</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>30</v>
       </c>
       <c r="J37" t="n">
-        <v>20.06</v>
+        <v>16.26</v>
       </c>
       <c r="K37" t="n">
-        <v>-155.11</v>
+        <v>-125.73</v>
       </c>
       <c r="L37" t="n">
-        <v>156.4</v>
+        <v>126.78</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>27</v>
       </c>
       <c r="J38" t="n">
-        <v>63.85</v>
+        <v>53.03</v>
       </c>
       <c r="K38" t="n">
-        <v>-329.4</v>
+        <v>-273.61</v>
       </c>
       <c r="L38" t="n">
-        <v>335.53</v>
+        <v>278.7</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>27</v>
       </c>
       <c r="J39" t="n">
-        <v>-305.89</v>
+        <v>-258.11</v>
       </c>
       <c r="K39" t="n">
-        <v>41.59</v>
+        <v>35.09</v>
       </c>
       <c r="L39" t="n">
-        <v>308.7</v>
+        <v>260.49</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>103.95</v>
+        <v>86.06999999999999</v>
       </c>
       <c r="K40" t="n">
-        <v>-376.02</v>
+        <v>-311.35</v>
       </c>
       <c r="L40" t="n">
-        <v>390.12</v>
+        <v>323.03</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>27</v>
       </c>
       <c r="J41" t="n">
-        <v>137.18</v>
+        <v>209.81</v>
       </c>
       <c r="K41" t="n">
-        <v>26.84</v>
+        <v>41.05</v>
       </c>
       <c r="L41" t="n">
-        <v>139.78</v>
+        <v>213.78</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>25</v>
       </c>
       <c r="J42" t="n">
-        <v>531.65</v>
+        <v>581.55</v>
       </c>
       <c r="K42" t="n">
-        <v>-457.03</v>
+        <v>-499.92</v>
       </c>
       <c r="L42" t="n">
-        <v>701.09</v>
+        <v>766.89</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>28</v>
       </c>
       <c r="J43" t="n">
-        <v>-128.84</v>
+        <v>-191.2</v>
       </c>
       <c r="K43" t="n">
-        <v>-61.68</v>
+        <v>-91.54000000000001</v>
       </c>
       <c r="L43" t="n">
-        <v>142.85</v>
+        <v>211.99</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>31</v>
       </c>
       <c r="J44" t="n">
-        <v>43.14</v>
+        <v>29.03</v>
       </c>
       <c r="K44" t="n">
-        <v>-59.29</v>
+        <v>-39.89</v>
       </c>
       <c r="L44" t="n">
-        <v>73.31999999999999</v>
+        <v>49.34</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>29</v>
       </c>
       <c r="J45" t="n">
-        <v>-68.14</v>
+        <v>-51.85</v>
       </c>
       <c r="K45" t="n">
-        <v>92.42</v>
+        <v>70.31</v>
       </c>
       <c r="L45" t="n">
-        <v>114.82</v>
+        <v>87.36</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>28</v>
       </c>
       <c r="J46" t="n">
-        <v>67.2</v>
+        <v>42.97</v>
       </c>
       <c r="K46" t="n">
-        <v>133.95</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="L46" t="n">
-        <v>149.86</v>
+        <v>95.83</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>-42.27</v>
+        <v>-60.12</v>
       </c>
       <c r="K47" t="n">
-        <v>-16.74</v>
+        <v>-23.82</v>
       </c>
       <c r="L47" t="n">
-        <v>45.46</v>
+        <v>64.67</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>27</v>
       </c>
       <c r="J48" t="n">
-        <v>-181.14</v>
+        <v>-149.24</v>
       </c>
       <c r="K48" t="n">
-        <v>69.75</v>
+        <v>57.47</v>
       </c>
       <c r="L48" t="n">
-        <v>194.1</v>
+        <v>159.92</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>30</v>
       </c>
       <c r="J49" t="n">
-        <v>-18.04</v>
+        <v>-24.7</v>
       </c>
       <c r="K49" t="n">
-        <v>-37.24</v>
+        <v>-50.99</v>
       </c>
       <c r="L49" t="n">
-        <v>41.37</v>
+        <v>56.65</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>27</v>
       </c>
       <c r="J50" t="n">
-        <v>180.34</v>
+        <v>178.31</v>
       </c>
       <c r="K50" t="n">
-        <v>-24.94</v>
+        <v>-24.65</v>
       </c>
       <c r="L50" t="n">
-        <v>182.06</v>
+        <v>180</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>30</v>
       </c>
       <c r="J51" t="n">
-        <v>92.66</v>
+        <v>71.67</v>
       </c>
       <c r="K51" t="n">
-        <v>192.84</v>
+        <v>149.15</v>
       </c>
       <c r="L51" t="n">
-        <v>213.95</v>
+        <v>165.48</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>26</v>
       </c>
       <c r="J52" t="n">
-        <v>91.06999999999999</v>
+        <v>89.29000000000001</v>
       </c>
       <c r="K52" t="n">
-        <v>-165.08</v>
+        <v>-161.86</v>
       </c>
       <c r="L52" t="n">
-        <v>188.53</v>
+        <v>184.85</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>26</v>
       </c>
       <c r="J53" t="n">
-        <v>226.53</v>
+        <v>207.07</v>
       </c>
       <c r="K53" t="n">
-        <v>-284.19</v>
+        <v>-259.77</v>
       </c>
       <c r="L53" t="n">
-        <v>363.43</v>
+        <v>332.2</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>30</v>
       </c>
       <c r="J54" t="n">
-        <v>-57.1</v>
+        <v>-61.16</v>
       </c>
       <c r="K54" t="n">
-        <v>105.8</v>
+        <v>113.33</v>
       </c>
       <c r="L54" t="n">
-        <v>120.23</v>
+        <v>128.78</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>31</v>
       </c>
       <c r="J55" t="n">
-        <v>206.54</v>
+        <v>170.3</v>
       </c>
       <c r="K55" t="n">
-        <v>-111.15</v>
+        <v>-91.65000000000001</v>
       </c>
       <c r="L55" t="n">
-        <v>234.55</v>
+        <v>193.4</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>30</v>
       </c>
       <c r="J56" t="n">
-        <v>-131.83</v>
+        <v>-144.84</v>
       </c>
       <c r="K56" t="n">
-        <v>264.01</v>
+        <v>290.07</v>
       </c>
       <c r="L56" t="n">
-        <v>295.09</v>
+        <v>324.23</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>31</v>
       </c>
       <c r="J57" t="n">
-        <v>250.49</v>
+        <v>266.34</v>
       </c>
       <c r="K57" t="n">
-        <v>55.84</v>
+        <v>59.38</v>
       </c>
       <c r="L57" t="n">
-        <v>256.63</v>
+        <v>272.88</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>26</v>
       </c>
       <c r="J58" t="n">
-        <v>154.06</v>
+        <v>223.9</v>
       </c>
       <c r="K58" t="n">
-        <v>131.85</v>
+        <v>191.61</v>
       </c>
       <c r="L58" t="n">
-        <v>202.78</v>
+        <v>294.7</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>-3.83</v>
+        <v>-2.73</v>
       </c>
       <c r="K59" t="n">
-        <v>-198.23</v>
+        <v>-141.42</v>
       </c>
       <c r="L59" t="n">
-        <v>198.27</v>
+        <v>141.45</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>31</v>
       </c>
       <c r="J60" t="n">
-        <v>2.97</v>
+        <v>1.78</v>
       </c>
       <c r="K60" t="n">
-        <v>84.05</v>
+        <v>50.44</v>
       </c>
       <c r="L60" t="n">
-        <v>84.09999999999999</v>
+        <v>50.47</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>28</v>
       </c>
       <c r="J61" t="n">
-        <v>26.38</v>
+        <v>28.01</v>
       </c>
       <c r="K61" t="n">
-        <v>43.94</v>
+        <v>46.67</v>
       </c>
       <c r="L61" t="n">
-        <v>51.25</v>
+        <v>54.43</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>31</v>
       </c>
       <c r="J62" t="n">
-        <v>-144</v>
+        <v>-91.12</v>
       </c>
       <c r="K62" t="n">
-        <v>-160.6</v>
+        <v>-101.62</v>
       </c>
       <c r="L62" t="n">
-        <v>215.7</v>
+        <v>136.49</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>31</v>
       </c>
       <c r="J63" t="n">
-        <v>11.19</v>
+        <v>6.22</v>
       </c>
       <c r="K63" t="n">
-        <v>-225.67</v>
+        <v>-125.39</v>
       </c>
       <c r="L63" t="n">
-        <v>225.94</v>
+        <v>125.54</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>31</v>
       </c>
       <c r="J64" t="n">
-        <v>-147.48</v>
+        <v>-92.45</v>
       </c>
       <c r="K64" t="n">
-        <v>139.51</v>
+        <v>87.45</v>
       </c>
       <c r="L64" t="n">
-        <v>203.01</v>
+        <v>127.26</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>30</v>
       </c>
       <c r="J65" t="n">
-        <v>124.46</v>
+        <v>120.77</v>
       </c>
       <c r="K65" t="n">
-        <v>140.7</v>
+        <v>136.53</v>
       </c>
       <c r="L65" t="n">
-        <v>187.84</v>
+        <v>182.28</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>29</v>
       </c>
       <c r="J66" t="n">
-        <v>51.89</v>
+        <v>60.42</v>
       </c>
       <c r="K66" t="n">
-        <v>83.20999999999999</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="L66" t="n">
-        <v>98.06</v>
+        <v>114.2</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>29</v>
       </c>
       <c r="J67" t="n">
-        <v>-197.4</v>
+        <v>-165.32</v>
       </c>
       <c r="K67" t="n">
-        <v>-28.84</v>
+        <v>-24.15</v>
       </c>
       <c r="L67" t="n">
-        <v>199.5</v>
+        <v>167.07</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>31</v>
       </c>
       <c r="J68" t="n">
-        <v>-210.07</v>
+        <v>-171.45</v>
       </c>
       <c r="K68" t="n">
-        <v>27.19</v>
+        <v>22.19</v>
       </c>
       <c r="L68" t="n">
-        <v>211.82</v>
+        <v>172.88</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>-267.15</v>
+        <v>-241.1</v>
       </c>
       <c r="K69" t="n">
-        <v>-366.5</v>
+        <v>-330.76</v>
       </c>
       <c r="L69" t="n">
-        <v>453.54</v>
+        <v>409.3</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>-156.89</v>
+        <v>-182.1</v>
       </c>
       <c r="K70" t="n">
-        <v>178.68</v>
+        <v>207.4</v>
       </c>
       <c r="L70" t="n">
-        <v>237.79</v>
+        <v>276</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>28</v>
       </c>
       <c r="J71" t="n">
-        <v>106.91</v>
+        <v>115.17</v>
       </c>
       <c r="K71" t="n">
-        <v>-403.18</v>
+        <v>-434.32</v>
       </c>
       <c r="L71" t="n">
-        <v>417.11</v>
+        <v>449.33</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>29</v>
       </c>
       <c r="J72" t="n">
-        <v>-347.87</v>
+        <v>-307.86</v>
       </c>
       <c r="K72" t="n">
-        <v>393.95</v>
+        <v>348.64</v>
       </c>
       <c r="L72" t="n">
-        <v>525.5599999999999</v>
+        <v>465.11</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>-224.03</v>
+        <v>-296.36</v>
       </c>
       <c r="K73" t="n">
-        <v>-206.43</v>
+        <v>-273.09</v>
       </c>
       <c r="L73" t="n">
-        <v>304.64</v>
+        <v>403</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>29</v>
       </c>
       <c r="J74" t="n">
-        <v>22.83</v>
+        <v>18.51</v>
       </c>
       <c r="K74" t="n">
-        <v>-128.43</v>
+        <v>-104.08</v>
       </c>
       <c r="L74" t="n">
-        <v>130.44</v>
+        <v>105.71</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>31</v>
       </c>
       <c r="J75" t="n">
-        <v>132.96</v>
+        <v>83.19</v>
       </c>
       <c r="K75" t="n">
-        <v>-12.88</v>
+        <v>-8.06</v>
       </c>
       <c r="L75" t="n">
-        <v>133.59</v>
+        <v>83.58</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>29</v>
       </c>
       <c r="J76" t="n">
-        <v>59.41</v>
+        <v>49.65</v>
       </c>
       <c r="K76" t="n">
-        <v>48.93</v>
+        <v>40.89</v>
       </c>
       <c r="L76" t="n">
-        <v>76.97</v>
+        <v>64.31999999999999</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>27</v>
       </c>
       <c r="J77" t="n">
-        <v>-165.27</v>
+        <v>-143.51</v>
       </c>
       <c r="K77" t="n">
-        <v>61.51</v>
+        <v>53.41</v>
       </c>
       <c r="L77" t="n">
-        <v>176.35</v>
+        <v>153.13</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>30</v>
       </c>
       <c r="J78" t="n">
-        <v>79.54000000000001</v>
+        <v>60.68</v>
       </c>
       <c r="K78" t="n">
-        <v>-166.02</v>
+        <v>-126.66</v>
       </c>
       <c r="L78" t="n">
-        <v>184.09</v>
+        <v>140.44</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>28</v>
       </c>
       <c r="J79" t="n">
-        <v>-108.94</v>
+        <v>-87.98999999999999</v>
       </c>
       <c r="K79" t="n">
-        <v>53.56</v>
+        <v>43.26</v>
       </c>
       <c r="L79" t="n">
-        <v>121.39</v>
+        <v>98.05</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>31</v>
       </c>
       <c r="J80" t="n">
-        <v>-89.40000000000001</v>
+        <v>-95.95</v>
       </c>
       <c r="K80" t="n">
-        <v>-57.02</v>
+        <v>-61.2</v>
       </c>
       <c r="L80" t="n">
-        <v>106.03</v>
+        <v>113.81</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>29</v>
       </c>
       <c r="J81" t="n">
-        <v>-234.16</v>
+        <v>-175.68</v>
       </c>
       <c r="K81" t="n">
-        <v>181.97</v>
+        <v>136.52</v>
       </c>
       <c r="L81" t="n">
-        <v>296.55</v>
+        <v>222.49</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>26</v>
       </c>
       <c r="J82" t="n">
-        <v>-160.86</v>
+        <v>-148.58</v>
       </c>
       <c r="K82" t="n">
-        <v>294.68</v>
+        <v>272.17</v>
       </c>
       <c r="L82" t="n">
-        <v>335.73</v>
+        <v>310.09</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>26</v>
       </c>
       <c r="J83" t="n">
-        <v>151.46</v>
+        <v>160.88</v>
       </c>
       <c r="K83" t="n">
-        <v>92.11</v>
+        <v>97.83</v>
       </c>
       <c r="L83" t="n">
-        <v>177.27</v>
+        <v>188.29</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>27</v>
       </c>
       <c r="J84" t="n">
-        <v>-65.84</v>
+        <v>-93.23</v>
       </c>
       <c r="K84" t="n">
-        <v>75.42</v>
+        <v>106.8</v>
       </c>
       <c r="L84" t="n">
-        <v>100.11</v>
+        <v>141.77</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>25</v>
       </c>
       <c r="J85" t="n">
-        <v>-267.35</v>
+        <v>-294.15</v>
       </c>
       <c r="K85" t="n">
-        <v>58.42</v>
+        <v>64.27</v>
       </c>
       <c r="L85" t="n">
-        <v>273.66</v>
+        <v>301.09</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>28</v>
       </c>
       <c r="J86" t="n">
-        <v>30.29</v>
+        <v>27.08</v>
       </c>
       <c r="K86" t="n">
-        <v>-539.35</v>
+        <v>-482.13</v>
       </c>
       <c r="L86" t="n">
-        <v>540.2</v>
+        <v>482.89</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>29</v>
       </c>
       <c r="J87" t="n">
-        <v>-197.79</v>
+        <v>-168.91</v>
       </c>
       <c r="K87" t="n">
-        <v>-595.9299999999999</v>
+        <v>-508.94</v>
       </c>
       <c r="L87" t="n">
-        <v>627.9</v>
+        <v>536.24</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>-20.49</v>
+        <v>-26.5</v>
       </c>
       <c r="K88" t="n">
-        <v>248.24</v>
+        <v>320.98</v>
       </c>
       <c r="L88" t="n">
-        <v>249.08</v>
+        <v>322.08</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-05-25.xlsx
+++ b/output/2024-05-25.xlsx
@@ -640,13 +640,13 @@
         <v>31</v>
       </c>
       <c r="J14" t="n">
-        <v>-28.41</v>
+        <v>-36.77</v>
       </c>
       <c r="K14" t="n">
-        <v>-26.17</v>
+        <v>-33.87</v>
       </c>
       <c r="L14" t="n">
-        <v>38.62</v>
+        <v>49.99</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>26</v>
       </c>
       <c r="J15" t="n">
-        <v>49.78</v>
+        <v>48.33</v>
       </c>
       <c r="K15" t="n">
-        <v>-99.08</v>
+        <v>-96.18000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>110.88</v>
+        <v>107.64</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>28</v>
       </c>
       <c r="J16" t="n">
-        <v>-43.05</v>
+        <v>-40.53</v>
       </c>
       <c r="K16" t="n">
-        <v>58.93</v>
+        <v>55.49</v>
       </c>
       <c r="L16" t="n">
-        <v>72.97</v>
+        <v>68.70999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>27</v>
       </c>
       <c r="J17" t="n">
-        <v>-98.27</v>
+        <v>-91.51000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>38.79</v>
+        <v>36.12</v>
       </c>
       <c r="L17" t="n">
-        <v>105.64</v>
+        <v>98.38</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>28</v>
       </c>
       <c r="J18" t="n">
-        <v>85.14</v>
+        <v>84.38</v>
       </c>
       <c r="K18" t="n">
-        <v>-30.72</v>
+        <v>-30.44</v>
       </c>
       <c r="L18" t="n">
-        <v>90.51000000000001</v>
+        <v>89.7</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>79.15000000000001</v>
+        <v>69.7</v>
       </c>
       <c r="K19" t="n">
-        <v>68.88</v>
+        <v>60.65</v>
       </c>
       <c r="L19" t="n">
-        <v>104.92</v>
+        <v>92.39</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>30</v>
       </c>
       <c r="J20" t="n">
-        <v>103.1</v>
+        <v>99.83</v>
       </c>
       <c r="K20" t="n">
-        <v>41.37</v>
+        <v>40.06</v>
       </c>
       <c r="L20" t="n">
-        <v>111.09</v>
+        <v>107.57</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>26</v>
       </c>
       <c r="J21" t="n">
-        <v>11.55</v>
+        <v>8.92</v>
       </c>
       <c r="K21" t="n">
-        <v>260.89</v>
+        <v>201.39</v>
       </c>
       <c r="L21" t="n">
-        <v>261.15</v>
+        <v>201.59</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>27</v>
       </c>
       <c r="J22" t="n">
-        <v>131.36</v>
+        <v>102.81</v>
       </c>
       <c r="K22" t="n">
-        <v>116.56</v>
+        <v>91.23</v>
       </c>
       <c r="L22" t="n">
-        <v>175.61</v>
+        <v>137.45</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>31</v>
       </c>
       <c r="J23" t="n">
-        <v>90.18000000000001</v>
+        <v>80.08</v>
       </c>
       <c r="K23" t="n">
-        <v>104.58</v>
+        <v>92.87</v>
       </c>
       <c r="L23" t="n">
-        <v>138.09</v>
+        <v>122.62</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>27</v>
       </c>
       <c r="J24" t="n">
-        <v>-249.67</v>
+        <v>-171.45</v>
       </c>
       <c r="K24" t="n">
-        <v>105.88</v>
+        <v>72.70999999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>271.2</v>
+        <v>186.23</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>31</v>
       </c>
       <c r="J25" t="n">
-        <v>10.91</v>
+        <v>9.6</v>
       </c>
       <c r="K25" t="n">
-        <v>-185.05</v>
+        <v>-162.88</v>
       </c>
       <c r="L25" t="n">
-        <v>185.37</v>
+        <v>163.16</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>31</v>
       </c>
       <c r="J26" t="n">
-        <v>158.69</v>
+        <v>124.13</v>
       </c>
       <c r="K26" t="n">
-        <v>112.33</v>
+        <v>87.87</v>
       </c>
       <c r="L26" t="n">
-        <v>194.42</v>
+        <v>152.08</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>29</v>
       </c>
       <c r="J27" t="n">
-        <v>-332.29</v>
+        <v>-234.06</v>
       </c>
       <c r="K27" t="n">
-        <v>-11.96</v>
+        <v>-8.43</v>
       </c>
       <c r="L27" t="n">
-        <v>332.5</v>
+        <v>234.21</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>29</v>
       </c>
       <c r="J28" t="n">
-        <v>-102.01</v>
+        <v>-71.34999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>-180.77</v>
+        <v>-126.43</v>
       </c>
       <c r="L28" t="n">
-        <v>207.56</v>
+        <v>145.18</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>26</v>
       </c>
       <c r="J29" t="n">
-        <v>-15.79</v>
+        <v>-15.75</v>
       </c>
       <c r="K29" t="n">
-        <v>59.58</v>
+        <v>59.41</v>
       </c>
       <c r="L29" t="n">
-        <v>61.63</v>
+        <v>61.47</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>26</v>
       </c>
       <c r="J30" t="n">
-        <v>-106.62</v>
+        <v>-95.19</v>
       </c>
       <c r="K30" t="n">
-        <v>-82.76000000000001</v>
+        <v>-73.89</v>
       </c>
       <c r="L30" t="n">
-        <v>134.97</v>
+        <v>120.5</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>-29.97</v>
+        <v>-27.6</v>
       </c>
       <c r="K31" t="n">
-        <v>-55.97</v>
+        <v>-51.55</v>
       </c>
       <c r="L31" t="n">
-        <v>63.49</v>
+        <v>58.47</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>30</v>
       </c>
       <c r="J32" t="n">
-        <v>-43.87</v>
+        <v>-45.71</v>
       </c>
       <c r="K32" t="n">
-        <v>-72.43000000000001</v>
+        <v>-75.47</v>
       </c>
       <c r="L32" t="n">
-        <v>84.68000000000001</v>
+        <v>88.23</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>25</v>
       </c>
       <c r="J33" t="n">
-        <v>58.21</v>
+        <v>49.54</v>
       </c>
       <c r="K33" t="n">
-        <v>69.08</v>
+        <v>58.79</v>
       </c>
       <c r="L33" t="n">
-        <v>90.34</v>
+        <v>76.88</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>26</v>
       </c>
       <c r="J34" t="n">
-        <v>147.64</v>
+        <v>128.05</v>
       </c>
       <c r="K34" t="n">
-        <v>88.08</v>
+        <v>76.39</v>
       </c>
       <c r="L34" t="n">
-        <v>171.92</v>
+        <v>149.11</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>30</v>
       </c>
       <c r="J35" t="n">
-        <v>-48.12</v>
+        <v>-44.18</v>
       </c>
       <c r="K35" t="n">
-        <v>192.17</v>
+        <v>176.45</v>
       </c>
       <c r="L35" t="n">
-        <v>198.1</v>
+        <v>181.89</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>30</v>
       </c>
       <c r="J36" t="n">
-        <v>124.94</v>
+        <v>115.28</v>
       </c>
       <c r="K36" t="n">
-        <v>-102.01</v>
+        <v>-94.12</v>
       </c>
       <c r="L36" t="n">
-        <v>161.29</v>
+        <v>148.82</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>30</v>
       </c>
       <c r="J37" t="n">
-        <v>16.26</v>
+        <v>15.22</v>
       </c>
       <c r="K37" t="n">
-        <v>-125.73</v>
+        <v>-117.7</v>
       </c>
       <c r="L37" t="n">
-        <v>126.78</v>
+        <v>118.68</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>27</v>
       </c>
       <c r="J38" t="n">
-        <v>53.03</v>
+        <v>38.35</v>
       </c>
       <c r="K38" t="n">
-        <v>-273.61</v>
+        <v>-197.83</v>
       </c>
       <c r="L38" t="n">
-        <v>278.7</v>
+        <v>201.51</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>27</v>
       </c>
       <c r="J39" t="n">
-        <v>-258.11</v>
+        <v>-187.14</v>
       </c>
       <c r="K39" t="n">
-        <v>35.09</v>
+        <v>25.44</v>
       </c>
       <c r="L39" t="n">
-        <v>260.49</v>
+        <v>188.87</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>86.06999999999999</v>
+        <v>59.78</v>
       </c>
       <c r="K40" t="n">
-        <v>-311.35</v>
+        <v>-216.25</v>
       </c>
       <c r="L40" t="n">
-        <v>323.03</v>
+        <v>224.36</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>27</v>
       </c>
       <c r="J41" t="n">
-        <v>209.81</v>
+        <v>134.15</v>
       </c>
       <c r="K41" t="n">
-        <v>41.05</v>
+        <v>26.25</v>
       </c>
       <c r="L41" t="n">
-        <v>213.78</v>
+        <v>136.69</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>25</v>
       </c>
       <c r="J42" t="n">
-        <v>581.55</v>
+        <v>319.35</v>
       </c>
       <c r="K42" t="n">
-        <v>-499.92</v>
+        <v>-274.52</v>
       </c>
       <c r="L42" t="n">
-        <v>766.89</v>
+        <v>421.12</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>28</v>
       </c>
       <c r="J43" t="n">
-        <v>-191.2</v>
+        <v>-126.66</v>
       </c>
       <c r="K43" t="n">
-        <v>-91.54000000000001</v>
+        <v>-60.64</v>
       </c>
       <c r="L43" t="n">
-        <v>211.99</v>
+        <v>140.43</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>31</v>
       </c>
       <c r="J44" t="n">
-        <v>29.03</v>
+        <v>33</v>
       </c>
       <c r="K44" t="n">
-        <v>-39.89</v>
+        <v>-45.35</v>
       </c>
       <c r="L44" t="n">
-        <v>49.34</v>
+        <v>56.08</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>29</v>
       </c>
       <c r="J45" t="n">
-        <v>-51.85</v>
+        <v>-54.34</v>
       </c>
       <c r="K45" t="n">
-        <v>70.31</v>
+        <v>73.7</v>
       </c>
       <c r="L45" t="n">
-        <v>87.36</v>
+        <v>91.56999999999999</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>28</v>
       </c>
       <c r="J46" t="n">
-        <v>42.97</v>
+        <v>45.48</v>
       </c>
       <c r="K46" t="n">
-        <v>85.65000000000001</v>
+        <v>90.65000000000001</v>
       </c>
       <c r="L46" t="n">
-        <v>95.83</v>
+        <v>101.42</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>-60.12</v>
+        <v>-53.51</v>
       </c>
       <c r="K47" t="n">
-        <v>-23.82</v>
+        <v>-21.2</v>
       </c>
       <c r="L47" t="n">
-        <v>64.67</v>
+        <v>57.56</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>27</v>
       </c>
       <c r="J48" t="n">
-        <v>-149.24</v>
+        <v>-131.49</v>
       </c>
       <c r="K48" t="n">
-        <v>57.47</v>
+        <v>50.63</v>
       </c>
       <c r="L48" t="n">
-        <v>159.92</v>
+        <v>140.9</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>30</v>
       </c>
       <c r="J49" t="n">
-        <v>-24.7</v>
+        <v>-25.61</v>
       </c>
       <c r="K49" t="n">
-        <v>-50.99</v>
+        <v>-52.87</v>
       </c>
       <c r="L49" t="n">
-        <v>56.65</v>
+        <v>58.74</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>27</v>
       </c>
       <c r="J50" t="n">
-        <v>178.31</v>
+        <v>138.95</v>
       </c>
       <c r="K50" t="n">
-        <v>-24.65</v>
+        <v>-19.21</v>
       </c>
       <c r="L50" t="n">
-        <v>180</v>
+        <v>140.28</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>30</v>
       </c>
       <c r="J51" t="n">
-        <v>71.67</v>
+        <v>65.89</v>
       </c>
       <c r="K51" t="n">
-        <v>149.15</v>
+        <v>137.12</v>
       </c>
       <c r="L51" t="n">
-        <v>165.48</v>
+        <v>152.12</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>26</v>
       </c>
       <c r="J52" t="n">
-        <v>89.29000000000001</v>
+        <v>67.64</v>
       </c>
       <c r="K52" t="n">
-        <v>-161.86</v>
+        <v>-122.62</v>
       </c>
       <c r="L52" t="n">
-        <v>184.85</v>
+        <v>140.04</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>26</v>
       </c>
       <c r="J53" t="n">
-        <v>207.07</v>
+        <v>139.25</v>
       </c>
       <c r="K53" t="n">
-        <v>-259.77</v>
+        <v>-174.69</v>
       </c>
       <c r="L53" t="n">
-        <v>332.2</v>
+        <v>223.39</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>30</v>
       </c>
       <c r="J54" t="n">
-        <v>-61.16</v>
+        <v>-51.23</v>
       </c>
       <c r="K54" t="n">
-        <v>113.33</v>
+        <v>94.94</v>
       </c>
       <c r="L54" t="n">
-        <v>128.78</v>
+        <v>107.88</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>31</v>
       </c>
       <c r="J55" t="n">
-        <v>170.3</v>
+        <v>146.97</v>
       </c>
       <c r="K55" t="n">
-        <v>-91.65000000000001</v>
+        <v>-79.09999999999999</v>
       </c>
       <c r="L55" t="n">
-        <v>193.4</v>
+        <v>166.9</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>30</v>
       </c>
       <c r="J56" t="n">
-        <v>-144.84</v>
+        <v>-102.25</v>
       </c>
       <c r="K56" t="n">
-        <v>290.07</v>
+        <v>204.77</v>
       </c>
       <c r="L56" t="n">
-        <v>324.23</v>
+        <v>228.88</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>31</v>
       </c>
       <c r="J57" t="n">
-        <v>266.34</v>
+        <v>201.31</v>
       </c>
       <c r="K57" t="n">
-        <v>59.38</v>
+        <v>44.88</v>
       </c>
       <c r="L57" t="n">
-        <v>272.88</v>
+        <v>206.26</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>26</v>
       </c>
       <c r="J58" t="n">
-        <v>223.9</v>
+        <v>134.45</v>
       </c>
       <c r="K58" t="n">
-        <v>191.61</v>
+        <v>115.06</v>
       </c>
       <c r="L58" t="n">
-        <v>294.7</v>
+        <v>176.97</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>-2.73</v>
+        <v>-2.53</v>
       </c>
       <c r="K59" t="n">
-        <v>-141.42</v>
+        <v>-131.07</v>
       </c>
       <c r="L59" t="n">
-        <v>141.45</v>
+        <v>131.09</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>31</v>
       </c>
       <c r="J60" t="n">
-        <v>1.78</v>
+        <v>2.31</v>
       </c>
       <c r="K60" t="n">
-        <v>50.44</v>
+        <v>65.42</v>
       </c>
       <c r="L60" t="n">
-        <v>50.47</v>
+        <v>65.45999999999999</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>28</v>
       </c>
       <c r="J61" t="n">
-        <v>28.01</v>
+        <v>28.72</v>
       </c>
       <c r="K61" t="n">
-        <v>46.67</v>
+        <v>47.84</v>
       </c>
       <c r="L61" t="n">
-        <v>54.43</v>
+        <v>55.8</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>31</v>
       </c>
       <c r="J62" t="n">
-        <v>-91.12</v>
+        <v>-100.46</v>
       </c>
       <c r="K62" t="n">
-        <v>-101.62</v>
+        <v>-112.04</v>
       </c>
       <c r="L62" t="n">
-        <v>136.49</v>
+        <v>150.49</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>31</v>
       </c>
       <c r="J63" t="n">
-        <v>6.22</v>
+        <v>7.23</v>
       </c>
       <c r="K63" t="n">
-        <v>-125.39</v>
+        <v>-145.83</v>
       </c>
       <c r="L63" t="n">
-        <v>125.54</v>
+        <v>146.01</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>31</v>
       </c>
       <c r="J64" t="n">
-        <v>-92.45</v>
+        <v>-102.97</v>
       </c>
       <c r="K64" t="n">
-        <v>87.45</v>
+        <v>97.41</v>
       </c>
       <c r="L64" t="n">
-        <v>127.26</v>
+        <v>141.74</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>30</v>
       </c>
       <c r="J65" t="n">
-        <v>120.77</v>
+        <v>103.98</v>
       </c>
       <c r="K65" t="n">
-        <v>136.53</v>
+        <v>117.55</v>
       </c>
       <c r="L65" t="n">
-        <v>182.28</v>
+        <v>156.94</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>29</v>
       </c>
       <c r="J66" t="n">
-        <v>60.42</v>
+        <v>52.08</v>
       </c>
       <c r="K66" t="n">
-        <v>96.90000000000001</v>
+        <v>83.53</v>
       </c>
       <c r="L66" t="n">
-        <v>114.2</v>
+        <v>98.44</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>29</v>
       </c>
       <c r="J67" t="n">
-        <v>-165.32</v>
+        <v>-143.83</v>
       </c>
       <c r="K67" t="n">
-        <v>-24.15</v>
+        <v>-21.01</v>
       </c>
       <c r="L67" t="n">
-        <v>167.07</v>
+        <v>145.36</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>31</v>
       </c>
       <c r="J68" t="n">
-        <v>-171.45</v>
+        <v>-150.71</v>
       </c>
       <c r="K68" t="n">
-        <v>22.19</v>
+        <v>19.51</v>
       </c>
       <c r="L68" t="n">
-        <v>172.88</v>
+        <v>151.97</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>-241.1</v>
+        <v>-163.47</v>
       </c>
       <c r="K69" t="n">
-        <v>-330.76</v>
+        <v>-224.26</v>
       </c>
       <c r="L69" t="n">
-        <v>409.3</v>
+        <v>277.52</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>-182.1</v>
+        <v>-115.29</v>
       </c>
       <c r="K70" t="n">
-        <v>207.4</v>
+        <v>131.3</v>
       </c>
       <c r="L70" t="n">
-        <v>276</v>
+        <v>174.74</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>28</v>
       </c>
       <c r="J71" t="n">
-        <v>115.17</v>
+        <v>73.22</v>
       </c>
       <c r="K71" t="n">
-        <v>-434.32</v>
+        <v>-276.12</v>
       </c>
       <c r="L71" t="n">
-        <v>449.33</v>
+        <v>285.66</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>29</v>
       </c>
       <c r="J72" t="n">
-        <v>-307.86</v>
+        <v>-211.55</v>
       </c>
       <c r="K72" t="n">
-        <v>348.64</v>
+        <v>239.58</v>
       </c>
       <c r="L72" t="n">
-        <v>465.11</v>
+        <v>319.61</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>-296.36</v>
+        <v>-168.34</v>
       </c>
       <c r="K73" t="n">
-        <v>-273.09</v>
+        <v>-155.12</v>
       </c>
       <c r="L73" t="n">
-        <v>403</v>
+        <v>228.92</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>29</v>
       </c>
       <c r="J74" t="n">
-        <v>18.51</v>
+        <v>18.6</v>
       </c>
       <c r="K74" t="n">
-        <v>-104.08</v>
+        <v>-104.62</v>
       </c>
       <c r="L74" t="n">
-        <v>105.71</v>
+        <v>106.26</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>31</v>
       </c>
       <c r="J75" t="n">
-        <v>83.19</v>
+        <v>98.95999999999999</v>
       </c>
       <c r="K75" t="n">
-        <v>-8.06</v>
+        <v>-9.59</v>
       </c>
       <c r="L75" t="n">
-        <v>83.58</v>
+        <v>99.42</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>29</v>
       </c>
       <c r="J76" t="n">
-        <v>49.65</v>
+        <v>53.07</v>
       </c>
       <c r="K76" t="n">
-        <v>40.89</v>
+        <v>43.71</v>
       </c>
       <c r="L76" t="n">
-        <v>64.31999999999999</v>
+        <v>68.76000000000001</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>27</v>
       </c>
       <c r="J77" t="n">
-        <v>-143.51</v>
+        <v>-125.14</v>
       </c>
       <c r="K77" t="n">
-        <v>53.41</v>
+        <v>46.57</v>
       </c>
       <c r="L77" t="n">
-        <v>153.13</v>
+        <v>133.52</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>30</v>
       </c>
       <c r="J78" t="n">
-        <v>60.68</v>
+        <v>60.82</v>
       </c>
       <c r="K78" t="n">
-        <v>-126.66</v>
+        <v>-126.94</v>
       </c>
       <c r="L78" t="n">
-        <v>140.44</v>
+        <v>140.76</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>28</v>
       </c>
       <c r="J79" t="n">
-        <v>-87.98999999999999</v>
+        <v>-85.06999999999999</v>
       </c>
       <c r="K79" t="n">
-        <v>43.26</v>
+        <v>41.82</v>
       </c>
       <c r="L79" t="n">
-        <v>98.05</v>
+        <v>94.79000000000001</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>31</v>
       </c>
       <c r="J80" t="n">
-        <v>-95.95</v>
+        <v>-89.78</v>
       </c>
       <c r="K80" t="n">
-        <v>-61.2</v>
+        <v>-57.26</v>
       </c>
       <c r="L80" t="n">
-        <v>113.81</v>
+        <v>106.49</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>29</v>
       </c>
       <c r="J81" t="n">
-        <v>-175.68</v>
+        <v>-152.13</v>
       </c>
       <c r="K81" t="n">
-        <v>136.52</v>
+        <v>118.22</v>
       </c>
       <c r="L81" t="n">
-        <v>222.49</v>
+        <v>192.66</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>26</v>
       </c>
       <c r="J82" t="n">
-        <v>-148.58</v>
+        <v>-107.18</v>
       </c>
       <c r="K82" t="n">
-        <v>272.17</v>
+        <v>196.34</v>
       </c>
       <c r="L82" t="n">
-        <v>310.09</v>
+        <v>223.69</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>26</v>
       </c>
       <c r="J83" t="n">
-        <v>160.88</v>
+        <v>112.21</v>
       </c>
       <c r="K83" t="n">
-        <v>97.83</v>
+        <v>68.23999999999999</v>
       </c>
       <c r="L83" t="n">
-        <v>188.29</v>
+        <v>131.33</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>27</v>
       </c>
       <c r="J84" t="n">
-        <v>-93.23</v>
+        <v>-66.53</v>
       </c>
       <c r="K84" t="n">
-        <v>106.8</v>
+        <v>76.20999999999999</v>
       </c>
       <c r="L84" t="n">
-        <v>141.77</v>
+        <v>101.16</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>25</v>
       </c>
       <c r="J85" t="n">
-        <v>-294.15</v>
+        <v>-185.71</v>
       </c>
       <c r="K85" t="n">
-        <v>64.27</v>
+        <v>40.58</v>
       </c>
       <c r="L85" t="n">
-        <v>301.09</v>
+        <v>190.09</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>28</v>
       </c>
       <c r="J86" t="n">
-        <v>27.08</v>
+        <v>17.89</v>
       </c>
       <c r="K86" t="n">
-        <v>-482.13</v>
+        <v>-318.6</v>
       </c>
       <c r="L86" t="n">
-        <v>482.89</v>
+        <v>319.11</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>29</v>
       </c>
       <c r="J87" t="n">
-        <v>-168.91</v>
+        <v>-115.56</v>
       </c>
       <c r="K87" t="n">
-        <v>-508.94</v>
+        <v>-348.19</v>
       </c>
       <c r="L87" t="n">
-        <v>536.24</v>
+        <v>366.86</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>-26.5</v>
+        <v>-15.95</v>
       </c>
       <c r="K88" t="n">
-        <v>320.98</v>
+        <v>193.19</v>
       </c>
       <c r="L88" t="n">
-        <v>322.08</v>
+        <v>193.85</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-05-25.xlsx
+++ b/output/2024-05-25.xlsx
@@ -640,13 +640,13 @@
         <v>31</v>
       </c>
       <c r="J14" t="n">
-        <v>-36.77</v>
+        <v>-33.21</v>
       </c>
       <c r="K14" t="n">
-        <v>-33.87</v>
+        <v>-30.59</v>
       </c>
       <c r="L14" t="n">
-        <v>49.99</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>26</v>
       </c>
       <c r="J15" t="n">
-        <v>48.33</v>
+        <v>44.6</v>
       </c>
       <c r="K15" t="n">
-        <v>-96.18000000000001</v>
+        <v>-88.77</v>
       </c>
       <c r="L15" t="n">
-        <v>107.64</v>
+        <v>99.34999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>28</v>
       </c>
       <c r="J16" t="n">
-        <v>-40.53</v>
+        <v>-36.67</v>
       </c>
       <c r="K16" t="n">
-        <v>55.49</v>
+        <v>50.2</v>
       </c>
       <c r="L16" t="n">
-        <v>68.70999999999999</v>
+        <v>62.17</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>27</v>
       </c>
       <c r="J17" t="n">
-        <v>-91.51000000000001</v>
+        <v>-87.61</v>
       </c>
       <c r="K17" t="n">
-        <v>36.12</v>
+        <v>34.58</v>
       </c>
       <c r="L17" t="n">
-        <v>98.38</v>
+        <v>94.19</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>28</v>
       </c>
       <c r="J18" t="n">
-        <v>84.38</v>
+        <v>79.72</v>
       </c>
       <c r="K18" t="n">
-        <v>-30.44</v>
+        <v>-28.76</v>
       </c>
       <c r="L18" t="n">
-        <v>89.7</v>
+        <v>84.75</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>69.7</v>
+        <v>66.77</v>
       </c>
       <c r="K19" t="n">
-        <v>60.65</v>
+        <v>58.1</v>
       </c>
       <c r="L19" t="n">
-        <v>92.39</v>
+        <v>88.51000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>30</v>
       </c>
       <c r="J20" t="n">
-        <v>99.83</v>
+        <v>97.55</v>
       </c>
       <c r="K20" t="n">
-        <v>40.06</v>
+        <v>39.15</v>
       </c>
       <c r="L20" t="n">
-        <v>107.57</v>
+        <v>105.12</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>26</v>
       </c>
       <c r="J21" t="n">
-        <v>8.92</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>201.39</v>
+        <v>202.05</v>
       </c>
       <c r="L21" t="n">
-        <v>201.59</v>
+        <v>202.25</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>27</v>
       </c>
       <c r="J22" t="n">
-        <v>102.81</v>
+        <v>102</v>
       </c>
       <c r="K22" t="n">
-        <v>91.23</v>
+        <v>90.51000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>137.45</v>
+        <v>136.37</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>31</v>
       </c>
       <c r="J23" t="n">
-        <v>80.08</v>
+        <v>79.55</v>
       </c>
       <c r="K23" t="n">
-        <v>92.87</v>
+        <v>92.26000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>122.62</v>
+        <v>121.82</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>27</v>
       </c>
       <c r="J24" t="n">
-        <v>-171.45</v>
+        <v>-172.69</v>
       </c>
       <c r="K24" t="n">
-        <v>72.70999999999999</v>
+        <v>73.23</v>
       </c>
       <c r="L24" t="n">
-        <v>186.23</v>
+        <v>187.57</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>31</v>
       </c>
       <c r="J25" t="n">
-        <v>9.6</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>-162.88</v>
+        <v>-161.66</v>
       </c>
       <c r="L25" t="n">
-        <v>163.16</v>
+        <v>161.94</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>31</v>
       </c>
       <c r="J26" t="n">
-        <v>124.13</v>
+        <v>125.39</v>
       </c>
       <c r="K26" t="n">
-        <v>87.87</v>
+        <v>88.76000000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>152.08</v>
+        <v>153.63</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>29</v>
       </c>
       <c r="J27" t="n">
-        <v>-234.06</v>
+        <v>-239.02</v>
       </c>
       <c r="K27" t="n">
-        <v>-8.43</v>
+        <v>-8.6</v>
       </c>
       <c r="L27" t="n">
-        <v>234.21</v>
+        <v>239.18</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>29</v>
       </c>
       <c r="J28" t="n">
-        <v>-71.34999999999999</v>
+        <v>-72.8</v>
       </c>
       <c r="K28" t="n">
-        <v>-126.43</v>
+        <v>-129</v>
       </c>
       <c r="L28" t="n">
-        <v>145.18</v>
+        <v>148.12</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>26</v>
       </c>
       <c r="J29" t="n">
-        <v>-15.75</v>
+        <v>-14.75</v>
       </c>
       <c r="K29" t="n">
-        <v>59.41</v>
+        <v>55.65</v>
       </c>
       <c r="L29" t="n">
-        <v>61.47</v>
+        <v>57.57</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>26</v>
       </c>
       <c r="J30" t="n">
-        <v>-95.19</v>
+        <v>-88.52</v>
       </c>
       <c r="K30" t="n">
-        <v>-73.89</v>
+        <v>-68.70999999999999</v>
       </c>
       <c r="L30" t="n">
-        <v>120.5</v>
+        <v>112.05</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>-27.6</v>
+        <v>-25.68</v>
       </c>
       <c r="K31" t="n">
-        <v>-51.55</v>
+        <v>-47.95</v>
       </c>
       <c r="L31" t="n">
-        <v>58.47</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>30</v>
       </c>
       <c r="J32" t="n">
-        <v>-45.71</v>
+        <v>-42.39</v>
       </c>
       <c r="K32" t="n">
-        <v>-75.47</v>
+        <v>-69.98999999999999</v>
       </c>
       <c r="L32" t="n">
-        <v>88.23</v>
+        <v>81.83</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>25</v>
       </c>
       <c r="J33" t="n">
-        <v>49.54</v>
+        <v>47.56</v>
       </c>
       <c r="K33" t="n">
-        <v>58.79</v>
+        <v>56.44</v>
       </c>
       <c r="L33" t="n">
-        <v>76.88</v>
+        <v>73.8</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>26</v>
       </c>
       <c r="J34" t="n">
-        <v>128.05</v>
+        <v>123.03</v>
       </c>
       <c r="K34" t="n">
-        <v>76.39</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="L34" t="n">
-        <v>149.11</v>
+        <v>143.27</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>30</v>
       </c>
       <c r="J35" t="n">
-        <v>-44.18</v>
+        <v>-42.94</v>
       </c>
       <c r="K35" t="n">
-        <v>176.45</v>
+        <v>171.51</v>
       </c>
       <c r="L35" t="n">
-        <v>181.89</v>
+        <v>176.81</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>30</v>
       </c>
       <c r="J36" t="n">
-        <v>115.28</v>
+        <v>112.35</v>
       </c>
       <c r="K36" t="n">
-        <v>-94.12</v>
+        <v>-91.73</v>
       </c>
       <c r="L36" t="n">
-        <v>148.82</v>
+        <v>145.04</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>30</v>
       </c>
       <c r="J37" t="n">
-        <v>15.22</v>
+        <v>14.78</v>
       </c>
       <c r="K37" t="n">
-        <v>-117.7</v>
+        <v>-114.24</v>
       </c>
       <c r="L37" t="n">
-        <v>118.68</v>
+        <v>115.19</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>27</v>
       </c>
       <c r="J38" t="n">
-        <v>38.35</v>
+        <v>39.15</v>
       </c>
       <c r="K38" t="n">
-        <v>-197.83</v>
+        <v>-201.99</v>
       </c>
       <c r="L38" t="n">
-        <v>201.51</v>
+        <v>205.75</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>27</v>
       </c>
       <c r="J39" t="n">
-        <v>-187.14</v>
+        <v>-189.09</v>
       </c>
       <c r="K39" t="n">
-        <v>25.44</v>
+        <v>25.71</v>
       </c>
       <c r="L39" t="n">
-        <v>188.87</v>
+        <v>190.83</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>59.78</v>
+        <v>61.33</v>
       </c>
       <c r="K40" t="n">
-        <v>-216.25</v>
+        <v>-221.85</v>
       </c>
       <c r="L40" t="n">
-        <v>224.36</v>
+        <v>230.17</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>27</v>
       </c>
       <c r="J41" t="n">
-        <v>134.15</v>
+        <v>138.2</v>
       </c>
       <c r="K41" t="n">
-        <v>26.25</v>
+        <v>27.04</v>
       </c>
       <c r="L41" t="n">
-        <v>136.69</v>
+        <v>140.82</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>25</v>
       </c>
       <c r="J42" t="n">
-        <v>319.35</v>
+        <v>330.24</v>
       </c>
       <c r="K42" t="n">
-        <v>-274.52</v>
+        <v>-283.89</v>
       </c>
       <c r="L42" t="n">
-        <v>421.12</v>
+        <v>435.49</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>28</v>
       </c>
       <c r="J43" t="n">
-        <v>-126.66</v>
+        <v>-129.37</v>
       </c>
       <c r="K43" t="n">
-        <v>-60.64</v>
+        <v>-61.94</v>
       </c>
       <c r="L43" t="n">
-        <v>140.43</v>
+        <v>143.43</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>31</v>
       </c>
       <c r="J44" t="n">
-        <v>33</v>
+        <v>29.35</v>
       </c>
       <c r="K44" t="n">
-        <v>-45.35</v>
+        <v>-40.34</v>
       </c>
       <c r="L44" t="n">
-        <v>56.08</v>
+        <v>49.88</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>29</v>
       </c>
       <c r="J45" t="n">
-        <v>-54.34</v>
+        <v>-49.39</v>
       </c>
       <c r="K45" t="n">
-        <v>73.7</v>
+        <v>66.98999999999999</v>
       </c>
       <c r="L45" t="n">
-        <v>91.56999999999999</v>
+        <v>83.23</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>28</v>
       </c>
       <c r="J46" t="n">
-        <v>45.48</v>
+        <v>41.68</v>
       </c>
       <c r="K46" t="n">
-        <v>90.65000000000001</v>
+        <v>83.08</v>
       </c>
       <c r="L46" t="n">
-        <v>101.42</v>
+        <v>92.95</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>-53.51</v>
+        <v>-51.05</v>
       </c>
       <c r="K47" t="n">
-        <v>-21.2</v>
+        <v>-20.22</v>
       </c>
       <c r="L47" t="n">
-        <v>57.56</v>
+        <v>54.91</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>27</v>
       </c>
       <c r="J48" t="n">
-        <v>-131.49</v>
+        <v>-125.12</v>
       </c>
       <c r="K48" t="n">
-        <v>50.63</v>
+        <v>48.18</v>
       </c>
       <c r="L48" t="n">
-        <v>140.9</v>
+        <v>134.07</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>30</v>
       </c>
       <c r="J49" t="n">
-        <v>-25.61</v>
+        <v>-24.08</v>
       </c>
       <c r="K49" t="n">
-        <v>-52.87</v>
+        <v>-49.7</v>
       </c>
       <c r="L49" t="n">
-        <v>58.74</v>
+        <v>55.23</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>27</v>
       </c>
       <c r="J50" t="n">
-        <v>138.95</v>
+        <v>137.7</v>
       </c>
       <c r="K50" t="n">
-        <v>-19.21</v>
+        <v>-19.04</v>
       </c>
       <c r="L50" t="n">
-        <v>140.28</v>
+        <v>139.01</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>30</v>
       </c>
       <c r="J51" t="n">
-        <v>65.89</v>
+        <v>64.02</v>
       </c>
       <c r="K51" t="n">
-        <v>137.12</v>
+        <v>133.22</v>
       </c>
       <c r="L51" t="n">
-        <v>152.12</v>
+        <v>147.8</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>26</v>
       </c>
       <c r="J52" t="n">
-        <v>67.64</v>
+        <v>67.48</v>
       </c>
       <c r="K52" t="n">
-        <v>-122.62</v>
+        <v>-122.33</v>
       </c>
       <c r="L52" t="n">
-        <v>140.04</v>
+        <v>139.7</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>26</v>
       </c>
       <c r="J53" t="n">
-        <v>139.25</v>
+        <v>143.12</v>
       </c>
       <c r="K53" t="n">
-        <v>-174.69</v>
+        <v>-179.55</v>
       </c>
       <c r="L53" t="n">
-        <v>223.39</v>
+        <v>229.61</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>30</v>
       </c>
       <c r="J54" t="n">
-        <v>-51.23</v>
+        <v>-51.4</v>
       </c>
       <c r="K54" t="n">
-        <v>94.94</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="L54" t="n">
-        <v>107.88</v>
+        <v>108.22</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>31</v>
       </c>
       <c r="J55" t="n">
-        <v>146.97</v>
+        <v>145.56</v>
       </c>
       <c r="K55" t="n">
-        <v>-79.09999999999999</v>
+        <v>-78.34</v>
       </c>
       <c r="L55" t="n">
-        <v>166.9</v>
+        <v>165.3</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>30</v>
       </c>
       <c r="J56" t="n">
-        <v>-102.25</v>
+        <v>-103.01</v>
       </c>
       <c r="K56" t="n">
-        <v>204.77</v>
+        <v>206.3</v>
       </c>
       <c r="L56" t="n">
-        <v>228.88</v>
+        <v>230.59</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>31</v>
       </c>
       <c r="J57" t="n">
-        <v>201.31</v>
+        <v>202.14</v>
       </c>
       <c r="K57" t="n">
-        <v>44.88</v>
+        <v>45.06</v>
       </c>
       <c r="L57" t="n">
-        <v>206.26</v>
+        <v>207.11</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>26</v>
       </c>
       <c r="J58" t="n">
-        <v>134.45</v>
+        <v>138.35</v>
       </c>
       <c r="K58" t="n">
-        <v>115.06</v>
+        <v>118.4</v>
       </c>
       <c r="L58" t="n">
-        <v>176.97</v>
+        <v>182.09</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>-2.53</v>
+        <v>-2.33</v>
       </c>
       <c r="K59" t="n">
-        <v>-131.07</v>
+        <v>-120.76</v>
       </c>
       <c r="L59" t="n">
-        <v>131.09</v>
+        <v>120.78</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>31</v>
       </c>
       <c r="J60" t="n">
-        <v>2.31</v>
+        <v>2.1</v>
       </c>
       <c r="K60" t="n">
-        <v>65.42</v>
+        <v>59.46</v>
       </c>
       <c r="L60" t="n">
-        <v>65.45999999999999</v>
+        <v>59.5</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>28</v>
       </c>
       <c r="J61" t="n">
-        <v>28.72</v>
+        <v>26.29</v>
       </c>
       <c r="K61" t="n">
-        <v>47.84</v>
+        <v>43.8</v>
       </c>
       <c r="L61" t="n">
-        <v>55.8</v>
+        <v>51.09</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>31</v>
       </c>
       <c r="J62" t="n">
-        <v>-100.46</v>
+        <v>-93.68000000000001</v>
       </c>
       <c r="K62" t="n">
-        <v>-112.04</v>
+        <v>-104.48</v>
       </c>
       <c r="L62" t="n">
-        <v>150.49</v>
+        <v>140.33</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>31</v>
       </c>
       <c r="J63" t="n">
-        <v>7.23</v>
+        <v>6.7</v>
       </c>
       <c r="K63" t="n">
-        <v>-145.83</v>
+        <v>-135.09</v>
       </c>
       <c r="L63" t="n">
-        <v>146.01</v>
+        <v>135.25</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>31</v>
       </c>
       <c r="J64" t="n">
-        <v>-102.97</v>
+        <v>-96.79000000000001</v>
       </c>
       <c r="K64" t="n">
-        <v>97.41</v>
+        <v>91.56</v>
       </c>
       <c r="L64" t="n">
-        <v>141.74</v>
+        <v>133.24</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>30</v>
       </c>
       <c r="J65" t="n">
-        <v>103.98</v>
+        <v>101.93</v>
       </c>
       <c r="K65" t="n">
-        <v>117.55</v>
+        <v>115.23</v>
       </c>
       <c r="L65" t="n">
-        <v>156.94</v>
+        <v>153.85</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>29</v>
       </c>
       <c r="J66" t="n">
-        <v>52.08</v>
+        <v>51.35</v>
       </c>
       <c r="K66" t="n">
-        <v>83.53</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="L66" t="n">
-        <v>98.44</v>
+        <v>97.05</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>29</v>
       </c>
       <c r="J67" t="n">
-        <v>-143.83</v>
+        <v>-141.31</v>
       </c>
       <c r="K67" t="n">
-        <v>-21.01</v>
+        <v>-20.65</v>
       </c>
       <c r="L67" t="n">
-        <v>145.36</v>
+        <v>142.81</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>31</v>
       </c>
       <c r="J68" t="n">
-        <v>-150.71</v>
+        <v>-150.44</v>
       </c>
       <c r="K68" t="n">
-        <v>19.51</v>
+        <v>19.47</v>
       </c>
       <c r="L68" t="n">
-        <v>151.97</v>
+        <v>151.7</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>-163.47</v>
+        <v>-164.07</v>
       </c>
       <c r="K69" t="n">
-        <v>-224.26</v>
+        <v>-225.09</v>
       </c>
       <c r="L69" t="n">
-        <v>277.52</v>
+        <v>278.54</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>-115.29</v>
+        <v>-117.24</v>
       </c>
       <c r="K70" t="n">
-        <v>131.3</v>
+        <v>133.53</v>
       </c>
       <c r="L70" t="n">
-        <v>174.74</v>
+        <v>177.7</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>28</v>
       </c>
       <c r="J71" t="n">
-        <v>73.22</v>
+        <v>73.54000000000001</v>
       </c>
       <c r="K71" t="n">
-        <v>-276.12</v>
+        <v>-277.33</v>
       </c>
       <c r="L71" t="n">
-        <v>285.66</v>
+        <v>286.91</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>29</v>
       </c>
       <c r="J72" t="n">
-        <v>-211.55</v>
+        <v>-213.31</v>
       </c>
       <c r="K72" t="n">
-        <v>239.58</v>
+        <v>241.56</v>
       </c>
       <c r="L72" t="n">
-        <v>319.61</v>
+        <v>322.26</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>-168.34</v>
+        <v>-176.74</v>
       </c>
       <c r="K73" t="n">
-        <v>-155.12</v>
+        <v>-162.86</v>
       </c>
       <c r="L73" t="n">
-        <v>228.92</v>
+        <v>240.34</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>29</v>
       </c>
       <c r="J74" t="n">
-        <v>18.6</v>
+        <v>16.74</v>
       </c>
       <c r="K74" t="n">
-        <v>-104.62</v>
+        <v>-94.15000000000001</v>
       </c>
       <c r="L74" t="n">
-        <v>106.26</v>
+        <v>95.62</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>31</v>
       </c>
       <c r="J75" t="n">
-        <v>98.95999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="K75" t="n">
-        <v>-9.59</v>
+        <v>-8.609999999999999</v>
       </c>
       <c r="L75" t="n">
-        <v>99.42</v>
+        <v>89.3</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>29</v>
       </c>
       <c r="J76" t="n">
-        <v>53.07</v>
+        <v>48.13</v>
       </c>
       <c r="K76" t="n">
-        <v>43.71</v>
+        <v>39.64</v>
       </c>
       <c r="L76" t="n">
-        <v>68.76000000000001</v>
+        <v>62.35</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>27</v>
       </c>
       <c r="J77" t="n">
-        <v>-125.14</v>
+        <v>-120.07</v>
       </c>
       <c r="K77" t="n">
-        <v>46.57</v>
+        <v>44.69</v>
       </c>
       <c r="L77" t="n">
-        <v>133.52</v>
+        <v>128.11</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>30</v>
       </c>
       <c r="J78" t="n">
-        <v>60.82</v>
+        <v>57.76</v>
       </c>
       <c r="K78" t="n">
-        <v>-126.94</v>
+        <v>-120.57</v>
       </c>
       <c r="L78" t="n">
-        <v>140.76</v>
+        <v>133.69</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>28</v>
       </c>
       <c r="J79" t="n">
-        <v>-85.06999999999999</v>
+        <v>-80.38</v>
       </c>
       <c r="K79" t="n">
-        <v>41.82</v>
+        <v>39.52</v>
       </c>
       <c r="L79" t="n">
-        <v>94.79000000000001</v>
+        <v>89.56999999999999</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>31</v>
       </c>
       <c r="J80" t="n">
-        <v>-89.78</v>
+        <v>-87</v>
       </c>
       <c r="K80" t="n">
-        <v>-57.26</v>
+        <v>-55.49</v>
       </c>
       <c r="L80" t="n">
-        <v>106.49</v>
+        <v>103.18</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>29</v>
       </c>
       <c r="J81" t="n">
-        <v>-152.13</v>
+        <v>-148.13</v>
       </c>
       <c r="K81" t="n">
-        <v>118.22</v>
+        <v>115.11</v>
       </c>
       <c r="L81" t="n">
-        <v>192.66</v>
+        <v>187.6</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>26</v>
       </c>
       <c r="J82" t="n">
-        <v>-107.18</v>
+        <v>-105.2</v>
       </c>
       <c r="K82" t="n">
-        <v>196.34</v>
+        <v>192.71</v>
       </c>
       <c r="L82" t="n">
-        <v>223.69</v>
+        <v>219.55</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>26</v>
       </c>
       <c r="J83" t="n">
-        <v>112.21</v>
+        <v>116.03</v>
       </c>
       <c r="K83" t="n">
-        <v>68.23999999999999</v>
+        <v>70.56</v>
       </c>
       <c r="L83" t="n">
-        <v>131.33</v>
+        <v>135.8</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>27</v>
       </c>
       <c r="J84" t="n">
-        <v>-66.53</v>
+        <v>-67.58</v>
       </c>
       <c r="K84" t="n">
-        <v>76.20999999999999</v>
+        <v>77.42</v>
       </c>
       <c r="L84" t="n">
-        <v>101.16</v>
+        <v>102.77</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>25</v>
       </c>
       <c r="J85" t="n">
-        <v>-185.71</v>
+        <v>-191.59</v>
       </c>
       <c r="K85" t="n">
-        <v>40.58</v>
+        <v>41.86</v>
       </c>
       <c r="L85" t="n">
-        <v>190.09</v>
+        <v>196.11</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>28</v>
       </c>
       <c r="J86" t="n">
-        <v>17.89</v>
+        <v>18.2</v>
       </c>
       <c r="K86" t="n">
-        <v>-318.6</v>
+        <v>-324.01</v>
       </c>
       <c r="L86" t="n">
-        <v>319.11</v>
+        <v>324.52</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>29</v>
       </c>
       <c r="J87" t="n">
-        <v>-115.56</v>
+        <v>-115.95</v>
       </c>
       <c r="K87" t="n">
-        <v>-348.19</v>
+        <v>-349.37</v>
       </c>
       <c r="L87" t="n">
-        <v>366.86</v>
+        <v>368.11</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>-15.95</v>
+        <v>-16.57</v>
       </c>
       <c r="K88" t="n">
-        <v>193.19</v>
+        <v>200.72</v>
       </c>
       <c r="L88" t="n">
-        <v>193.85</v>
+        <v>201.4</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-05-25.xlsx
+++ b/output/2024-05-25.xlsx
@@ -640,13 +640,13 @@
         <v>31</v>
       </c>
       <c r="J14" t="n">
-        <v>-33.21</v>
+        <v>-22.92</v>
       </c>
       <c r="K14" t="n">
-        <v>-30.59</v>
+        <v>-21.11</v>
       </c>
       <c r="L14" t="n">
-        <v>45.15</v>
+        <v>31.16</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>26</v>
       </c>
       <c r="J15" t="n">
-        <v>44.6</v>
+        <v>28.58</v>
       </c>
       <c r="K15" t="n">
-        <v>-88.77</v>
+        <v>-56.88</v>
       </c>
       <c r="L15" t="n">
-        <v>99.34999999999999</v>
+        <v>63.66</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>28</v>
       </c>
       <c r="J16" t="n">
-        <v>-36.67</v>
+        <v>-20.06</v>
       </c>
       <c r="K16" t="n">
-        <v>50.2</v>
+        <v>27.46</v>
       </c>
       <c r="L16" t="n">
-        <v>62.17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>27</v>
       </c>
       <c r="J17" t="n">
-        <v>-87.61</v>
+        <v>-56.86</v>
       </c>
       <c r="K17" t="n">
-        <v>34.58</v>
+        <v>22.44</v>
       </c>
       <c r="L17" t="n">
-        <v>94.19</v>
+        <v>61.13</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>28</v>
       </c>
       <c r="J18" t="n">
-        <v>79.72</v>
+        <v>53.52</v>
       </c>
       <c r="K18" t="n">
-        <v>-28.76</v>
+        <v>-19.31</v>
       </c>
       <c r="L18" t="n">
-        <v>84.75</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>66.77</v>
+        <v>42.08</v>
       </c>
       <c r="K19" t="n">
-        <v>58.1</v>
+        <v>36.62</v>
       </c>
       <c r="L19" t="n">
-        <v>88.51000000000001</v>
+        <v>55.79</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>30</v>
       </c>
       <c r="J20" t="n">
-        <v>97.55</v>
+        <v>66.18000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>39.15</v>
+        <v>26.56</v>
       </c>
       <c r="L20" t="n">
-        <v>105.12</v>
+        <v>71.31</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>26</v>
       </c>
       <c r="J21" t="n">
-        <v>8.949999999999999</v>
+        <v>5.62</v>
       </c>
       <c r="K21" t="n">
-        <v>202.05</v>
+        <v>126.84</v>
       </c>
       <c r="L21" t="n">
-        <v>202.25</v>
+        <v>126.97</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>27</v>
       </c>
       <c r="J22" t="n">
-        <v>102</v>
+        <v>60.26</v>
       </c>
       <c r="K22" t="n">
-        <v>90.51000000000001</v>
+        <v>53.47</v>
       </c>
       <c r="L22" t="n">
-        <v>136.37</v>
+        <v>80.56</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>31</v>
       </c>
       <c r="J23" t="n">
-        <v>79.55</v>
+        <v>56.41</v>
       </c>
       <c r="K23" t="n">
-        <v>92.26000000000001</v>
+        <v>65.42</v>
       </c>
       <c r="L23" t="n">
-        <v>121.82</v>
+        <v>86.39</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>27</v>
       </c>
       <c r="J24" t="n">
-        <v>-172.69</v>
+        <v>-108.65</v>
       </c>
       <c r="K24" t="n">
-        <v>73.23</v>
+        <v>46.08</v>
       </c>
       <c r="L24" t="n">
-        <v>187.57</v>
+        <v>118.02</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>31</v>
       </c>
       <c r="J25" t="n">
-        <v>9.529999999999999</v>
+        <v>6.46</v>
       </c>
       <c r="K25" t="n">
-        <v>-161.66</v>
+        <v>-109.56</v>
       </c>
       <c r="L25" t="n">
-        <v>161.94</v>
+        <v>109.75</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>31</v>
       </c>
       <c r="J26" t="n">
-        <v>125.39</v>
+        <v>84.67</v>
       </c>
       <c r="K26" t="n">
-        <v>88.76000000000001</v>
+        <v>59.93</v>
       </c>
       <c r="L26" t="n">
-        <v>153.63</v>
+        <v>103.73</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>29</v>
       </c>
       <c r="J27" t="n">
-        <v>-239.02</v>
+        <v>-163.47</v>
       </c>
       <c r="K27" t="n">
-        <v>-8.6</v>
+        <v>-5.88</v>
       </c>
       <c r="L27" t="n">
-        <v>239.18</v>
+        <v>163.58</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>29</v>
       </c>
       <c r="J28" t="n">
-        <v>-72.8</v>
+        <v>-48.94</v>
       </c>
       <c r="K28" t="n">
-        <v>-129</v>
+        <v>-86.73</v>
       </c>
       <c r="L28" t="n">
-        <v>148.12</v>
+        <v>99.59</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>26</v>
       </c>
       <c r="J29" t="n">
-        <v>-14.75</v>
+        <v>-9.75</v>
       </c>
       <c r="K29" t="n">
-        <v>55.65</v>
+        <v>36.78</v>
       </c>
       <c r="L29" t="n">
-        <v>57.57</v>
+        <v>38.05</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>26</v>
       </c>
       <c r="J30" t="n">
-        <v>-88.52</v>
+        <v>-50.87</v>
       </c>
       <c r="K30" t="n">
-        <v>-68.70999999999999</v>
+        <v>-39.48</v>
       </c>
       <c r="L30" t="n">
-        <v>112.05</v>
+        <v>64.39</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>-25.68</v>
+        <v>-16.18</v>
       </c>
       <c r="K31" t="n">
-        <v>-47.95</v>
+        <v>-30.22</v>
       </c>
       <c r="L31" t="n">
-        <v>54.4</v>
+        <v>34.28</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>30</v>
       </c>
       <c r="J32" t="n">
-        <v>-42.39</v>
+        <v>-25.66</v>
       </c>
       <c r="K32" t="n">
-        <v>-69.98999999999999</v>
+        <v>-42.36</v>
       </c>
       <c r="L32" t="n">
-        <v>81.83</v>
+        <v>49.52</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>25</v>
       </c>
       <c r="J33" t="n">
-        <v>47.56</v>
+        <v>30.26</v>
       </c>
       <c r="K33" t="n">
-        <v>56.44</v>
+        <v>35.91</v>
       </c>
       <c r="L33" t="n">
-        <v>73.8</v>
+        <v>46.97</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>26</v>
       </c>
       <c r="J34" t="n">
-        <v>123.03</v>
+        <v>75.11</v>
       </c>
       <c r="K34" t="n">
-        <v>73.40000000000001</v>
+        <v>44.81</v>
       </c>
       <c r="L34" t="n">
-        <v>143.27</v>
+        <v>87.45999999999999</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>30</v>
       </c>
       <c r="J35" t="n">
-        <v>-42.94</v>
+        <v>-26.17</v>
       </c>
       <c r="K35" t="n">
-        <v>171.51</v>
+        <v>104.5</v>
       </c>
       <c r="L35" t="n">
-        <v>176.81</v>
+        <v>107.73</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>30</v>
       </c>
       <c r="J36" t="n">
-        <v>112.35</v>
+        <v>69.19</v>
       </c>
       <c r="K36" t="n">
-        <v>-91.73</v>
+        <v>-56.49</v>
       </c>
       <c r="L36" t="n">
-        <v>145.04</v>
+        <v>89.31999999999999</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>30</v>
       </c>
       <c r="J37" t="n">
-        <v>14.78</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="K37" t="n">
-        <v>-114.24</v>
+        <v>-72.53</v>
       </c>
       <c r="L37" t="n">
-        <v>115.19</v>
+        <v>73.13</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>27</v>
       </c>
       <c r="J38" t="n">
-        <v>39.15</v>
+        <v>26.81</v>
       </c>
       <c r="K38" t="n">
-        <v>-201.99</v>
+        <v>-138.32</v>
       </c>
       <c r="L38" t="n">
-        <v>205.75</v>
+        <v>140.89</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>27</v>
       </c>
       <c r="J39" t="n">
-        <v>-189.09</v>
+        <v>-130.03</v>
       </c>
       <c r="K39" t="n">
-        <v>25.71</v>
+        <v>17.68</v>
       </c>
       <c r="L39" t="n">
-        <v>190.83</v>
+        <v>131.23</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>61.33</v>
+        <v>42.08</v>
       </c>
       <c r="K40" t="n">
-        <v>-221.85</v>
+        <v>-152.24</v>
       </c>
       <c r="L40" t="n">
-        <v>230.17</v>
+        <v>157.95</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>27</v>
       </c>
       <c r="J41" t="n">
-        <v>138.2</v>
+        <v>93.70999999999999</v>
       </c>
       <c r="K41" t="n">
-        <v>27.04</v>
+        <v>18.34</v>
       </c>
       <c r="L41" t="n">
-        <v>140.82</v>
+        <v>95.48999999999999</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>25</v>
       </c>
       <c r="J42" t="n">
-        <v>330.24</v>
+        <v>185.51</v>
       </c>
       <c r="K42" t="n">
-        <v>-283.89</v>
+        <v>-159.47</v>
       </c>
       <c r="L42" t="n">
-        <v>435.49</v>
+        <v>244.63</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>28</v>
       </c>
       <c r="J43" t="n">
-        <v>-129.37</v>
+        <v>-85.72</v>
       </c>
       <c r="K43" t="n">
-        <v>-61.94</v>
+        <v>-41.04</v>
       </c>
       <c r="L43" t="n">
-        <v>143.43</v>
+        <v>95.04000000000001</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>31</v>
       </c>
       <c r="J44" t="n">
-        <v>29.35</v>
+        <v>22.01</v>
       </c>
       <c r="K44" t="n">
-        <v>-40.34</v>
+        <v>-30.25</v>
       </c>
       <c r="L44" t="n">
-        <v>49.88</v>
+        <v>37.41</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>29</v>
       </c>
       <c r="J45" t="n">
-        <v>-49.39</v>
+        <v>-29.41</v>
       </c>
       <c r="K45" t="n">
-        <v>66.98999999999999</v>
+        <v>39.89</v>
       </c>
       <c r="L45" t="n">
-        <v>83.23</v>
+        <v>49.56</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>28</v>
       </c>
       <c r="J46" t="n">
-        <v>41.68</v>
+        <v>26.71</v>
       </c>
       <c r="K46" t="n">
-        <v>83.08</v>
+        <v>53.23</v>
       </c>
       <c r="L46" t="n">
-        <v>92.95</v>
+        <v>59.56</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>-51.05</v>
+        <v>-32.88</v>
       </c>
       <c r="K47" t="n">
-        <v>-20.22</v>
+        <v>-13.03</v>
       </c>
       <c r="L47" t="n">
-        <v>54.91</v>
+        <v>35.37</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>27</v>
       </c>
       <c r="J48" t="n">
-        <v>-125.12</v>
+        <v>-72.08</v>
       </c>
       <c r="K48" t="n">
-        <v>48.18</v>
+        <v>27.76</v>
       </c>
       <c r="L48" t="n">
-        <v>134.07</v>
+        <v>77.23999999999999</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>30</v>
       </c>
       <c r="J49" t="n">
-        <v>-24.08</v>
+        <v>-14.41</v>
       </c>
       <c r="K49" t="n">
-        <v>-49.7</v>
+        <v>-29.76</v>
       </c>
       <c r="L49" t="n">
-        <v>55.23</v>
+        <v>33.07</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>27</v>
       </c>
       <c r="J50" t="n">
-        <v>137.7</v>
+        <v>80.55</v>
       </c>
       <c r="K50" t="n">
-        <v>-19.04</v>
+        <v>-11.14</v>
       </c>
       <c r="L50" t="n">
-        <v>139.01</v>
+        <v>81.31</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>30</v>
       </c>
       <c r="J51" t="n">
-        <v>64.02</v>
+        <v>39.11</v>
       </c>
       <c r="K51" t="n">
-        <v>133.22</v>
+        <v>81.39</v>
       </c>
       <c r="L51" t="n">
-        <v>147.8</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>26</v>
       </c>
       <c r="J52" t="n">
-        <v>67.48</v>
+        <v>40.69</v>
       </c>
       <c r="K52" t="n">
-        <v>-122.33</v>
+        <v>-73.76000000000001</v>
       </c>
       <c r="L52" t="n">
-        <v>139.7</v>
+        <v>84.23</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>26</v>
       </c>
       <c r="J53" t="n">
-        <v>143.12</v>
+        <v>93.29000000000001</v>
       </c>
       <c r="K53" t="n">
-        <v>-179.55</v>
+        <v>-117.04</v>
       </c>
       <c r="L53" t="n">
-        <v>229.61</v>
+        <v>149.67</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>30</v>
       </c>
       <c r="J54" t="n">
-        <v>-51.4</v>
+        <v>-35.27</v>
       </c>
       <c r="K54" t="n">
-        <v>95.23999999999999</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="L54" t="n">
-        <v>108.22</v>
+        <v>74.26000000000001</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>31</v>
       </c>
       <c r="J55" t="n">
-        <v>145.56</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="K55" t="n">
-        <v>-78.34</v>
+        <v>-51.45</v>
       </c>
       <c r="L55" t="n">
-        <v>165.3</v>
+        <v>108.56</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>30</v>
       </c>
       <c r="J56" t="n">
-        <v>-103.01</v>
+        <v>-61.68</v>
       </c>
       <c r="K56" t="n">
-        <v>206.3</v>
+        <v>123.52</v>
       </c>
       <c r="L56" t="n">
-        <v>230.59</v>
+        <v>138.07</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>31</v>
       </c>
       <c r="J57" t="n">
-        <v>202.14</v>
+        <v>124.83</v>
       </c>
       <c r="K57" t="n">
-        <v>45.06</v>
+        <v>27.83</v>
       </c>
       <c r="L57" t="n">
-        <v>207.11</v>
+        <v>127.89</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>26</v>
       </c>
       <c r="J58" t="n">
-        <v>138.35</v>
+        <v>88.94</v>
       </c>
       <c r="K58" t="n">
-        <v>118.4</v>
+        <v>76.11</v>
       </c>
       <c r="L58" t="n">
-        <v>182.09</v>
+        <v>117.06</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>-2.33</v>
+        <v>-1.41</v>
       </c>
       <c r="K59" t="n">
-        <v>-120.76</v>
+        <v>-73.04000000000001</v>
       </c>
       <c r="L59" t="n">
-        <v>120.78</v>
+        <v>73.05</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>31</v>
       </c>
       <c r="J60" t="n">
-        <v>2.1</v>
+        <v>1.42</v>
       </c>
       <c r="K60" t="n">
-        <v>59.46</v>
+        <v>40.07</v>
       </c>
       <c r="L60" t="n">
-        <v>59.5</v>
+        <v>40.1</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>28</v>
       </c>
       <c r="J61" t="n">
-        <v>26.29</v>
+        <v>16.2</v>
       </c>
       <c r="K61" t="n">
-        <v>43.8</v>
+        <v>26.99</v>
       </c>
       <c r="L61" t="n">
-        <v>51.09</v>
+        <v>31.48</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>31</v>
       </c>
       <c r="J62" t="n">
-        <v>-93.68000000000001</v>
+        <v>-56.57</v>
       </c>
       <c r="K62" t="n">
-        <v>-104.48</v>
+        <v>-63.09</v>
       </c>
       <c r="L62" t="n">
-        <v>140.33</v>
+        <v>84.73999999999999</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>31</v>
       </c>
       <c r="J63" t="n">
-        <v>6.7</v>
+        <v>4.51</v>
       </c>
       <c r="K63" t="n">
-        <v>-135.09</v>
+        <v>-90.94</v>
       </c>
       <c r="L63" t="n">
-        <v>135.25</v>
+        <v>91.05</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>31</v>
       </c>
       <c r="J64" t="n">
-        <v>-96.79000000000001</v>
+        <v>-59.75</v>
       </c>
       <c r="K64" t="n">
-        <v>91.56</v>
+        <v>56.53</v>
       </c>
       <c r="L64" t="n">
-        <v>133.24</v>
+        <v>82.25</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>30</v>
       </c>
       <c r="J65" t="n">
-        <v>101.93</v>
+        <v>53.07</v>
       </c>
       <c r="K65" t="n">
-        <v>115.23</v>
+        <v>60</v>
       </c>
       <c r="L65" t="n">
-        <v>153.85</v>
+        <v>80.09999999999999</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>29</v>
       </c>
       <c r="J66" t="n">
-        <v>51.35</v>
+        <v>30.57</v>
       </c>
       <c r="K66" t="n">
-        <v>82.34999999999999</v>
+        <v>49.02</v>
       </c>
       <c r="L66" t="n">
-        <v>97.05</v>
+        <v>57.77</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>29</v>
       </c>
       <c r="J67" t="n">
-        <v>-141.31</v>
+        <v>-85.87</v>
       </c>
       <c r="K67" t="n">
-        <v>-20.65</v>
+        <v>-12.55</v>
       </c>
       <c r="L67" t="n">
-        <v>142.81</v>
+        <v>86.78</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>31</v>
       </c>
       <c r="J68" t="n">
-        <v>-150.44</v>
+        <v>-101.75</v>
       </c>
       <c r="K68" t="n">
-        <v>19.47</v>
+        <v>13.17</v>
       </c>
       <c r="L68" t="n">
-        <v>151.7</v>
+        <v>102.6</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>-164.07</v>
+        <v>-100.9</v>
       </c>
       <c r="K69" t="n">
-        <v>-225.09</v>
+        <v>-138.42</v>
       </c>
       <c r="L69" t="n">
-        <v>278.54</v>
+        <v>171.29</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>-117.24</v>
+        <v>-73.65000000000001</v>
       </c>
       <c r="K70" t="n">
-        <v>133.53</v>
+        <v>83.87</v>
       </c>
       <c r="L70" t="n">
-        <v>177.7</v>
+        <v>111.62</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>28</v>
       </c>
       <c r="J71" t="n">
-        <v>73.54000000000001</v>
+        <v>43.57</v>
       </c>
       <c r="K71" t="n">
-        <v>-277.33</v>
+        <v>-164.31</v>
       </c>
       <c r="L71" t="n">
-        <v>286.91</v>
+        <v>169.99</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>29</v>
       </c>
       <c r="J72" t="n">
-        <v>-213.31</v>
+        <v>-137.12</v>
       </c>
       <c r="K72" t="n">
-        <v>241.56</v>
+        <v>155.29</v>
       </c>
       <c r="L72" t="n">
-        <v>322.26</v>
+        <v>207.17</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>-176.74</v>
+        <v>-108.54</v>
       </c>
       <c r="K73" t="n">
-        <v>-162.86</v>
+        <v>-100.02</v>
       </c>
       <c r="L73" t="n">
-        <v>240.34</v>
+        <v>147.59</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>29</v>
       </c>
       <c r="J74" t="n">
-        <v>16.74</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="K74" t="n">
-        <v>-94.15000000000001</v>
+        <v>-52.83</v>
       </c>
       <c r="L74" t="n">
-        <v>95.62</v>
+        <v>53.66</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>31</v>
       </c>
       <c r="J75" t="n">
-        <v>88.89</v>
+        <v>54.09</v>
       </c>
       <c r="K75" t="n">
-        <v>-8.609999999999999</v>
+        <v>-5.24</v>
       </c>
       <c r="L75" t="n">
-        <v>89.3</v>
+        <v>54.34</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>29</v>
       </c>
       <c r="J76" t="n">
-        <v>48.13</v>
+        <v>29.41</v>
       </c>
       <c r="K76" t="n">
-        <v>39.64</v>
+        <v>24.22</v>
       </c>
       <c r="L76" t="n">
-        <v>62.35</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>27</v>
       </c>
       <c r="J77" t="n">
-        <v>-120.07</v>
+        <v>-67.5</v>
       </c>
       <c r="K77" t="n">
-        <v>44.69</v>
+        <v>25.12</v>
       </c>
       <c r="L77" t="n">
-        <v>128.11</v>
+        <v>72.02</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>30</v>
       </c>
       <c r="J78" t="n">
-        <v>57.76</v>
+        <v>31.95</v>
       </c>
       <c r="K78" t="n">
-        <v>-120.57</v>
+        <v>-66.69</v>
       </c>
       <c r="L78" t="n">
-        <v>133.69</v>
+        <v>73.95</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>28</v>
       </c>
       <c r="J79" t="n">
-        <v>-80.38</v>
+        <v>-51.4</v>
       </c>
       <c r="K79" t="n">
-        <v>39.52</v>
+        <v>25.27</v>
       </c>
       <c r="L79" t="n">
-        <v>89.56999999999999</v>
+        <v>57.28</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>31</v>
       </c>
       <c r="J80" t="n">
-        <v>-87</v>
+        <v>-48.44</v>
       </c>
       <c r="K80" t="n">
-        <v>-55.49</v>
+        <v>-30.9</v>
       </c>
       <c r="L80" t="n">
-        <v>103.18</v>
+        <v>57.46</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>29</v>
       </c>
       <c r="J81" t="n">
-        <v>-148.13</v>
+        <v>-89.08</v>
       </c>
       <c r="K81" t="n">
-        <v>115.11</v>
+        <v>69.23</v>
       </c>
       <c r="L81" t="n">
-        <v>187.6</v>
+        <v>112.82</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>26</v>
       </c>
       <c r="J82" t="n">
-        <v>-105.2</v>
+        <v>-56.35</v>
       </c>
       <c r="K82" t="n">
-        <v>192.71</v>
+        <v>103.22</v>
       </c>
       <c r="L82" t="n">
-        <v>219.55</v>
+        <v>117.6</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>26</v>
       </c>
       <c r="J83" t="n">
-        <v>116.03</v>
+        <v>80.13</v>
       </c>
       <c r="K83" t="n">
-        <v>70.56</v>
+        <v>48.73</v>
       </c>
       <c r="L83" t="n">
-        <v>135.8</v>
+        <v>93.78</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>27</v>
       </c>
       <c r="J84" t="n">
-        <v>-67.58</v>
+        <v>-45.34</v>
       </c>
       <c r="K84" t="n">
-        <v>77.42</v>
+        <v>51.94</v>
       </c>
       <c r="L84" t="n">
-        <v>102.77</v>
+        <v>68.95</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>25</v>
       </c>
       <c r="J85" t="n">
-        <v>-191.59</v>
+        <v>-119.74</v>
       </c>
       <c r="K85" t="n">
-        <v>41.86</v>
+        <v>26.16</v>
       </c>
       <c r="L85" t="n">
-        <v>196.11</v>
+        <v>122.57</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>28</v>
       </c>
       <c r="J86" t="n">
-        <v>18.2</v>
+        <v>11.98</v>
       </c>
       <c r="K86" t="n">
-        <v>-324.01</v>
+        <v>-213.37</v>
       </c>
       <c r="L86" t="n">
-        <v>324.52</v>
+        <v>213.71</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>29</v>
       </c>
       <c r="J87" t="n">
-        <v>-115.95</v>
+        <v>-73.67</v>
       </c>
       <c r="K87" t="n">
-        <v>-349.37</v>
+        <v>-221.97</v>
       </c>
       <c r="L87" t="n">
-        <v>368.11</v>
+        <v>233.88</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>-16.57</v>
+        <v>-10.72</v>
       </c>
       <c r="K88" t="n">
-        <v>200.72</v>
+        <v>129.8</v>
       </c>
       <c r="L88" t="n">
-        <v>201.4</v>
+        <v>130.24</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-05-25.xlsx
+++ b/output/2024-05-25.xlsx
@@ -640,13 +640,13 @@
         <v>31</v>
       </c>
       <c r="J14" t="n">
-        <v>-22.92</v>
+        <v>-23.67</v>
       </c>
       <c r="K14" t="n">
-        <v>-21.11</v>
+        <v>-21.8</v>
       </c>
       <c r="L14" t="n">
-        <v>31.16</v>
+        <v>32.18</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>26</v>
       </c>
       <c r="J15" t="n">
-        <v>28.58</v>
+        <v>27.68</v>
       </c>
       <c r="K15" t="n">
-        <v>-56.88</v>
+        <v>-55.08</v>
       </c>
       <c r="L15" t="n">
-        <v>63.66</v>
+        <v>61.65</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>28</v>
       </c>
       <c r="J16" t="n">
-        <v>-20.06</v>
+        <v>-21.64</v>
       </c>
       <c r="K16" t="n">
-        <v>27.46</v>
+        <v>29.62</v>
       </c>
       <c r="L16" t="n">
-        <v>34</v>
+        <v>36.68</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>27</v>
       </c>
       <c r="J17" t="n">
-        <v>-56.86</v>
+        <v>-56.81</v>
       </c>
       <c r="K17" t="n">
-        <v>22.44</v>
+        <v>22.42</v>
       </c>
       <c r="L17" t="n">
-        <v>61.13</v>
+        <v>61.07</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>28</v>
       </c>
       <c r="J18" t="n">
-        <v>53.52</v>
+        <v>53.65</v>
       </c>
       <c r="K18" t="n">
-        <v>-19.31</v>
+        <v>-19.36</v>
       </c>
       <c r="L18" t="n">
-        <v>56.9</v>
+        <v>57.04</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>42.08</v>
+        <v>42.7</v>
       </c>
       <c r="K19" t="n">
-        <v>36.62</v>
+        <v>37.16</v>
       </c>
       <c r="L19" t="n">
-        <v>55.79</v>
+        <v>56.61</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>30</v>
       </c>
       <c r="J20" t="n">
-        <v>66.18000000000001</v>
+        <v>66.98</v>
       </c>
       <c r="K20" t="n">
-        <v>26.56</v>
+        <v>26.88</v>
       </c>
       <c r="L20" t="n">
-        <v>71.31</v>
+        <v>72.17</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>26</v>
       </c>
       <c r="J21" t="n">
-        <v>5.62</v>
+        <v>5.13</v>
       </c>
       <c r="K21" t="n">
-        <v>126.84</v>
+        <v>115.96</v>
       </c>
       <c r="L21" t="n">
-        <v>126.97</v>
+        <v>116.08</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>27</v>
       </c>
       <c r="J22" t="n">
-        <v>60.26</v>
+        <v>60.94</v>
       </c>
       <c r="K22" t="n">
-        <v>53.47</v>
+        <v>54.07</v>
       </c>
       <c r="L22" t="n">
-        <v>80.56</v>
+        <v>81.47</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>31</v>
       </c>
       <c r="J23" t="n">
-        <v>56.41</v>
+        <v>57.41</v>
       </c>
       <c r="K23" t="n">
-        <v>65.42</v>
+        <v>66.58</v>
       </c>
       <c r="L23" t="n">
-        <v>86.39</v>
+        <v>87.92</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>27</v>
       </c>
       <c r="J24" t="n">
-        <v>-108.65</v>
+        <v>-108.85</v>
       </c>
       <c r="K24" t="n">
-        <v>46.08</v>
+        <v>46.16</v>
       </c>
       <c r="L24" t="n">
-        <v>118.02</v>
+        <v>118.23</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>31</v>
       </c>
       <c r="J25" t="n">
-        <v>6.46</v>
+        <v>6.41</v>
       </c>
       <c r="K25" t="n">
-        <v>-109.56</v>
+        <v>-108.71</v>
       </c>
       <c r="L25" t="n">
-        <v>109.75</v>
+        <v>108.9</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>31</v>
       </c>
       <c r="J26" t="n">
-        <v>84.67</v>
+        <v>89.27</v>
       </c>
       <c r="K26" t="n">
-        <v>59.93</v>
+        <v>63.19</v>
       </c>
       <c r="L26" t="n">
-        <v>103.73</v>
+        <v>109.37</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>29</v>
       </c>
       <c r="J27" t="n">
-        <v>-163.47</v>
+        <v>-162.49</v>
       </c>
       <c r="K27" t="n">
-        <v>-5.88</v>
+        <v>-5.85</v>
       </c>
       <c r="L27" t="n">
-        <v>163.58</v>
+        <v>162.6</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>29</v>
       </c>
       <c r="J28" t="n">
-        <v>-48.94</v>
+        <v>-52.38</v>
       </c>
       <c r="K28" t="n">
-        <v>-86.73</v>
+        <v>-92.81999999999999</v>
       </c>
       <c r="L28" t="n">
-        <v>99.59</v>
+        <v>106.58</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>26</v>
       </c>
       <c r="J29" t="n">
-        <v>-9.75</v>
+        <v>-9.9</v>
       </c>
       <c r="K29" t="n">
-        <v>36.78</v>
+        <v>37.34</v>
       </c>
       <c r="L29" t="n">
-        <v>38.05</v>
+        <v>38.63</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>26</v>
       </c>
       <c r="J30" t="n">
-        <v>-50.87</v>
+        <v>-49.52</v>
       </c>
       <c r="K30" t="n">
-        <v>-39.48</v>
+        <v>-38.44</v>
       </c>
       <c r="L30" t="n">
-        <v>64.39</v>
+        <v>62.69</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>-16.18</v>
+        <v>-16.83</v>
       </c>
       <c r="K31" t="n">
-        <v>-30.22</v>
+        <v>-31.43</v>
       </c>
       <c r="L31" t="n">
-        <v>34.28</v>
+        <v>35.66</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>30</v>
       </c>
       <c r="J32" t="n">
-        <v>-25.66</v>
+        <v>-25.9</v>
       </c>
       <c r="K32" t="n">
-        <v>-42.36</v>
+        <v>-42.76</v>
       </c>
       <c r="L32" t="n">
-        <v>49.52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>25</v>
       </c>
       <c r="J33" t="n">
-        <v>30.26</v>
+        <v>31.16</v>
       </c>
       <c r="K33" t="n">
-        <v>35.91</v>
+        <v>36.98</v>
       </c>
       <c r="L33" t="n">
-        <v>46.97</v>
+        <v>48.36</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>26</v>
       </c>
       <c r="J34" t="n">
-        <v>75.11</v>
+        <v>72.08</v>
       </c>
       <c r="K34" t="n">
-        <v>44.81</v>
+        <v>43</v>
       </c>
       <c r="L34" t="n">
-        <v>87.45999999999999</v>
+        <v>83.93000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>30</v>
       </c>
       <c r="J35" t="n">
-        <v>-26.17</v>
+        <v>-25.18</v>
       </c>
       <c r="K35" t="n">
-        <v>104.5</v>
+        <v>100.58</v>
       </c>
       <c r="L35" t="n">
-        <v>107.73</v>
+        <v>103.68</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>30</v>
       </c>
       <c r="J36" t="n">
-        <v>69.19</v>
+        <v>67.8</v>
       </c>
       <c r="K36" t="n">
-        <v>-56.49</v>
+        <v>-55.35</v>
       </c>
       <c r="L36" t="n">
-        <v>89.31999999999999</v>
+        <v>87.52</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>30</v>
       </c>
       <c r="J37" t="n">
-        <v>9.380000000000001</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="K37" t="n">
-        <v>-72.53</v>
+        <v>-72.56999999999999</v>
       </c>
       <c r="L37" t="n">
-        <v>73.13</v>
+        <v>73.18000000000001</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>27</v>
       </c>
       <c r="J38" t="n">
-        <v>26.81</v>
+        <v>25.93</v>
       </c>
       <c r="K38" t="n">
-        <v>-138.32</v>
+        <v>-133.76</v>
       </c>
       <c r="L38" t="n">
-        <v>140.89</v>
+        <v>136.25</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>27</v>
       </c>
       <c r="J39" t="n">
-        <v>-130.03</v>
+        <v>-126.43</v>
       </c>
       <c r="K39" t="n">
-        <v>17.68</v>
+        <v>17.19</v>
       </c>
       <c r="L39" t="n">
-        <v>131.23</v>
+        <v>127.6</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>42.08</v>
+        <v>40.35</v>
       </c>
       <c r="K40" t="n">
-        <v>-152.24</v>
+        <v>-145.97</v>
       </c>
       <c r="L40" t="n">
-        <v>157.95</v>
+        <v>151.45</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>27</v>
       </c>
       <c r="J41" t="n">
-        <v>93.70999999999999</v>
+        <v>100.27</v>
       </c>
       <c r="K41" t="n">
-        <v>18.34</v>
+        <v>19.62</v>
       </c>
       <c r="L41" t="n">
-        <v>95.48999999999999</v>
+        <v>102.18</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>25</v>
       </c>
       <c r="J42" t="n">
-        <v>185.51</v>
+        <v>180.36</v>
       </c>
       <c r="K42" t="n">
-        <v>-159.47</v>
+        <v>-155.05</v>
       </c>
       <c r="L42" t="n">
-        <v>244.63</v>
+        <v>237.85</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>28</v>
       </c>
       <c r="J43" t="n">
-        <v>-85.72</v>
+        <v>-91.55</v>
       </c>
       <c r="K43" t="n">
-        <v>-41.04</v>
+        <v>-43.83</v>
       </c>
       <c r="L43" t="n">
-        <v>95.04000000000001</v>
+        <v>101.5</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>31</v>
       </c>
       <c r="J44" t="n">
-        <v>22.01</v>
+        <v>21.88</v>
       </c>
       <c r="K44" t="n">
-        <v>-30.25</v>
+        <v>-30.07</v>
       </c>
       <c r="L44" t="n">
-        <v>37.41</v>
+        <v>37.19</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>29</v>
       </c>
       <c r="J45" t="n">
-        <v>-29.41</v>
+        <v>-29.35</v>
       </c>
       <c r="K45" t="n">
-        <v>39.89</v>
+        <v>39.8</v>
       </c>
       <c r="L45" t="n">
-        <v>49.56</v>
+        <v>49.45</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>28</v>
       </c>
       <c r="J46" t="n">
-        <v>26.71</v>
+        <v>25.94</v>
       </c>
       <c r="K46" t="n">
-        <v>53.23</v>
+        <v>51.7</v>
       </c>
       <c r="L46" t="n">
-        <v>59.56</v>
+        <v>57.84</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>-32.88</v>
+        <v>-35.89</v>
       </c>
       <c r="K47" t="n">
-        <v>-13.03</v>
+        <v>-14.22</v>
       </c>
       <c r="L47" t="n">
-        <v>35.37</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>27</v>
       </c>
       <c r="J48" t="n">
-        <v>-72.08</v>
+        <v>-70.58</v>
       </c>
       <c r="K48" t="n">
-        <v>27.76</v>
+        <v>27.18</v>
       </c>
       <c r="L48" t="n">
-        <v>77.23999999999999</v>
+        <v>75.63</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>30</v>
       </c>
       <c r="J49" t="n">
-        <v>-14.41</v>
+        <v>-15.81</v>
       </c>
       <c r="K49" t="n">
-        <v>-29.76</v>
+        <v>-32.64</v>
       </c>
       <c r="L49" t="n">
-        <v>33.07</v>
+        <v>36.27</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>27</v>
       </c>
       <c r="J50" t="n">
-        <v>80.55</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="K50" t="n">
-        <v>-11.14</v>
+        <v>-11.26</v>
       </c>
       <c r="L50" t="n">
-        <v>81.31</v>
+        <v>82.18000000000001</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>30</v>
       </c>
       <c r="J51" t="n">
-        <v>39.11</v>
+        <v>38.62</v>
       </c>
       <c r="K51" t="n">
-        <v>81.39</v>
+        <v>80.37</v>
       </c>
       <c r="L51" t="n">
-        <v>90.3</v>
+        <v>89.17</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>26</v>
       </c>
       <c r="J52" t="n">
-        <v>40.69</v>
+        <v>40.98</v>
       </c>
       <c r="K52" t="n">
-        <v>-73.76000000000001</v>
+        <v>-74.29000000000001</v>
       </c>
       <c r="L52" t="n">
-        <v>84.23</v>
+        <v>84.84999999999999</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>26</v>
       </c>
       <c r="J53" t="n">
-        <v>93.29000000000001</v>
+        <v>91.02</v>
       </c>
       <c r="K53" t="n">
-        <v>-117.04</v>
+        <v>-114.18</v>
       </c>
       <c r="L53" t="n">
-        <v>149.67</v>
+        <v>146.02</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>30</v>
       </c>
       <c r="J54" t="n">
-        <v>-35.27</v>
+        <v>-37.04</v>
       </c>
       <c r="K54" t="n">
-        <v>65.34999999999999</v>
+        <v>68.64</v>
       </c>
       <c r="L54" t="n">
-        <v>74.26000000000001</v>
+        <v>77.98999999999999</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>31</v>
       </c>
       <c r="J55" t="n">
-        <v>95.59999999999999</v>
+        <v>95.31</v>
       </c>
       <c r="K55" t="n">
-        <v>-51.45</v>
+        <v>-51.29</v>
       </c>
       <c r="L55" t="n">
-        <v>108.56</v>
+        <v>108.23</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>30</v>
       </c>
       <c r="J56" t="n">
-        <v>-61.68</v>
+        <v>-62.86</v>
       </c>
       <c r="K56" t="n">
-        <v>123.52</v>
+        <v>125.9</v>
       </c>
       <c r="L56" t="n">
-        <v>138.07</v>
+        <v>140.72</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>31</v>
       </c>
       <c r="J57" t="n">
-        <v>124.83</v>
+        <v>128.01</v>
       </c>
       <c r="K57" t="n">
-        <v>27.83</v>
+        <v>28.54</v>
       </c>
       <c r="L57" t="n">
-        <v>127.89</v>
+        <v>131.16</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>26</v>
       </c>
       <c r="J58" t="n">
-        <v>88.94</v>
+        <v>93.76000000000001</v>
       </c>
       <c r="K58" t="n">
-        <v>76.11</v>
+        <v>80.23999999999999</v>
       </c>
       <c r="L58" t="n">
-        <v>117.06</v>
+        <v>123.4</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>-1.41</v>
+        <v>-1.36</v>
       </c>
       <c r="K59" t="n">
-        <v>-73.04000000000001</v>
+        <v>-70.33</v>
       </c>
       <c r="L59" t="n">
-        <v>73.05</v>
+        <v>70.34</v>
       </c>
     </row>
     <row r="60">
@@ -2575,10 +2575,10 @@
         <v>1.42</v>
       </c>
       <c r="K60" t="n">
-        <v>40.07</v>
+        <v>40.18</v>
       </c>
       <c r="L60" t="n">
-        <v>40.1</v>
+        <v>40.21</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>28</v>
       </c>
       <c r="J61" t="n">
-        <v>16.2</v>
+        <v>17.24</v>
       </c>
       <c r="K61" t="n">
-        <v>26.99</v>
+        <v>28.73</v>
       </c>
       <c r="L61" t="n">
-        <v>31.48</v>
+        <v>33.51</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>31</v>
       </c>
       <c r="J62" t="n">
-        <v>-56.57</v>
+        <v>-54.36</v>
       </c>
       <c r="K62" t="n">
-        <v>-63.09</v>
+        <v>-60.62</v>
       </c>
       <c r="L62" t="n">
-        <v>84.73999999999999</v>
+        <v>81.42</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>31</v>
       </c>
       <c r="J63" t="n">
-        <v>4.51</v>
+        <v>4.29</v>
       </c>
       <c r="K63" t="n">
-        <v>-90.94</v>
+        <v>-86.45999999999999</v>
       </c>
       <c r="L63" t="n">
-        <v>91.05</v>
+        <v>86.56</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>31</v>
       </c>
       <c r="J64" t="n">
-        <v>-59.75</v>
+        <v>-57.55</v>
       </c>
       <c r="K64" t="n">
-        <v>56.53</v>
+        <v>54.44</v>
       </c>
       <c r="L64" t="n">
-        <v>82.25</v>
+        <v>79.22</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>30</v>
       </c>
       <c r="J65" t="n">
-        <v>53.07</v>
+        <v>53.74</v>
       </c>
       <c r="K65" t="n">
-        <v>60</v>
+        <v>60.76</v>
       </c>
       <c r="L65" t="n">
-        <v>80.09999999999999</v>
+        <v>81.11</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>29</v>
       </c>
       <c r="J66" t="n">
-        <v>30.57</v>
+        <v>32.34</v>
       </c>
       <c r="K66" t="n">
-        <v>49.02</v>
+        <v>51.86</v>
       </c>
       <c r="L66" t="n">
-        <v>57.77</v>
+        <v>61.11</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>29</v>
       </c>
       <c r="J67" t="n">
-        <v>-85.87</v>
+        <v>-85.53</v>
       </c>
       <c r="K67" t="n">
-        <v>-12.55</v>
+        <v>-12.5</v>
       </c>
       <c r="L67" t="n">
-        <v>86.78</v>
+        <v>86.44</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>31</v>
       </c>
       <c r="J68" t="n">
-        <v>-101.75</v>
+        <v>-101.97</v>
       </c>
       <c r="K68" t="n">
-        <v>13.17</v>
+        <v>13.2</v>
       </c>
       <c r="L68" t="n">
-        <v>102.6</v>
+        <v>102.82</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>-100.9</v>
+        <v>-97.41</v>
       </c>
       <c r="K69" t="n">
-        <v>-138.42</v>
+        <v>-133.64</v>
       </c>
       <c r="L69" t="n">
-        <v>171.29</v>
+        <v>165.38</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>-73.65000000000001</v>
+        <v>-74.8</v>
       </c>
       <c r="K70" t="n">
-        <v>83.87</v>
+        <v>85.19</v>
       </c>
       <c r="L70" t="n">
-        <v>111.62</v>
+        <v>113.36</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>28</v>
       </c>
       <c r="J71" t="n">
-        <v>43.57</v>
+        <v>43.45</v>
       </c>
       <c r="K71" t="n">
-        <v>-164.31</v>
+        <v>-163.85</v>
       </c>
       <c r="L71" t="n">
-        <v>169.99</v>
+        <v>169.51</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>29</v>
       </c>
       <c r="J72" t="n">
-        <v>-137.12</v>
+        <v>-133.17</v>
       </c>
       <c r="K72" t="n">
-        <v>155.29</v>
+        <v>150.82</v>
       </c>
       <c r="L72" t="n">
-        <v>207.17</v>
+        <v>201.2</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>-108.54</v>
+        <v>-111.39</v>
       </c>
       <c r="K73" t="n">
-        <v>-100.02</v>
+        <v>-102.64</v>
       </c>
       <c r="L73" t="n">
-        <v>147.59</v>
+        <v>151.47</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>29</v>
       </c>
       <c r="J74" t="n">
-        <v>9.390000000000001</v>
+        <v>9.33</v>
       </c>
       <c r="K74" t="n">
-        <v>-52.83</v>
+        <v>-52.48</v>
       </c>
       <c r="L74" t="n">
-        <v>53.66</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>31</v>
       </c>
       <c r="J75" t="n">
-        <v>54.09</v>
+        <v>52.79</v>
       </c>
       <c r="K75" t="n">
-        <v>-5.24</v>
+        <v>-5.12</v>
       </c>
       <c r="L75" t="n">
-        <v>54.34</v>
+        <v>53.04</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>29</v>
       </c>
       <c r="J76" t="n">
-        <v>29.41</v>
+        <v>30.1</v>
       </c>
       <c r="K76" t="n">
-        <v>24.22</v>
+        <v>24.79</v>
       </c>
       <c r="L76" t="n">
-        <v>38.1</v>
+        <v>38.99</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>27</v>
       </c>
       <c r="J77" t="n">
-        <v>-67.5</v>
+        <v>-66.5</v>
       </c>
       <c r="K77" t="n">
-        <v>25.12</v>
+        <v>24.75</v>
       </c>
       <c r="L77" t="n">
-        <v>72.02</v>
+        <v>70.95999999999999</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>30</v>
       </c>
       <c r="J78" t="n">
-        <v>31.95</v>
+        <v>31.23</v>
       </c>
       <c r="K78" t="n">
-        <v>-66.69</v>
+        <v>-65.19</v>
       </c>
       <c r="L78" t="n">
-        <v>73.95</v>
+        <v>72.28</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>28</v>
       </c>
       <c r="J79" t="n">
-        <v>-51.4</v>
+        <v>-51.41</v>
       </c>
       <c r="K79" t="n">
-        <v>25.27</v>
+        <v>25.28</v>
       </c>
       <c r="L79" t="n">
-        <v>57.28</v>
+        <v>57.29</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>31</v>
       </c>
       <c r="J80" t="n">
-        <v>-48.44</v>
+        <v>-50.77</v>
       </c>
       <c r="K80" t="n">
-        <v>-30.9</v>
+        <v>-32.38</v>
       </c>
       <c r="L80" t="n">
-        <v>57.46</v>
+        <v>60.21</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>29</v>
       </c>
       <c r="J81" t="n">
-        <v>-89.08</v>
+        <v>-85.93000000000001</v>
       </c>
       <c r="K81" t="n">
-        <v>69.23</v>
+        <v>66.78</v>
       </c>
       <c r="L81" t="n">
-        <v>112.82</v>
+        <v>108.83</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>26</v>
       </c>
       <c r="J82" t="n">
-        <v>-56.35</v>
+        <v>-54.68</v>
       </c>
       <c r="K82" t="n">
-        <v>103.22</v>
+        <v>100.17</v>
       </c>
       <c r="L82" t="n">
-        <v>117.6</v>
+        <v>114.12</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>26</v>
       </c>
       <c r="J83" t="n">
-        <v>80.13</v>
+        <v>81.88</v>
       </c>
       <c r="K83" t="n">
-        <v>48.73</v>
+        <v>49.79</v>
       </c>
       <c r="L83" t="n">
-        <v>93.78</v>
+        <v>95.83</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>27</v>
       </c>
       <c r="J84" t="n">
-        <v>-45.34</v>
+        <v>-48.63</v>
       </c>
       <c r="K84" t="n">
-        <v>51.94</v>
+        <v>55.71</v>
       </c>
       <c r="L84" t="n">
-        <v>68.95</v>
+        <v>73.95</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>25</v>
       </c>
       <c r="J85" t="n">
-        <v>-119.74</v>
+        <v>-119.83</v>
       </c>
       <c r="K85" t="n">
-        <v>26.16</v>
+        <v>26.18</v>
       </c>
       <c r="L85" t="n">
-        <v>122.57</v>
+        <v>122.65</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>28</v>
       </c>
       <c r="J86" t="n">
-        <v>11.98</v>
+        <v>11.58</v>
       </c>
       <c r="K86" t="n">
-        <v>-213.37</v>
+        <v>-206.13</v>
       </c>
       <c r="L86" t="n">
-        <v>213.71</v>
+        <v>206.46</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>29</v>
       </c>
       <c r="J87" t="n">
-        <v>-73.67</v>
+        <v>-70.51000000000001</v>
       </c>
       <c r="K87" t="n">
-        <v>-221.97</v>
+        <v>-212.46</v>
       </c>
       <c r="L87" t="n">
-        <v>233.88</v>
+        <v>223.86</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>-10.72</v>
+        <v>-11.06</v>
       </c>
       <c r="K88" t="n">
-        <v>129.8</v>
+        <v>133.96</v>
       </c>
       <c r="L88" t="n">
-        <v>130.24</v>
+        <v>134.41</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-05-25.xlsx
+++ b/output/2024-05-25.xlsx
@@ -640,13 +640,13 @@
         <v>31</v>
       </c>
       <c r="J14" t="n">
-        <v>-23.67</v>
+        <v>-24.53</v>
       </c>
       <c r="K14" t="n">
-        <v>-21.8</v>
+        <v>-22.59</v>
       </c>
       <c r="L14" t="n">
-        <v>32.18</v>
+        <v>33.35</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>26</v>
       </c>
       <c r="J15" t="n">
-        <v>27.68</v>
+        <v>26.64</v>
       </c>
       <c r="K15" t="n">
-        <v>-55.08</v>
+        <v>-53.03</v>
       </c>
       <c r="L15" t="n">
-        <v>61.65</v>
+        <v>59.35</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>28</v>
       </c>
       <c r="J16" t="n">
-        <v>-21.64</v>
+        <v>-23.44</v>
       </c>
       <c r="K16" t="n">
-        <v>29.62</v>
+        <v>32.09</v>
       </c>
       <c r="L16" t="n">
-        <v>36.68</v>
+        <v>39.74</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>27</v>
       </c>
       <c r="J17" t="n">
-        <v>-56.81</v>
+        <v>-56.74</v>
       </c>
       <c r="K17" t="n">
-        <v>22.42</v>
+        <v>22.4</v>
       </c>
       <c r="L17" t="n">
-        <v>61.07</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>28</v>
       </c>
       <c r="J18" t="n">
-        <v>53.65</v>
+        <v>53.8</v>
       </c>
       <c r="K18" t="n">
-        <v>-19.36</v>
+        <v>-19.41</v>
       </c>
       <c r="L18" t="n">
-        <v>57.04</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>42.7</v>
+        <v>43.41</v>
       </c>
       <c r="K19" t="n">
-        <v>37.16</v>
+        <v>37.77</v>
       </c>
       <c r="L19" t="n">
-        <v>56.61</v>
+        <v>57.54</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>30</v>
       </c>
       <c r="J20" t="n">
-        <v>66.98</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>26.88</v>
+        <v>27.25</v>
       </c>
       <c r="L20" t="n">
-        <v>72.17</v>
+        <v>73.16</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>26</v>
       </c>
       <c r="J21" t="n">
-        <v>5.13</v>
+        <v>5.01</v>
       </c>
       <c r="K21" t="n">
-        <v>115.96</v>
+        <v>113.19</v>
       </c>
       <c r="L21" t="n">
-        <v>116.08</v>
+        <v>113.3</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>27</v>
       </c>
       <c r="J22" t="n">
-        <v>60.94</v>
+        <v>61.71</v>
       </c>
       <c r="K22" t="n">
-        <v>54.07</v>
+        <v>54.76</v>
       </c>
       <c r="L22" t="n">
-        <v>81.47</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>31</v>
       </c>
       <c r="J23" t="n">
-        <v>57.41</v>
+        <v>58.56</v>
       </c>
       <c r="K23" t="n">
-        <v>66.58</v>
+        <v>67.91</v>
       </c>
       <c r="L23" t="n">
-        <v>87.92</v>
+        <v>89.67</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>27</v>
       </c>
       <c r="J24" t="n">
-        <v>-108.85</v>
+        <v>-109.07</v>
       </c>
       <c r="K24" t="n">
-        <v>46.16</v>
+        <v>46.25</v>
       </c>
       <c r="L24" t="n">
-        <v>118.23</v>
+        <v>118.47</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>31</v>
       </c>
       <c r="J25" t="n">
-        <v>6.41</v>
+        <v>6.35</v>
       </c>
       <c r="K25" t="n">
-        <v>-108.71</v>
+        <v>-107.74</v>
       </c>
       <c r="L25" t="n">
-        <v>108.9</v>
+        <v>107.93</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>31</v>
       </c>
       <c r="J26" t="n">
-        <v>89.27</v>
+        <v>94.53</v>
       </c>
       <c r="K26" t="n">
-        <v>63.19</v>
+        <v>66.92</v>
       </c>
       <c r="L26" t="n">
-        <v>109.37</v>
+        <v>115.82</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>29</v>
       </c>
       <c r="J27" t="n">
-        <v>-162.49</v>
+        <v>-161.37</v>
       </c>
       <c r="K27" t="n">
-        <v>-5.85</v>
+        <v>-5.81</v>
       </c>
       <c r="L27" t="n">
-        <v>162.6</v>
+        <v>161.48</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>29</v>
       </c>
       <c r="J28" t="n">
-        <v>-52.38</v>
+        <v>-56.3</v>
       </c>
       <c r="K28" t="n">
-        <v>-92.81999999999999</v>
+        <v>-99.77</v>
       </c>
       <c r="L28" t="n">
-        <v>106.58</v>
+        <v>114.56</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>26</v>
       </c>
       <c r="J29" t="n">
-        <v>-9.9</v>
+        <v>-10.07</v>
       </c>
       <c r="K29" t="n">
-        <v>37.34</v>
+        <v>37.98</v>
       </c>
       <c r="L29" t="n">
-        <v>38.63</v>
+        <v>39.29</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>26</v>
       </c>
       <c r="J30" t="n">
-        <v>-49.52</v>
+        <v>-47.99</v>
       </c>
       <c r="K30" t="n">
-        <v>-38.44</v>
+        <v>-37.25</v>
       </c>
       <c r="L30" t="n">
-        <v>62.69</v>
+        <v>60.75</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>-16.83</v>
+        <v>-17.58</v>
       </c>
       <c r="K31" t="n">
-        <v>-31.43</v>
+        <v>-32.82</v>
       </c>
       <c r="L31" t="n">
-        <v>35.66</v>
+        <v>37.23</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>30</v>
       </c>
       <c r="J32" t="n">
-        <v>-25.9</v>
+        <v>-26.18</v>
       </c>
       <c r="K32" t="n">
-        <v>-42.76</v>
+        <v>-43.23</v>
       </c>
       <c r="L32" t="n">
-        <v>50</v>
+        <v>50.54</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>25</v>
       </c>
       <c r="J33" t="n">
-        <v>31.16</v>
+        <v>32.2</v>
       </c>
       <c r="K33" t="n">
-        <v>36.98</v>
+        <v>38.21</v>
       </c>
       <c r="L33" t="n">
-        <v>48.36</v>
+        <v>49.96</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>26</v>
       </c>
       <c r="J34" t="n">
-        <v>72.08</v>
+        <v>68.61</v>
       </c>
       <c r="K34" t="n">
-        <v>43</v>
+        <v>40.93</v>
       </c>
       <c r="L34" t="n">
-        <v>83.93000000000001</v>
+        <v>79.89</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>30</v>
       </c>
       <c r="J35" t="n">
-        <v>-25.18</v>
+        <v>-24.06</v>
       </c>
       <c r="K35" t="n">
-        <v>100.58</v>
+        <v>96.09</v>
       </c>
       <c r="L35" t="n">
-        <v>103.68</v>
+        <v>99.06</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>30</v>
       </c>
       <c r="J36" t="n">
-        <v>67.8</v>
+        <v>66.2</v>
       </c>
       <c r="K36" t="n">
-        <v>-55.35</v>
+        <v>-54.05</v>
       </c>
       <c r="L36" t="n">
-        <v>87.52</v>
+        <v>85.47</v>
       </c>
     </row>
     <row r="37">
@@ -1609,10 +1609,10 @@
         <v>9.390000000000001</v>
       </c>
       <c r="K37" t="n">
-        <v>-72.56999999999999</v>
+        <v>-72.62</v>
       </c>
       <c r="L37" t="n">
-        <v>73.18000000000001</v>
+        <v>73.23</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>27</v>
       </c>
       <c r="J38" t="n">
-        <v>25.93</v>
+        <v>24.92</v>
       </c>
       <c r="K38" t="n">
-        <v>-133.76</v>
+        <v>-128.56</v>
       </c>
       <c r="L38" t="n">
-        <v>136.25</v>
+        <v>130.95</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>27</v>
       </c>
       <c r="J39" t="n">
-        <v>-126.43</v>
+        <v>-122.32</v>
       </c>
       <c r="K39" t="n">
-        <v>17.19</v>
+        <v>16.63</v>
       </c>
       <c r="L39" t="n">
-        <v>127.6</v>
+        <v>123.45</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>40.35</v>
+        <v>38.37</v>
       </c>
       <c r="K40" t="n">
-        <v>-145.97</v>
+        <v>-138.82</v>
       </c>
       <c r="L40" t="n">
-        <v>151.45</v>
+        <v>144.02</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>27</v>
       </c>
       <c r="J41" t="n">
-        <v>100.27</v>
+        <v>107.78</v>
       </c>
       <c r="K41" t="n">
-        <v>19.62</v>
+        <v>21.09</v>
       </c>
       <c r="L41" t="n">
-        <v>102.18</v>
+        <v>109.82</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>25</v>
       </c>
       <c r="J42" t="n">
-        <v>180.36</v>
+        <v>172.65</v>
       </c>
       <c r="K42" t="n">
-        <v>-155.05</v>
+        <v>-148.42</v>
       </c>
       <c r="L42" t="n">
-        <v>237.85</v>
+        <v>227.68</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>28</v>
       </c>
       <c r="J43" t="n">
-        <v>-91.55</v>
+        <v>-98.20999999999999</v>
       </c>
       <c r="K43" t="n">
-        <v>-43.83</v>
+        <v>-47.02</v>
       </c>
       <c r="L43" t="n">
-        <v>101.5</v>
+        <v>108.88</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>31</v>
       </c>
       <c r="J44" t="n">
-        <v>21.88</v>
+        <v>21.72</v>
       </c>
       <c r="K44" t="n">
-        <v>-30.07</v>
+        <v>-29.86</v>
       </c>
       <c r="L44" t="n">
-        <v>37.19</v>
+        <v>36.92</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>29</v>
       </c>
       <c r="J45" t="n">
-        <v>-29.35</v>
+        <v>-29.28</v>
       </c>
       <c r="K45" t="n">
-        <v>39.8</v>
+        <v>39.7</v>
       </c>
       <c r="L45" t="n">
-        <v>49.45</v>
+        <v>49.33</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>28</v>
       </c>
       <c r="J46" t="n">
-        <v>25.94</v>
+        <v>25.06</v>
       </c>
       <c r="K46" t="n">
-        <v>51.7</v>
+        <v>49.94</v>
       </c>
       <c r="L46" t="n">
-        <v>57.84</v>
+        <v>55.88</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>-35.89</v>
+        <v>-39.32</v>
       </c>
       <c r="K47" t="n">
-        <v>-14.22</v>
+        <v>-15.58</v>
       </c>
       <c r="L47" t="n">
-        <v>38.6</v>
+        <v>42.29</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>27</v>
       </c>
       <c r="J48" t="n">
-        <v>-70.58</v>
+        <v>-68.86</v>
       </c>
       <c r="K48" t="n">
-        <v>27.18</v>
+        <v>26.52</v>
       </c>
       <c r="L48" t="n">
-        <v>75.63</v>
+        <v>73.79000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>30</v>
       </c>
       <c r="J49" t="n">
-        <v>-15.81</v>
+        <v>-17.4</v>
       </c>
       <c r="K49" t="n">
-        <v>-32.64</v>
+        <v>-35.93</v>
       </c>
       <c r="L49" t="n">
-        <v>36.27</v>
+        <v>39.92</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>27</v>
       </c>
       <c r="J50" t="n">
-        <v>81.40000000000001</v>
+        <v>82.38</v>
       </c>
       <c r="K50" t="n">
-        <v>-11.26</v>
+        <v>-11.39</v>
       </c>
       <c r="L50" t="n">
-        <v>82.18000000000001</v>
+        <v>83.17</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>30</v>
       </c>
       <c r="J51" t="n">
-        <v>38.62</v>
+        <v>38.06</v>
       </c>
       <c r="K51" t="n">
-        <v>80.37</v>
+        <v>79.2</v>
       </c>
       <c r="L51" t="n">
-        <v>89.17</v>
+        <v>87.87</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>26</v>
       </c>
       <c r="J52" t="n">
-        <v>40.98</v>
+        <v>41.32</v>
       </c>
       <c r="K52" t="n">
-        <v>-74.29000000000001</v>
+        <v>-74.90000000000001</v>
       </c>
       <c r="L52" t="n">
-        <v>84.84999999999999</v>
+        <v>85.54000000000001</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>26</v>
       </c>
       <c r="J53" t="n">
-        <v>91.02</v>
+        <v>88.42</v>
       </c>
       <c r="K53" t="n">
-        <v>-114.18</v>
+        <v>-110.92</v>
       </c>
       <c r="L53" t="n">
-        <v>146.02</v>
+        <v>141.85</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>30</v>
       </c>
       <c r="J54" t="n">
-        <v>-37.04</v>
+        <v>-39.07</v>
       </c>
       <c r="K54" t="n">
-        <v>68.64</v>
+        <v>72.39</v>
       </c>
       <c r="L54" t="n">
-        <v>77.98999999999999</v>
+        <v>82.26000000000001</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>31</v>
       </c>
       <c r="J55" t="n">
-        <v>95.31</v>
+        <v>94.97</v>
       </c>
       <c r="K55" t="n">
-        <v>-51.29</v>
+        <v>-51.11</v>
       </c>
       <c r="L55" t="n">
-        <v>108.23</v>
+        <v>107.85</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>30</v>
       </c>
       <c r="J56" t="n">
-        <v>-62.86</v>
+        <v>-64.22</v>
       </c>
       <c r="K56" t="n">
-        <v>125.9</v>
+        <v>128.61</v>
       </c>
       <c r="L56" t="n">
-        <v>140.72</v>
+        <v>143.75</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>31</v>
       </c>
       <c r="J57" t="n">
-        <v>128.01</v>
+        <v>131.65</v>
       </c>
       <c r="K57" t="n">
-        <v>28.54</v>
+        <v>29.35</v>
       </c>
       <c r="L57" t="n">
-        <v>131.16</v>
+        <v>134.88</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>26</v>
       </c>
       <c r="J58" t="n">
-        <v>93.76000000000001</v>
+        <v>99.27</v>
       </c>
       <c r="K58" t="n">
-        <v>80.23999999999999</v>
+        <v>84.95</v>
       </c>
       <c r="L58" t="n">
-        <v>123.4</v>
+        <v>130.65</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>-1.36</v>
+        <v>-1.3</v>
       </c>
       <c r="K59" t="n">
-        <v>-70.33</v>
+        <v>-67.23</v>
       </c>
       <c r="L59" t="n">
-        <v>70.34</v>
+        <v>67.23999999999999</v>
       </c>
     </row>
     <row r="60">
@@ -2575,10 +2575,10 @@
         <v>1.42</v>
       </c>
       <c r="K60" t="n">
-        <v>40.18</v>
+        <v>40.31</v>
       </c>
       <c r="L60" t="n">
-        <v>40.21</v>
+        <v>40.33</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>28</v>
       </c>
       <c r="J61" t="n">
-        <v>17.24</v>
+        <v>18.43</v>
       </c>
       <c r="K61" t="n">
-        <v>28.73</v>
+        <v>30.71</v>
       </c>
       <c r="L61" t="n">
-        <v>33.51</v>
+        <v>35.82</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>31</v>
       </c>
       <c r="J62" t="n">
-        <v>-54.36</v>
+        <v>-51.83</v>
       </c>
       <c r="K62" t="n">
-        <v>-60.62</v>
+        <v>-57.8</v>
       </c>
       <c r="L62" t="n">
-        <v>81.42</v>
+        <v>77.63</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>31</v>
       </c>
       <c r="J63" t="n">
-        <v>4.29</v>
+        <v>4.03</v>
       </c>
       <c r="K63" t="n">
-        <v>-86.45999999999999</v>
+        <v>-81.33</v>
       </c>
       <c r="L63" t="n">
-        <v>86.56</v>
+        <v>81.43000000000001</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>31</v>
       </c>
       <c r="J64" t="n">
-        <v>-57.55</v>
+        <v>-55.03</v>
       </c>
       <c r="K64" t="n">
-        <v>54.44</v>
+        <v>52.06</v>
       </c>
       <c r="L64" t="n">
-        <v>79.22</v>
+        <v>75.75</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>30</v>
       </c>
       <c r="J65" t="n">
-        <v>53.74</v>
+        <v>54.51</v>
       </c>
       <c r="K65" t="n">
-        <v>60.76</v>
+        <v>61.62</v>
       </c>
       <c r="L65" t="n">
-        <v>81.11</v>
+        <v>82.27</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>29</v>
       </c>
       <c r="J66" t="n">
-        <v>32.34</v>
+        <v>34.36</v>
       </c>
       <c r="K66" t="n">
-        <v>51.86</v>
+        <v>55.1</v>
       </c>
       <c r="L66" t="n">
-        <v>61.11</v>
+        <v>64.94</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>29</v>
       </c>
       <c r="J67" t="n">
-        <v>-85.53</v>
+        <v>-85.15000000000001</v>
       </c>
       <c r="K67" t="n">
-        <v>-12.5</v>
+        <v>-12.44</v>
       </c>
       <c r="L67" t="n">
-        <v>86.44</v>
+        <v>86.05</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>31</v>
       </c>
       <c r="J68" t="n">
-        <v>-101.97</v>
+        <v>-102.21</v>
       </c>
       <c r="K68" t="n">
-        <v>13.2</v>
+        <v>13.23</v>
       </c>
       <c r="L68" t="n">
-        <v>102.82</v>
+        <v>103.07</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>-97.41</v>
+        <v>-93.43000000000001</v>
       </c>
       <c r="K69" t="n">
-        <v>-133.64</v>
+        <v>-128.18</v>
       </c>
       <c r="L69" t="n">
-        <v>165.38</v>
+        <v>158.62</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>-74.8</v>
+        <v>-76.11</v>
       </c>
       <c r="K70" t="n">
-        <v>85.19</v>
+        <v>86.68000000000001</v>
       </c>
       <c r="L70" t="n">
-        <v>113.36</v>
+        <v>115.36</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>28</v>
       </c>
       <c r="J71" t="n">
-        <v>43.45</v>
+        <v>43.31</v>
       </c>
       <c r="K71" t="n">
-        <v>-163.85</v>
+        <v>-163.32</v>
       </c>
       <c r="L71" t="n">
-        <v>169.51</v>
+        <v>168.96</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>29</v>
       </c>
       <c r="J72" t="n">
-        <v>-133.17</v>
+        <v>-128.66</v>
       </c>
       <c r="K72" t="n">
-        <v>150.82</v>
+        <v>145.7</v>
       </c>
       <c r="L72" t="n">
-        <v>201.2</v>
+        <v>194.37</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>-111.39</v>
+        <v>-114.65</v>
       </c>
       <c r="K73" t="n">
-        <v>-102.64</v>
+        <v>-105.65</v>
       </c>
       <c r="L73" t="n">
-        <v>151.47</v>
+        <v>155.9</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>29</v>
       </c>
       <c r="J74" t="n">
-        <v>9.33</v>
+        <v>9.26</v>
       </c>
       <c r="K74" t="n">
-        <v>-52.48</v>
+        <v>-52.07</v>
       </c>
       <c r="L74" t="n">
-        <v>53.3</v>
+        <v>52.89</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>31</v>
       </c>
       <c r="J75" t="n">
-        <v>52.79</v>
+        <v>51.31</v>
       </c>
       <c r="K75" t="n">
-        <v>-5.12</v>
+        <v>-4.97</v>
       </c>
       <c r="L75" t="n">
-        <v>53.04</v>
+        <v>51.55</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>29</v>
       </c>
       <c r="J76" t="n">
-        <v>30.1</v>
+        <v>30.89</v>
       </c>
       <c r="K76" t="n">
-        <v>24.79</v>
+        <v>25.44</v>
       </c>
       <c r="L76" t="n">
-        <v>38.99</v>
+        <v>40.01</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>27</v>
       </c>
       <c r="J77" t="n">
-        <v>-66.5</v>
+        <v>-65.37</v>
       </c>
       <c r="K77" t="n">
-        <v>24.75</v>
+        <v>24.33</v>
       </c>
       <c r="L77" t="n">
-        <v>70.95999999999999</v>
+        <v>69.75</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>30</v>
       </c>
       <c r="J78" t="n">
-        <v>31.23</v>
+        <v>30.41</v>
       </c>
       <c r="K78" t="n">
-        <v>-65.19</v>
+        <v>-63.47</v>
       </c>
       <c r="L78" t="n">
-        <v>72.28</v>
+        <v>70.38</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>28</v>
       </c>
       <c r="J79" t="n">
-        <v>-51.41</v>
+        <v>-51.43</v>
       </c>
       <c r="K79" t="n">
         <v>25.28</v>
       </c>
       <c r="L79" t="n">
-        <v>57.29</v>
+        <v>57.31</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>31</v>
       </c>
       <c r="J80" t="n">
-        <v>-50.77</v>
+        <v>-53.42</v>
       </c>
       <c r="K80" t="n">
-        <v>-32.38</v>
+        <v>-34.07</v>
       </c>
       <c r="L80" t="n">
-        <v>60.21</v>
+        <v>63.36</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>29</v>
       </c>
       <c r="J81" t="n">
-        <v>-85.93000000000001</v>
+        <v>-82.33</v>
       </c>
       <c r="K81" t="n">
-        <v>66.78</v>
+        <v>63.98</v>
       </c>
       <c r="L81" t="n">
-        <v>108.83</v>
+        <v>104.26</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>26</v>
       </c>
       <c r="J82" t="n">
-        <v>-54.68</v>
+        <v>-52.78</v>
       </c>
       <c r="K82" t="n">
-        <v>100.17</v>
+        <v>96.69</v>
       </c>
       <c r="L82" t="n">
-        <v>114.12</v>
+        <v>110.15</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>26</v>
       </c>
       <c r="J83" t="n">
-        <v>81.88</v>
+        <v>83.88</v>
       </c>
       <c r="K83" t="n">
-        <v>49.79</v>
+        <v>51.01</v>
       </c>
       <c r="L83" t="n">
-        <v>95.83</v>
+        <v>98.17</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>27</v>
       </c>
       <c r="J84" t="n">
-        <v>-48.63</v>
+        <v>-52.39</v>
       </c>
       <c r="K84" t="n">
-        <v>55.71</v>
+        <v>60.02</v>
       </c>
       <c r="L84" t="n">
-        <v>73.95</v>
+        <v>79.67</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>25</v>
       </c>
       <c r="J85" t="n">
-        <v>-119.83</v>
+        <v>-119.92</v>
       </c>
       <c r="K85" t="n">
-        <v>26.18</v>
+        <v>26.2</v>
       </c>
       <c r="L85" t="n">
-        <v>122.65</v>
+        <v>122.75</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>28</v>
       </c>
       <c r="J86" t="n">
-        <v>11.58</v>
+        <v>11.11</v>
       </c>
       <c r="K86" t="n">
-        <v>-206.13</v>
+        <v>-197.85</v>
       </c>
       <c r="L86" t="n">
-        <v>206.46</v>
+        <v>198.16</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>29</v>
       </c>
       <c r="J87" t="n">
-        <v>-70.51000000000001</v>
+        <v>-66.91</v>
       </c>
       <c r="K87" t="n">
-        <v>-212.46</v>
+        <v>-201.6</v>
       </c>
       <c r="L87" t="n">
-        <v>223.86</v>
+        <v>212.41</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>-11.06</v>
+        <v>-11.45</v>
       </c>
       <c r="K88" t="n">
-        <v>133.96</v>
+        <v>138.71</v>
       </c>
       <c r="L88" t="n">
-        <v>134.41</v>
+        <v>139.18</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-05-25.xlsx
+++ b/output/2024-05-25.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2.09</v>
+        <v>2.16</v>
       </c>
       <c r="F14" t="n">
-        <v>7.7</v>
+        <v>4.16</v>
       </c>
       <c r="G14" t="n">
-        <v>233.6</v>
+        <v>233.9</v>
       </c>
       <c r="H14" t="n">
-        <v>17</v>
+        <v>15.3</v>
       </c>
       <c r="I14" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="J14" t="n">
-        <v>-24.53</v>
+        <v>45.13</v>
       </c>
       <c r="K14" t="n">
-        <v>-22.59</v>
+        <v>-6.12</v>
       </c>
       <c r="L14" t="n">
-        <v>33.35</v>
+        <v>45.54</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:46:34</t>
+          <t>04:47:33</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2.36</v>
+        <v>2.52</v>
       </c>
       <c r="F15" t="n">
-        <v>8.15</v>
+        <v>6.04</v>
       </c>
       <c r="G15" t="n">
-        <v>238.7</v>
+        <v>222</v>
       </c>
       <c r="H15" t="n">
-        <v>11.6</v>
+        <v>21.2</v>
       </c>
       <c r="I15" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J15" t="n">
-        <v>26.64</v>
+        <v>54.2</v>
       </c>
       <c r="K15" t="n">
-        <v>-53.03</v>
+        <v>-30.56</v>
       </c>
       <c r="L15" t="n">
-        <v>59.35</v>
+        <v>62.23</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:48:09</t>
+          <t>04:49:05</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>3.23</v>
+        <v>2.25</v>
       </c>
       <c r="F16" t="n">
-        <v>8.18</v>
+        <v>6.47</v>
       </c>
       <c r="G16" t="n">
-        <v>236.9</v>
+        <v>241.3</v>
       </c>
       <c r="H16" t="n">
-        <v>5.7</v>
+        <v>19.8</v>
       </c>
       <c r="I16" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J16" t="n">
-        <v>-23.44</v>
+        <v>-22.44</v>
       </c>
       <c r="K16" t="n">
-        <v>32.09</v>
+        <v>-43.93</v>
       </c>
       <c r="L16" t="n">
-        <v>39.74</v>
+        <v>49.33</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04:52:00</t>
+          <t>04:53:51</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="F17" t="n">
-        <v>7.3</v>
+        <v>7.02</v>
       </c>
       <c r="G17" t="n">
-        <v>234.8</v>
+        <v>241.7</v>
       </c>
       <c r="H17" t="n">
-        <v>18.8</v>
+        <v>10.8</v>
       </c>
       <c r="I17" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J17" t="n">
-        <v>-56.74</v>
+        <v>48.06</v>
       </c>
       <c r="K17" t="n">
-        <v>22.4</v>
+        <v>-33.66</v>
       </c>
       <c r="L17" t="n">
-        <v>61</v>
+        <v>58.68</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:54:33</t>
+          <t>04:55:39</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.22</v>
+        <v>2.6</v>
       </c>
       <c r="F18" t="n">
-        <v>7.91</v>
+        <v>7.39</v>
       </c>
       <c r="G18" t="n">
-        <v>228.6</v>
+        <v>239.1</v>
       </c>
       <c r="H18" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="I18" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>53.8</v>
+        <v>2.61</v>
       </c>
       <c r="K18" t="n">
-        <v>-19.41</v>
+        <v>-81.8</v>
       </c>
       <c r="L18" t="n">
-        <v>57.2</v>
+        <v>81.84999999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04:56:05</t>
+          <t>04:57:38</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>2.47</v>
+        <v>2.56</v>
       </c>
       <c r="F19" t="n">
-        <v>8</v>
+        <v>8.43</v>
       </c>
       <c r="G19" t="n">
-        <v>224.4</v>
+        <v>230.4</v>
       </c>
       <c r="H19" t="n">
-        <v>13.9</v>
+        <v>10.4</v>
       </c>
       <c r="I19" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J19" t="n">
-        <v>43.41</v>
+        <v>-25.36</v>
       </c>
       <c r="K19" t="n">
-        <v>37.77</v>
+        <v>64.43000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>57.54</v>
+        <v>69.23999999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>05:00:51</t>
+          <t>05:03:49</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>2.14</v>
+        <v>2.29</v>
       </c>
       <c r="F20" t="n">
-        <v>7.97</v>
+        <v>7.06</v>
       </c>
       <c r="G20" t="n">
-        <v>235.3</v>
+        <v>234.7</v>
       </c>
       <c r="H20" t="n">
-        <v>16.1</v>
+        <v>14.7</v>
       </c>
       <c r="I20" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J20" t="n">
-        <v>67.90000000000001</v>
+        <v>92.87</v>
       </c>
       <c r="K20" t="n">
-        <v>27.25</v>
+        <v>-11.69</v>
       </c>
       <c r="L20" t="n">
-        <v>73.16</v>
+        <v>93.61</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>05:02:39</t>
+          <t>05:05:11</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>2.4</v>
+        <v>3.33</v>
       </c>
       <c r="F21" t="n">
-        <v>7.81</v>
+        <v>8.74</v>
       </c>
       <c r="G21" t="n">
-        <v>237.3</v>
+        <v>239.4</v>
       </c>
       <c r="H21" t="n">
-        <v>18.3</v>
+        <v>13.8</v>
       </c>
       <c r="I21" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>5.01</v>
+        <v>-73.94</v>
       </c>
       <c r="K21" t="n">
-        <v>113.19</v>
+        <v>43.4</v>
       </c>
       <c r="L21" t="n">
-        <v>113.3</v>
+        <v>85.73</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05:04:38</t>
+          <t>05:07:19</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="F22" t="n">
-        <v>7.53</v>
+        <v>5.09</v>
       </c>
       <c r="G22" t="n">
-        <v>232.1</v>
+        <v>237</v>
       </c>
       <c r="H22" t="n">
-        <v>14.4</v>
+        <v>17.4</v>
       </c>
       <c r="I22" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J22" t="n">
-        <v>61.71</v>
+        <v>72.41</v>
       </c>
       <c r="K22" t="n">
-        <v>54.76</v>
+        <v>82.81</v>
       </c>
       <c r="L22" t="n">
-        <v>82.5</v>
+        <v>110</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05:10:49</t>
+          <t>05:13:02</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>2.08</v>
+        <v>2.42</v>
       </c>
       <c r="F23" t="n">
-        <v>8.19</v>
+        <v>8.07</v>
       </c>
       <c r="G23" t="n">
-        <v>248.4</v>
+        <v>227.1</v>
       </c>
       <c r="H23" t="n">
-        <v>9.6</v>
+        <v>16.4</v>
       </c>
       <c r="I23" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="J23" t="n">
-        <v>58.56</v>
+        <v>99.77</v>
       </c>
       <c r="K23" t="n">
-        <v>67.91</v>
+        <v>-77.16</v>
       </c>
       <c r="L23" t="n">
-        <v>89.67</v>
+        <v>126.12</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:12:11</t>
+          <t>05:15:24</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>2.69</v>
+        <v>2.11</v>
       </c>
       <c r="F24" t="n">
-        <v>8.029999999999999</v>
+        <v>5.37</v>
       </c>
       <c r="G24" t="n">
-        <v>253.8</v>
+        <v>243.6</v>
       </c>
       <c r="H24" t="n">
-        <v>8.199999999999999</v>
+        <v>14.8</v>
       </c>
       <c r="I24" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J24" t="n">
-        <v>-109.07</v>
+        <v>-116.39</v>
       </c>
       <c r="K24" t="n">
-        <v>46.25</v>
+        <v>25.53</v>
       </c>
       <c r="L24" t="n">
-        <v>118.47</v>
+        <v>119.16</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:14:19</t>
+          <t>05:17:16</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>2.29</v>
+        <v>2.24</v>
       </c>
       <c r="F25" t="n">
-        <v>7.75</v>
+        <v>3.86</v>
       </c>
       <c r="G25" t="n">
-        <v>228.8</v>
+        <v>242.5</v>
       </c>
       <c r="H25" t="n">
-        <v>11.2</v>
+        <v>16.4</v>
       </c>
       <c r="I25" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>6.35</v>
+        <v>-126.36</v>
       </c>
       <c r="K25" t="n">
-        <v>-107.74</v>
+        <v>-8.460000000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>107.93</v>
+        <v>126.64</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:20:02</t>
+          <t>05:22:01</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>2.31</v>
+        <v>2.51</v>
       </c>
       <c r="F26" t="n">
-        <v>7.13</v>
+        <v>6.1</v>
       </c>
       <c r="G26" t="n">
-        <v>231.4</v>
+        <v>249.7</v>
       </c>
       <c r="H26" t="n">
-        <v>15.9</v>
+        <v>14.7</v>
       </c>
       <c r="I26" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="J26" t="n">
-        <v>94.53</v>
+        <v>-211.44</v>
       </c>
       <c r="K26" t="n">
-        <v>66.92</v>
+        <v>7.57</v>
       </c>
       <c r="L26" t="n">
-        <v>115.82</v>
+        <v>211.57</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:22:24</t>
+          <t>05:23:16</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2.25</v>
+        <v>2.88</v>
       </c>
       <c r="F27" t="n">
-        <v>7.68</v>
+        <v>8.1</v>
       </c>
       <c r="G27" t="n">
-        <v>224.6</v>
+        <v>239.3</v>
       </c>
       <c r="H27" t="n">
-        <v>14.3</v>
+        <v>13.9</v>
       </c>
       <c r="I27" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J27" t="n">
-        <v>-161.37</v>
+        <v>-44.95</v>
       </c>
       <c r="K27" t="n">
-        <v>-5.81</v>
+        <v>186.1</v>
       </c>
       <c r="L27" t="n">
-        <v>161.48</v>
+        <v>191.45</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:24:17</t>
+          <t>05:25:41</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.33</v>
+        <v>3.35</v>
       </c>
       <c r="F28" t="n">
-        <v>7.63</v>
+        <v>6.16</v>
       </c>
       <c r="G28" t="n">
-        <v>246.8</v>
+        <v>254.1</v>
       </c>
       <c r="H28" t="n">
-        <v>14.3</v>
+        <v>14.6</v>
       </c>
       <c r="I28" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J28" t="n">
-        <v>-56.3</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>-99.77</v>
+        <v>-126.56</v>
       </c>
       <c r="L28" t="n">
-        <v>114.56</v>
+        <v>146.18</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:33:38</t>
+          <t>05:33:54</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>2.24</v>
+        <v>2.34</v>
       </c>
       <c r="F29" t="n">
-        <v>7.87</v>
+        <v>8.74</v>
       </c>
       <c r="G29" t="n">
-        <v>241.4</v>
+        <v>238</v>
       </c>
       <c r="H29" t="n">
-        <v>21.7</v>
+        <v>16.7</v>
       </c>
       <c r="I29" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>-10.07</v>
+        <v>-30.25</v>
       </c>
       <c r="K29" t="n">
-        <v>37.98</v>
+        <v>-56.86</v>
       </c>
       <c r="L29" t="n">
-        <v>39.29</v>
+        <v>64.40000000000001</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:36:16</t>
+          <t>05:35:53</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2.9</v>
+        <v>2.13</v>
       </c>
       <c r="F30" t="n">
-        <v>7.68</v>
+        <v>5.48</v>
       </c>
       <c r="G30" t="n">
-        <v>238</v>
+        <v>237.4</v>
       </c>
       <c r="H30" t="n">
-        <v>16.7</v>
+        <v>7.6</v>
       </c>
       <c r="I30" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J30" t="n">
-        <v>-47.99</v>
+        <v>-45.14</v>
       </c>
       <c r="K30" t="n">
-        <v>-37.25</v>
+        <v>-14.53</v>
       </c>
       <c r="L30" t="n">
-        <v>60.75</v>
+        <v>47.42</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:38:13</t>
+          <t>05:37:05</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.43</v>
+        <v>3.34</v>
       </c>
       <c r="F31" t="n">
-        <v>7.13</v>
+        <v>6.05</v>
       </c>
       <c r="G31" t="n">
-        <v>235.2</v>
+        <v>238.5</v>
       </c>
       <c r="H31" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="I31" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J31" t="n">
-        <v>-17.58</v>
+        <v>-28.51</v>
       </c>
       <c r="K31" t="n">
-        <v>-32.82</v>
+        <v>-46.58</v>
       </c>
       <c r="L31" t="n">
-        <v>37.23</v>
+        <v>54.61</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:42:02</t>
+          <t>05:41:54</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>2.65</v>
+        <v>2.42</v>
       </c>
       <c r="F32" t="n">
-        <v>7.64</v>
+        <v>8.74</v>
       </c>
       <c r="G32" t="n">
-        <v>237.7</v>
+        <v>237.3</v>
       </c>
       <c r="H32" t="n">
-        <v>5.6</v>
+        <v>12.2</v>
       </c>
       <c r="I32" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>-26.18</v>
+        <v>-23.8</v>
       </c>
       <c r="K32" t="n">
-        <v>-43.23</v>
+        <v>50.71</v>
       </c>
       <c r="L32" t="n">
-        <v>50.54</v>
+        <v>56.01</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:44:01</t>
+          <t>05:43:15</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>2.43</v>
+        <v>2.58</v>
       </c>
       <c r="F33" t="n">
-        <v>8.59</v>
+        <v>7.81</v>
       </c>
       <c r="G33" t="n">
-        <v>237.3</v>
+        <v>233.1</v>
       </c>
       <c r="H33" t="n">
-        <v>12.2</v>
+        <v>13.9</v>
       </c>
       <c r="I33" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J33" t="n">
-        <v>32.2</v>
+        <v>76.72</v>
       </c>
       <c r="K33" t="n">
-        <v>38.21</v>
+        <v>45.48</v>
       </c>
       <c r="L33" t="n">
-        <v>49.96</v>
+        <v>89.18000000000001</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:45:13</t>
+          <t>05:44:34</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="F34" t="n">
-        <v>7.37</v>
+        <v>5.54</v>
       </c>
       <c r="G34" t="n">
-        <v>238.5</v>
+        <v>245.3</v>
       </c>
       <c r="H34" t="n">
-        <v>14.3</v>
+        <v>12.5</v>
       </c>
       <c r="I34" t="n">
         <v>26</v>
       </c>
       <c r="J34" t="n">
-        <v>68.61</v>
+        <v>-49.9</v>
       </c>
       <c r="K34" t="n">
-        <v>40.93</v>
+        <v>-30.73</v>
       </c>
       <c r="L34" t="n">
-        <v>79.89</v>
+        <v>58.6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:50:02</t>
+          <t>05:49:57</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>2.51</v>
+        <v>2.97</v>
       </c>
       <c r="F35" t="n">
-        <v>8.19</v>
+        <v>8.74</v>
       </c>
       <c r="G35" t="n">
-        <v>245.3</v>
+        <v>235.3</v>
       </c>
       <c r="H35" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="I35" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>-24.06</v>
+        <v>87.78</v>
       </c>
       <c r="K35" t="n">
-        <v>96.09</v>
+        <v>-82.8</v>
       </c>
       <c r="L35" t="n">
-        <v>99.06</v>
+        <v>120.67</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:51:23</t>
+          <t>05:51:29</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2.47</v>
+        <v>2.36</v>
       </c>
       <c r="F36" t="n">
-        <v>7.48</v>
+        <v>6.48</v>
       </c>
       <c r="G36" t="n">
-        <v>239.7</v>
+        <v>245.8</v>
       </c>
       <c r="H36" t="n">
-        <v>14.3</v>
+        <v>11.5</v>
       </c>
       <c r="I36" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="J36" t="n">
-        <v>66.2</v>
+        <v>-77.31999999999999</v>
       </c>
       <c r="K36" t="n">
-        <v>-54.05</v>
+        <v>20.3</v>
       </c>
       <c r="L36" t="n">
-        <v>85.47</v>
+        <v>79.94</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:52:41</t>
+          <t>05:53:34</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>2.36</v>
+        <v>2.15</v>
       </c>
       <c r="F37" t="n">
-        <v>8.039999999999999</v>
+        <v>6.34</v>
       </c>
       <c r="G37" t="n">
-        <v>245.8</v>
+        <v>232</v>
       </c>
       <c r="H37" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="I37" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>9.390000000000001</v>
+        <v>19.81</v>
       </c>
       <c r="K37" t="n">
-        <v>-72.62</v>
+        <v>-115.7</v>
       </c>
       <c r="L37" t="n">
-        <v>73.23</v>
+        <v>117.38</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05:58:05</t>
+          <t>05:58:22</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
       <c r="F38" t="n">
-        <v>7.31</v>
+        <v>7.05</v>
       </c>
       <c r="G38" t="n">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="H38" t="n">
-        <v>13.6</v>
+        <v>6.3</v>
       </c>
       <c r="I38" t="n">
         <v>27</v>
       </c>
       <c r="J38" t="n">
-        <v>24.92</v>
+        <v>100.47</v>
       </c>
       <c r="K38" t="n">
-        <v>-128.56</v>
+        <v>-131.06</v>
       </c>
       <c r="L38" t="n">
-        <v>130.95</v>
+        <v>165.14</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>05:59:37</t>
+          <t>06:00:10</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>2.22</v>
+        <v>2.54</v>
       </c>
       <c r="F39" t="n">
-        <v>8.26</v>
+        <v>5.15</v>
       </c>
       <c r="G39" t="n">
-        <v>238</v>
+        <v>242.5</v>
       </c>
       <c r="H39" t="n">
-        <v>6.3</v>
+        <v>18.4</v>
       </c>
       <c r="I39" t="n">
         <v>27</v>
       </c>
       <c r="J39" t="n">
-        <v>-122.32</v>
+        <v>31.11</v>
       </c>
       <c r="K39" t="n">
-        <v>16.63</v>
+        <v>-156.56</v>
       </c>
       <c r="L39" t="n">
-        <v>123.45</v>
+        <v>159.62</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06:01:42</t>
+          <t>06:00:49</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>2.23</v>
+        <v>2.28</v>
       </c>
       <c r="F40" t="n">
-        <v>7.84</v>
+        <v>6.66</v>
       </c>
       <c r="G40" t="n">
-        <v>247.5</v>
+        <v>236.6</v>
       </c>
       <c r="H40" t="n">
-        <v>13</v>
+        <v>12.7</v>
       </c>
       <c r="I40" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J40" t="n">
-        <v>38.37</v>
+        <v>-36.04</v>
       </c>
       <c r="K40" t="n">
-        <v>-138.82</v>
+        <v>83.8</v>
       </c>
       <c r="L40" t="n">
-        <v>144.02</v>
+        <v>91.22</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06:06:30</t>
+          <t>06:05:11</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>2.29</v>
+        <v>2.51</v>
       </c>
       <c r="F41" t="n">
-        <v>7.53</v>
+        <v>7.9</v>
       </c>
       <c r="G41" t="n">
-        <v>236.6</v>
+        <v>237.2</v>
       </c>
       <c r="H41" t="n">
-        <v>12.7</v>
+        <v>11.3</v>
       </c>
       <c r="I41" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J41" t="n">
-        <v>107.78</v>
+        <v>-169.72</v>
       </c>
       <c r="K41" t="n">
-        <v>21.09</v>
+        <v>190.75</v>
       </c>
       <c r="L41" t="n">
-        <v>109.82</v>
+        <v>255.33</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06:08:17</t>
+          <t>06:07:14</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>3.41</v>
+        <v>2.15</v>
       </c>
       <c r="F42" t="n">
-        <v>8.06</v>
+        <v>4.49</v>
       </c>
       <c r="G42" t="n">
-        <v>237.2</v>
+        <v>233.7</v>
       </c>
       <c r="H42" t="n">
-        <v>11.3</v>
+        <v>22.3</v>
       </c>
       <c r="I42" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J42" t="n">
-        <v>172.65</v>
+        <v>-133.39</v>
       </c>
       <c r="K42" t="n">
-        <v>-148.42</v>
+        <v>-20.49</v>
       </c>
       <c r="L42" t="n">
-        <v>227.68</v>
+        <v>134.95</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06:08:57</t>
+          <t>06:08:46</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1846,31 +1846,31 @@
         <v>2.4</v>
       </c>
       <c r="F43" t="n">
-        <v>7.45</v>
+        <v>2.7</v>
       </c>
       <c r="G43" t="n">
-        <v>233.7</v>
+        <v>246</v>
       </c>
       <c r="H43" t="n">
-        <v>11.5</v>
+        <v>13.6</v>
       </c>
       <c r="I43" t="n">
         <v>28</v>
       </c>
       <c r="J43" t="n">
-        <v>-98.20999999999999</v>
+        <v>-82.69</v>
       </c>
       <c r="K43" t="n">
-        <v>-47.02</v>
+        <v>106.29</v>
       </c>
       <c r="L43" t="n">
-        <v>108.88</v>
+        <v>134.66</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:20:25</t>
+          <t>06:19:49</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>1.65</v>
+        <v>2.24</v>
       </c>
       <c r="F44" t="n">
-        <v>8.119999999999999</v>
+        <v>5.46</v>
       </c>
       <c r="G44" t="n">
-        <v>246</v>
+        <v>236.2</v>
       </c>
       <c r="H44" t="n">
-        <v>13.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I44" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="J44" t="n">
-        <v>21.72</v>
+        <v>5.21</v>
       </c>
       <c r="K44" t="n">
-        <v>-29.86</v>
+        <v>49.1</v>
       </c>
       <c r="L44" t="n">
-        <v>36.92</v>
+        <v>49.38</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:21:00</t>
+          <t>06:21:35</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>2.7</v>
+        <v>2.33</v>
       </c>
       <c r="F45" t="n">
-        <v>7.67</v>
+        <v>5.59</v>
       </c>
       <c r="G45" t="n">
-        <v>248.9</v>
+        <v>243</v>
       </c>
       <c r="H45" t="n">
-        <v>12.8</v>
+        <v>14.4</v>
       </c>
       <c r="I45" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>-29.28</v>
+        <v>-33.28</v>
       </c>
       <c r="K45" t="n">
-        <v>39.7</v>
+        <v>37.66</v>
       </c>
       <c r="L45" t="n">
-        <v>49.33</v>
+        <v>50.25</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:23:29</t>
+          <t>06:24:00</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>2.36</v>
+        <v>2.94</v>
       </c>
       <c r="F46" t="n">
-        <v>7.7</v>
+        <v>5.27</v>
       </c>
       <c r="G46" t="n">
-        <v>243</v>
+        <v>235.1</v>
       </c>
       <c r="H46" t="n">
-        <v>14.4</v>
+        <v>15.5</v>
       </c>
       <c r="I46" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>25.06</v>
+        <v>37.01</v>
       </c>
       <c r="K46" t="n">
-        <v>49.94</v>
+        <v>-33.69</v>
       </c>
       <c r="L46" t="n">
-        <v>55.88</v>
+        <v>50.05</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:28:42</t>
+          <t>06:29:37</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="F47" t="n">
-        <v>7.82</v>
+        <v>8.74</v>
       </c>
       <c r="G47" t="n">
-        <v>236.7</v>
+        <v>228.1</v>
       </c>
       <c r="H47" t="n">
-        <v>12.2</v>
+        <v>8.6</v>
       </c>
       <c r="I47" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J47" t="n">
-        <v>-39.32</v>
+        <v>-49.78</v>
       </c>
       <c r="K47" t="n">
-        <v>-15.58</v>
+        <v>-67.92</v>
       </c>
       <c r="L47" t="n">
-        <v>42.29</v>
+        <v>84.20999999999999</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:30:28</t>
+          <t>06:31:09</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>2.89</v>
+        <v>2.69</v>
       </c>
       <c r="F48" t="n">
-        <v>7.66</v>
+        <v>7.17</v>
       </c>
       <c r="G48" t="n">
-        <v>228.1</v>
+        <v>239.2</v>
       </c>
       <c r="H48" t="n">
-        <v>8.6</v>
+        <v>14.7</v>
       </c>
       <c r="I48" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J48" t="n">
-        <v>-68.86</v>
+        <v>21.37</v>
       </c>
       <c r="K48" t="n">
-        <v>26.52</v>
+        <v>-103.17</v>
       </c>
       <c r="L48" t="n">
-        <v>73.79000000000001</v>
+        <v>105.36</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:32:53</t>
+          <t>06:32:54</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>2.7</v>
+        <v>3.04</v>
       </c>
       <c r="F49" t="n">
-        <v>7.84</v>
+        <v>8.74</v>
       </c>
       <c r="G49" t="n">
-        <v>242.5</v>
+        <v>249.8</v>
       </c>
       <c r="H49" t="n">
-        <v>14.3</v>
+        <v>13.8</v>
       </c>
       <c r="I49" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="J49" t="n">
-        <v>-17.4</v>
+        <v>-37.08</v>
       </c>
       <c r="K49" t="n">
-        <v>-35.93</v>
+        <v>-43.8</v>
       </c>
       <c r="L49" t="n">
-        <v>39.92</v>
+        <v>57.39</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:38:30</t>
+          <t>06:37:22</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>2.67</v>
+        <v>1.85</v>
       </c>
       <c r="F50" t="n">
-        <v>7.63</v>
+        <v>3.01</v>
       </c>
       <c r="G50" t="n">
-        <v>243.7</v>
+        <v>238.9</v>
       </c>
       <c r="H50" t="n">
-        <v>13.6</v>
+        <v>14.4</v>
       </c>
       <c r="I50" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J50" t="n">
-        <v>82.38</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K50" t="n">
-        <v>-11.39</v>
+        <v>-5.36</v>
       </c>
       <c r="L50" t="n">
-        <v>83.17</v>
+        <v>82.08</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:40:02</t>
+          <t>06:38:30</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="F51" t="n">
-        <v>7.69</v>
+        <v>6.74</v>
       </c>
       <c r="G51" t="n">
-        <v>226.9</v>
+        <v>242.4</v>
       </c>
       <c r="H51" t="n">
-        <v>12.2</v>
+        <v>12</v>
       </c>
       <c r="I51" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J51" t="n">
-        <v>38.06</v>
+        <v>-68.66</v>
       </c>
       <c r="K51" t="n">
-        <v>79.2</v>
+        <v>-36.67</v>
       </c>
       <c r="L51" t="n">
-        <v>87.87</v>
+        <v>77.84</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:41:46</t>
+          <t>06:39:55</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>2.55</v>
+        <v>2.44</v>
       </c>
       <c r="F52" t="n">
-        <v>7.38</v>
+        <v>8.27</v>
       </c>
       <c r="G52" t="n">
-        <v>227.2</v>
+        <v>235.1</v>
       </c>
       <c r="H52" t="n">
-        <v>14.4</v>
+        <v>18.2</v>
       </c>
       <c r="I52" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>41.32</v>
+        <v>-95.95999999999999</v>
       </c>
       <c r="K52" t="n">
-        <v>-74.90000000000001</v>
+        <v>-95.13</v>
       </c>
       <c r="L52" t="n">
-        <v>85.54000000000001</v>
+        <v>135.12</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:46:15</t>
+          <t>06:44:59</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>2.49</v>
+        <v>2.27</v>
       </c>
       <c r="F53" t="n">
-        <v>8.07</v>
+        <v>8.74</v>
       </c>
       <c r="G53" t="n">
-        <v>242.8</v>
+        <v>236</v>
       </c>
       <c r="H53" t="n">
-        <v>16.7</v>
+        <v>11.6</v>
       </c>
       <c r="I53" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J53" t="n">
-        <v>88.42</v>
+        <v>-86.69</v>
       </c>
       <c r="K53" t="n">
-        <v>-110.92</v>
+        <v>-85.65000000000001</v>
       </c>
       <c r="L53" t="n">
-        <v>141.85</v>
+        <v>121.86</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:47:23</t>
+          <t>06:47:03</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="F54" t="n">
-        <v>7.36</v>
+        <v>8.66</v>
       </c>
       <c r="G54" t="n">
-        <v>247.3</v>
+        <v>231.8</v>
       </c>
       <c r="H54" t="n">
-        <v>13.5</v>
+        <v>13.9</v>
       </c>
       <c r="I54" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J54" t="n">
-        <v>-39.07</v>
+        <v>-78.65000000000001</v>
       </c>
       <c r="K54" t="n">
-        <v>72.39</v>
+        <v>130.5</v>
       </c>
       <c r="L54" t="n">
-        <v>82.26000000000001</v>
+        <v>152.36</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:48:47</t>
+          <t>06:48:34</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,28 +2347,28 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>2.45</v>
+        <v>2.91</v>
       </c>
       <c r="F55" t="n">
-        <v>7.64</v>
+        <v>5.9</v>
       </c>
       <c r="G55" t="n">
-        <v>247.1</v>
+        <v>235.1</v>
       </c>
       <c r="H55" t="n">
-        <v>11.2</v>
+        <v>15</v>
       </c>
       <c r="I55" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="J55" t="n">
-        <v>94.97</v>
+        <v>45.9</v>
       </c>
       <c r="K55" t="n">
-        <v>-51.11</v>
+        <v>115.13</v>
       </c>
       <c r="L55" t="n">
-        <v>107.85</v>
+        <v>123.94</v>
       </c>
     </row>
     <row r="56">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>2.93</v>
+        <v>3.1</v>
       </c>
       <c r="F56" t="n">
-        <v>8.52</v>
+        <v>8.74</v>
       </c>
       <c r="G56" t="n">
-        <v>225.7</v>
+        <v>239.9</v>
       </c>
       <c r="H56" t="n">
-        <v>13.7</v>
+        <v>13.4</v>
       </c>
       <c r="I56" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J56" t="n">
-        <v>-64.22</v>
+        <v>-93.14</v>
       </c>
       <c r="K56" t="n">
-        <v>128.61</v>
+        <v>-166.74</v>
       </c>
       <c r="L56" t="n">
-        <v>143.75</v>
+        <v>190.99</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06:55:55</t>
+          <t>06:55:53</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="F57" t="n">
-        <v>7.87</v>
+        <v>7.21</v>
       </c>
       <c r="G57" t="n">
-        <v>228.2</v>
+        <v>237.8</v>
       </c>
       <c r="H57" t="n">
-        <v>14.8</v>
+        <v>15.2</v>
       </c>
       <c r="I57" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="J57" t="n">
-        <v>131.65</v>
+        <v>-193.38</v>
       </c>
       <c r="K57" t="n">
-        <v>29.35</v>
+        <v>-117.22</v>
       </c>
       <c r="L57" t="n">
-        <v>134.88</v>
+        <v>226.13</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06:57:27</t>
+          <t>06:58:23</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>2.55</v>
+        <v>2.07</v>
       </c>
       <c r="F58" t="n">
-        <v>8.199999999999999</v>
+        <v>6.76</v>
       </c>
       <c r="G58" t="n">
-        <v>244</v>
+        <v>220.2</v>
       </c>
       <c r="H58" t="n">
-        <v>10</v>
+        <v>13.4</v>
       </c>
       <c r="I58" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J58" t="n">
-        <v>99.27</v>
+        <v>-26.63</v>
       </c>
       <c r="K58" t="n">
-        <v>84.95</v>
+        <v>225.09</v>
       </c>
       <c r="L58" t="n">
-        <v>130.65</v>
+        <v>226.66</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07:10:03</t>
+          <t>07:08:44</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="F59" t="n">
-        <v>8.16</v>
+        <v>6.4</v>
       </c>
       <c r="G59" t="n">
-        <v>220.6</v>
+        <v>234.9</v>
       </c>
       <c r="H59" t="n">
-        <v>10.4</v>
+        <v>18.4</v>
       </c>
       <c r="I59" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J59" t="n">
-        <v>-1.3</v>
+        <v>52.15</v>
       </c>
       <c r="K59" t="n">
-        <v>-67.23</v>
+        <v>1.03</v>
       </c>
       <c r="L59" t="n">
-        <v>67.23999999999999</v>
+        <v>52.16</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07:10:55</t>
+          <t>07:10:23</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>2.17</v>
+        <v>2.88</v>
       </c>
       <c r="F60" t="n">
-        <v>7.95</v>
+        <v>8.74</v>
       </c>
       <c r="G60" t="n">
-        <v>232.1</v>
+        <v>241.2</v>
       </c>
       <c r="H60" t="n">
-        <v>21.4</v>
+        <v>14.6</v>
       </c>
       <c r="I60" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="J60" t="n">
-        <v>1.42</v>
+        <v>-48.59</v>
       </c>
       <c r="K60" t="n">
-        <v>40.31</v>
+        <v>-1.76</v>
       </c>
       <c r="L60" t="n">
-        <v>40.33</v>
+        <v>48.63</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07:12:38</t>
+          <t>07:11:41</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>2.53</v>
+        <v>2.51</v>
       </c>
       <c r="F61" t="n">
-        <v>7.33</v>
+        <v>7.1</v>
       </c>
       <c r="G61" t="n">
-        <v>246.4</v>
+        <v>223.9</v>
       </c>
       <c r="H61" t="n">
-        <v>13.7</v>
+        <v>6.8</v>
       </c>
       <c r="I61" t="n">
         <v>28</v>
       </c>
       <c r="J61" t="n">
-        <v>18.43</v>
+        <v>-49.06</v>
       </c>
       <c r="K61" t="n">
-        <v>30.71</v>
+        <v>11.57</v>
       </c>
       <c r="L61" t="n">
-        <v>35.82</v>
+        <v>50.41</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:18:10</t>
+          <t>07:15:01</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2644,31 +2644,31 @@
         <v>2.66</v>
       </c>
       <c r="F62" t="n">
-        <v>7.98</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G62" t="n">
-        <v>234.2</v>
+        <v>216</v>
       </c>
       <c r="H62" t="n">
-        <v>13.5</v>
+        <v>14.1</v>
       </c>
       <c r="I62" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="J62" t="n">
-        <v>-51.83</v>
+        <v>18.69</v>
       </c>
       <c r="K62" t="n">
-        <v>-57.8</v>
+        <v>76.8</v>
       </c>
       <c r="L62" t="n">
-        <v>77.63</v>
+        <v>79.04000000000001</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:19:50</t>
+          <t>07:17:13</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>2.21</v>
+        <v>3.04</v>
       </c>
       <c r="F63" t="n">
-        <v>7.57</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="G63" t="n">
-        <v>238.8</v>
+        <v>245.8</v>
       </c>
       <c r="H63" t="n">
-        <v>14.7</v>
+        <v>19.6</v>
       </c>
       <c r="I63" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="J63" t="n">
-        <v>4.03</v>
+        <v>5.3</v>
       </c>
       <c r="K63" t="n">
-        <v>-81.33</v>
+        <v>73.93000000000001</v>
       </c>
       <c r="L63" t="n">
-        <v>81.43000000000001</v>
+        <v>74.12</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:21:08</t>
+          <t>07:19:18</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>2.56</v>
+        <v>2.93</v>
       </c>
       <c r="F64" t="n">
-        <v>7.05</v>
+        <v>8.74</v>
       </c>
       <c r="G64" t="n">
-        <v>251.2</v>
+        <v>243.8</v>
       </c>
       <c r="H64" t="n">
-        <v>20.1</v>
+        <v>12.1</v>
       </c>
       <c r="I64" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="J64" t="n">
-        <v>-55.03</v>
+        <v>-29.8</v>
       </c>
       <c r="K64" t="n">
-        <v>52.06</v>
+        <v>-44.59</v>
       </c>
       <c r="L64" t="n">
-        <v>75.75</v>
+        <v>53.64</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:24:27</t>
+          <t>07:23:31</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="F65" t="n">
-        <v>7.78</v>
+        <v>7.41</v>
       </c>
       <c r="G65" t="n">
-        <v>247</v>
+        <v>241.6</v>
       </c>
       <c r="H65" t="n">
-        <v>18.3</v>
+        <v>14.9</v>
       </c>
       <c r="I65" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>54.51</v>
+        <v>120.22</v>
       </c>
       <c r="K65" t="n">
-        <v>61.62</v>
+        <v>23.45</v>
       </c>
       <c r="L65" t="n">
-        <v>82.27</v>
+        <v>122.48</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:26:39</t>
+          <t>07:26:14</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>2.6</v>
+        <v>2.77</v>
       </c>
       <c r="F66" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="G66" t="n">
-        <v>251</v>
+        <v>227.7</v>
       </c>
       <c r="H66" t="n">
-        <v>18</v>
+        <v>13.1</v>
       </c>
       <c r="I66" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>34.36</v>
+        <v>-108.71</v>
       </c>
       <c r="K66" t="n">
-        <v>55.1</v>
+        <v>42.62</v>
       </c>
       <c r="L66" t="n">
-        <v>64.94</v>
+        <v>116.76</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:28:45</t>
+          <t>07:27:23</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>2.52</v>
+        <v>2.75</v>
       </c>
       <c r="F67" t="n">
-        <v>7.42</v>
+        <v>8.06</v>
       </c>
       <c r="G67" t="n">
-        <v>251.8</v>
+        <v>239.3</v>
       </c>
       <c r="H67" t="n">
-        <v>15.6</v>
+        <v>9</v>
       </c>
       <c r="I67" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J67" t="n">
-        <v>-85.15000000000001</v>
+        <v>-121.1</v>
       </c>
       <c r="K67" t="n">
-        <v>-12.44</v>
+        <v>37.6</v>
       </c>
       <c r="L67" t="n">
-        <v>86.05</v>
+        <v>126.8</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:32:58</t>
+          <t>07:32:54</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="F68" t="n">
-        <v>7.56</v>
+        <v>4.71</v>
       </c>
       <c r="G68" t="n">
-        <v>235.5</v>
+        <v>228.4</v>
       </c>
       <c r="H68" t="n">
-        <v>15.2</v>
+        <v>19.2</v>
       </c>
       <c r="I68" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="J68" t="n">
-        <v>-102.21</v>
+        <v>-7.06</v>
       </c>
       <c r="K68" t="n">
-        <v>13.23</v>
+        <v>-95.65000000000001</v>
       </c>
       <c r="L68" t="n">
-        <v>103.07</v>
+        <v>95.91</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:35:41</t>
+          <t>07:34:57</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>2.83</v>
+        <v>2.3</v>
       </c>
       <c r="F69" t="n">
-        <v>7.13</v>
+        <v>3.4</v>
       </c>
       <c r="G69" t="n">
-        <v>236.8</v>
+        <v>244.1</v>
       </c>
       <c r="H69" t="n">
-        <v>6.8</v>
+        <v>11.2</v>
       </c>
       <c r="I69" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J69" t="n">
-        <v>-93.43000000000001</v>
+        <v>99.98</v>
       </c>
       <c r="K69" t="n">
-        <v>-128.18</v>
+        <v>-29.08</v>
       </c>
       <c r="L69" t="n">
-        <v>158.62</v>
+        <v>104.12</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:36:50</t>
+          <t>07:35:52</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>2.7</v>
+        <v>3.11</v>
       </c>
       <c r="F70" t="n">
-        <v>6.8</v>
+        <v>8.74</v>
       </c>
       <c r="G70" t="n">
-        <v>241.9</v>
+        <v>228.2</v>
       </c>
       <c r="H70" t="n">
-        <v>7.5</v>
+        <v>15.4</v>
       </c>
       <c r="I70" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J70" t="n">
-        <v>-76.11</v>
+        <v>137.21</v>
       </c>
       <c r="K70" t="n">
-        <v>86.68000000000001</v>
+        <v>-132.4</v>
       </c>
       <c r="L70" t="n">
-        <v>115.36</v>
+        <v>190.67</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:42:21</t>
+          <t>07:40:01</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>2.99</v>
+        <v>2.39</v>
       </c>
       <c r="F71" t="n">
-        <v>8.19</v>
+        <v>6.45</v>
       </c>
       <c r="G71" t="n">
-        <v>240.8</v>
+        <v>241.4</v>
       </c>
       <c r="H71" t="n">
-        <v>3.8</v>
+        <v>19.6</v>
       </c>
       <c r="I71" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>43.31</v>
+        <v>-161.81</v>
       </c>
       <c r="K71" t="n">
-        <v>-163.32</v>
+        <v>207.17</v>
       </c>
       <c r="L71" t="n">
-        <v>168.96</v>
+        <v>262.87</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:44:23</t>
+          <t>07:42:29</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>2.55</v>
+        <v>2.67</v>
       </c>
       <c r="F72" t="n">
-        <v>7.98</v>
+        <v>8.74</v>
       </c>
       <c r="G72" t="n">
-        <v>228.5</v>
+        <v>233.6</v>
       </c>
       <c r="H72" t="n">
-        <v>7.8</v>
+        <v>11.4</v>
       </c>
       <c r="I72" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J72" t="n">
-        <v>-128.66</v>
+        <v>127.8</v>
       </c>
       <c r="K72" t="n">
-        <v>145.7</v>
+        <v>-236.91</v>
       </c>
       <c r="L72" t="n">
-        <v>194.37</v>
+        <v>269.18</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:45:18</t>
+          <t>07:43:45</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>2.79</v>
+        <v>3.19</v>
       </c>
       <c r="F73" t="n">
-        <v>8.16</v>
+        <v>8.74</v>
       </c>
       <c r="G73" t="n">
-        <v>237.5</v>
+        <v>231.3</v>
       </c>
       <c r="H73" t="n">
-        <v>21.7</v>
+        <v>11.6</v>
       </c>
       <c r="I73" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J73" t="n">
-        <v>-114.65</v>
+        <v>-56.53</v>
       </c>
       <c r="K73" t="n">
-        <v>-105.65</v>
+        <v>-186.49</v>
       </c>
       <c r="L73" t="n">
-        <v>155.9</v>
+        <v>194.87</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:54:48</t>
+          <t>07:55:53</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="F74" t="n">
-        <v>7.55</v>
+        <v>8.74</v>
       </c>
       <c r="G74" t="n">
-        <v>242.1</v>
+        <v>233.3</v>
       </c>
       <c r="H74" t="n">
-        <v>6</v>
+        <v>12.9</v>
       </c>
       <c r="I74" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J74" t="n">
-        <v>9.26</v>
+        <v>-46.75</v>
       </c>
       <c r="K74" t="n">
-        <v>-52.07</v>
+        <v>-15.48</v>
       </c>
       <c r="L74" t="n">
-        <v>52.89</v>
+        <v>49.25</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:55:54</t>
+          <t>07:57:41</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>2.59</v>
+        <v>2.88</v>
       </c>
       <c r="F75" t="n">
-        <v>8.23</v>
+        <v>8.74</v>
       </c>
       <c r="G75" t="n">
-        <v>229.6</v>
+        <v>244.8</v>
       </c>
       <c r="H75" t="n">
-        <v>13.2</v>
+        <v>18.6</v>
       </c>
       <c r="I75" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="J75" t="n">
-        <v>51.31</v>
+        <v>-8.31</v>
       </c>
       <c r="K75" t="n">
-        <v>-4.97</v>
+        <v>-50.69</v>
       </c>
       <c r="L75" t="n">
-        <v>51.55</v>
+        <v>51.37</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07:58:28</t>
+          <t>07:59:17</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>2.57</v>
+        <v>3.22</v>
       </c>
       <c r="F76" t="n">
-        <v>7.89</v>
+        <v>7.28</v>
       </c>
       <c r="G76" t="n">
-        <v>236.3</v>
+        <v>250.7</v>
       </c>
       <c r="H76" t="n">
-        <v>11.2</v>
+        <v>15.8</v>
       </c>
       <c r="I76" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J76" t="n">
-        <v>30.89</v>
+        <v>32.82</v>
       </c>
       <c r="K76" t="n">
-        <v>25.44</v>
+        <v>-68.69</v>
       </c>
       <c r="L76" t="n">
-        <v>40.01</v>
+        <v>76.13</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>08:03:41</t>
+          <t>08:03:24</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>3.02</v>
+        <v>2.59</v>
       </c>
       <c r="F77" t="n">
-        <v>8.44</v>
+        <v>8.74</v>
       </c>
       <c r="G77" t="n">
-        <v>230.8</v>
+        <v>241.8</v>
       </c>
       <c r="H77" t="n">
-        <v>13.1</v>
+        <v>8.4</v>
       </c>
       <c r="I77" t="n">
         <v>27</v>
       </c>
       <c r="J77" t="n">
-        <v>-65.37</v>
+        <v>-20.75</v>
       </c>
       <c r="K77" t="n">
-        <v>24.33</v>
+        <v>51.83</v>
       </c>
       <c r="L77" t="n">
-        <v>69.75</v>
+        <v>55.83</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>08:05:28</t>
+          <t>08:05:49</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>3.11</v>
+        <v>2.85</v>
       </c>
       <c r="F78" t="n">
-        <v>7.4</v>
+        <v>6.76</v>
       </c>
       <c r="G78" t="n">
-        <v>221.7</v>
+        <v>242.6</v>
       </c>
       <c r="H78" t="n">
-        <v>17.5</v>
+        <v>15.8</v>
       </c>
       <c r="I78" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J78" t="n">
-        <v>30.41</v>
+        <v>13.13</v>
       </c>
       <c r="K78" t="n">
-        <v>-63.47</v>
+        <v>-63.36</v>
       </c>
       <c r="L78" t="n">
-        <v>70.38</v>
+        <v>64.70999999999999</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>08:07:05</t>
+          <t>08:07:07</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>2.41</v>
+        <v>2.89</v>
       </c>
       <c r="F79" t="n">
-        <v>7.82</v>
+        <v>7.97</v>
       </c>
       <c r="G79" t="n">
-        <v>242.3</v>
+        <v>244.8</v>
       </c>
       <c r="H79" t="n">
-        <v>12.9</v>
+        <v>10.7</v>
       </c>
       <c r="I79" t="n">
         <v>28</v>
       </c>
       <c r="J79" t="n">
-        <v>-51.43</v>
+        <v>-61.24</v>
       </c>
       <c r="K79" t="n">
-        <v>25.28</v>
+        <v>-20.8</v>
       </c>
       <c r="L79" t="n">
-        <v>57.31</v>
+        <v>64.68000000000001</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>08:11:12</t>
+          <t>08:10:59</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>2.88</v>
+        <v>3.12</v>
       </c>
       <c r="F80" t="n">
-        <v>7.88</v>
+        <v>6.64</v>
       </c>
       <c r="G80" t="n">
-        <v>228.4</v>
+        <v>248.5</v>
       </c>
       <c r="H80" t="n">
-        <v>14.7</v>
+        <v>18.9</v>
       </c>
       <c r="I80" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>-53.42</v>
+        <v>-145.64</v>
       </c>
       <c r="K80" t="n">
-        <v>-34.07</v>
+        <v>-7.69</v>
       </c>
       <c r="L80" t="n">
-        <v>63.36</v>
+        <v>145.84</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08:13:37</t>
+          <t>08:12:09</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>2.56</v>
+        <v>3</v>
       </c>
       <c r="F81" t="n">
-        <v>8.25</v>
+        <v>7.64</v>
       </c>
       <c r="G81" t="n">
-        <v>235.1</v>
+        <v>234.8</v>
       </c>
       <c r="H81" t="n">
-        <v>9.5</v>
+        <v>4.6</v>
       </c>
       <c r="I81" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J81" t="n">
-        <v>-82.33</v>
+        <v>66.33</v>
       </c>
       <c r="K81" t="n">
-        <v>63.98</v>
+        <v>78.94</v>
       </c>
       <c r="L81" t="n">
-        <v>104.26</v>
+        <v>103.11</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:14:55</t>
+          <t>08:14:15</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>3.06</v>
+        <v>2.97</v>
       </c>
       <c r="F82" t="n">
-        <v>8.050000000000001</v>
+        <v>8.74</v>
       </c>
       <c r="G82" t="n">
-        <v>237.1</v>
+        <v>224.3</v>
       </c>
       <c r="H82" t="n">
-        <v>3.4</v>
+        <v>15.5</v>
       </c>
       <c r="I82" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>-52.78</v>
+        <v>-63.41</v>
       </c>
       <c r="K82" t="n">
-        <v>96.69</v>
+        <v>78.47</v>
       </c>
       <c r="L82" t="n">
-        <v>110.15</v>
+        <v>100.89</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:18:47</t>
+          <t>08:19:41</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="F83" t="n">
-        <v>7.98</v>
+        <v>7.92</v>
       </c>
       <c r="G83" t="n">
-        <v>248.1</v>
+        <v>225.3</v>
       </c>
       <c r="H83" t="n">
-        <v>18.1</v>
+        <v>13.2</v>
       </c>
       <c r="I83" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J83" t="n">
-        <v>83.88</v>
+        <v>108.78</v>
       </c>
       <c r="K83" t="n">
-        <v>51.01</v>
+        <v>-72.15000000000001</v>
       </c>
       <c r="L83" t="n">
-        <v>98.17</v>
+        <v>130.53</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:19:57</t>
+          <t>08:21:41</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>2.34</v>
+        <v>2.67</v>
       </c>
       <c r="F84" t="n">
-        <v>7.53</v>
+        <v>6.21</v>
       </c>
       <c r="G84" t="n">
-        <v>246</v>
+        <v>227.1</v>
       </c>
       <c r="H84" t="n">
-        <v>11.1</v>
+        <v>14.8</v>
       </c>
       <c r="I84" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J84" t="n">
-        <v>-52.39</v>
+        <v>-116.06</v>
       </c>
       <c r="K84" t="n">
-        <v>60.02</v>
+        <v>-110.57</v>
       </c>
       <c r="L84" t="n">
-        <v>79.67</v>
+        <v>160.3</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:22:03</t>
+          <t>08:23:42</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>2.73</v>
+        <v>3.15</v>
       </c>
       <c r="F85" t="n">
-        <v>7.48</v>
+        <v>8.74</v>
       </c>
       <c r="G85" t="n">
-        <v>235</v>
+        <v>241.4</v>
       </c>
       <c r="H85" t="n">
-        <v>17.5</v>
+        <v>11.1</v>
       </c>
       <c r="I85" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J85" t="n">
-        <v>-119.92</v>
+        <v>-191.66</v>
       </c>
       <c r="K85" t="n">
-        <v>26.2</v>
+        <v>3.92</v>
       </c>
       <c r="L85" t="n">
-        <v>122.75</v>
+        <v>191.7</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:27:28</t>
+          <t>08:28:06</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>2.43</v>
+        <v>2.85</v>
       </c>
       <c r="F86" t="n">
-        <v>8.26</v>
+        <v>7.62</v>
       </c>
       <c r="G86" t="n">
-        <v>228.8</v>
+        <v>229.7</v>
       </c>
       <c r="H86" t="n">
-        <v>8.800000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="I86" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>11.11</v>
+        <v>40.35</v>
       </c>
       <c r="K86" t="n">
-        <v>-197.85</v>
+        <v>-278.16</v>
       </c>
       <c r="L86" t="n">
-        <v>198.16</v>
+        <v>281.07</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:29:29</t>
+          <t>08:29:30</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>2.61</v>
+        <v>2.65</v>
       </c>
       <c r="F87" t="n">
-        <v>7.75</v>
+        <v>8.18</v>
       </c>
       <c r="G87" t="n">
-        <v>239.4</v>
+        <v>224.9</v>
       </c>
       <c r="H87" t="n">
-        <v>4.9</v>
+        <v>6.9</v>
       </c>
       <c r="I87" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J87" t="n">
-        <v>-66.91</v>
+        <v>-80.26000000000001</v>
       </c>
       <c r="K87" t="n">
-        <v>-201.6</v>
+        <v>-79.79000000000001</v>
       </c>
       <c r="L87" t="n">
-        <v>212.41</v>
+        <v>113.17</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:31:30</t>
+          <t>08:30:32</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>2.52</v>
+        <v>3.44</v>
       </c>
       <c r="F88" t="n">
-        <v>7.42</v>
+        <v>8.74</v>
       </c>
       <c r="G88" t="n">
-        <v>216</v>
+        <v>241.6</v>
       </c>
       <c r="H88" t="n">
-        <v>16.4</v>
+        <v>24.4</v>
       </c>
       <c r="I88" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J88" t="n">
-        <v>-11.45</v>
+        <v>-285.12</v>
       </c>
       <c r="K88" t="n">
-        <v>138.71</v>
+        <v>-185.24</v>
       </c>
       <c r="L88" t="n">
-        <v>139.18</v>
+        <v>340.02</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-05-25.xlsx
+++ b/output/2024-05-25.xlsx
@@ -640,13 +640,13 @@
         <v>28</v>
       </c>
       <c r="J14" t="n">
-        <v>45.13</v>
+        <v>41.2</v>
       </c>
       <c r="K14" t="n">
-        <v>-6.12</v>
+        <v>-5.59</v>
       </c>
       <c r="L14" t="n">
-        <v>45.54</v>
+        <v>41.58</v>
       </c>
     </row>
     <row r="15">
@@ -724,13 +724,13 @@
         <v>22</v>
       </c>
       <c r="J16" t="n">
-        <v>-22.44</v>
+        <v>-23.3</v>
       </c>
       <c r="K16" t="n">
-        <v>-43.93</v>
+        <v>-45.62</v>
       </c>
       <c r="L16" t="n">
-        <v>49.33</v>
+        <v>51.22</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>28</v>
       </c>
       <c r="J17" t="n">
-        <v>48.06</v>
+        <v>43.88</v>
       </c>
       <c r="K17" t="n">
-        <v>-33.66</v>
+        <v>-30.74</v>
       </c>
       <c r="L17" t="n">
-        <v>58.68</v>
+        <v>53.57</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>2.61</v>
+        <v>2.56</v>
       </c>
       <c r="K18" t="n">
-        <v>-81.8</v>
+        <v>-80.13</v>
       </c>
       <c r="L18" t="n">
-        <v>81.84999999999999</v>
+        <v>80.18000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -892,13 +892,13 @@
         <v>26</v>
       </c>
       <c r="J20" t="n">
-        <v>92.87</v>
+        <v>89</v>
       </c>
       <c r="K20" t="n">
-        <v>-11.69</v>
+        <v>-11.2</v>
       </c>
       <c r="L20" t="n">
-        <v>93.61</v>
+        <v>89.70999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>-73.94</v>
+        <v>-76.77</v>
       </c>
       <c r="K21" t="n">
-        <v>43.4</v>
+        <v>45.07</v>
       </c>
       <c r="L21" t="n">
-        <v>85.73</v>
+        <v>89.02</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>25</v>
       </c>
       <c r="J22" t="n">
-        <v>72.41</v>
+        <v>70.93000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>82.81</v>
+        <v>81.12</v>
       </c>
       <c r="L22" t="n">
-        <v>110</v>
+        <v>107.76</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>28</v>
       </c>
       <c r="J23" t="n">
-        <v>99.77</v>
+        <v>91.09</v>
       </c>
       <c r="K23" t="n">
-        <v>-77.16</v>
+        <v>-70.45</v>
       </c>
       <c r="L23" t="n">
-        <v>126.12</v>
+        <v>115.16</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>28</v>
       </c>
       <c r="J24" t="n">
-        <v>-116.39</v>
+        <v>-106.27</v>
       </c>
       <c r="K24" t="n">
-        <v>25.53</v>
+        <v>23.31</v>
       </c>
       <c r="L24" t="n">
-        <v>119.16</v>
+        <v>108.8</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>-126.36</v>
+        <v>-128.84</v>
       </c>
       <c r="K25" t="n">
-        <v>-8.460000000000001</v>
+        <v>-8.619999999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>126.64</v>
+        <v>129.13</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>28</v>
       </c>
       <c r="J26" t="n">
-        <v>-211.44</v>
+        <v>-193.05</v>
       </c>
       <c r="K26" t="n">
-        <v>7.57</v>
+        <v>6.91</v>
       </c>
       <c r="L26" t="n">
-        <v>211.57</v>
+        <v>193.18</v>
       </c>
     </row>
     <row r="27">
@@ -1228,13 +1228,13 @@
         <v>27</v>
       </c>
       <c r="J28" t="n">
-        <v>73.15000000000001</v>
+        <v>68.54000000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>-126.56</v>
+        <v>-118.59</v>
       </c>
       <c r="L28" t="n">
-        <v>146.18</v>
+        <v>136.97</v>
       </c>
     </row>
     <row r="29">
@@ -1312,13 +1312,13 @@
         <v>25</v>
       </c>
       <c r="J30" t="n">
-        <v>-45.14</v>
+        <v>-44.22</v>
       </c>
       <c r="K30" t="n">
-        <v>-14.53</v>
+        <v>-14.23</v>
       </c>
       <c r="L30" t="n">
-        <v>47.42</v>
+        <v>46.45</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>27</v>
       </c>
       <c r="J31" t="n">
-        <v>-28.51</v>
+        <v>-26.68</v>
       </c>
       <c r="K31" t="n">
-        <v>-46.58</v>
+        <v>-43.59</v>
       </c>
       <c r="L31" t="n">
-        <v>54.61</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>-23.8</v>
+        <v>-22.28</v>
       </c>
       <c r="K32" t="n">
-        <v>50.71</v>
+        <v>47.47</v>
       </c>
       <c r="L32" t="n">
-        <v>56.01</v>
+        <v>52.44</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>27</v>
       </c>
       <c r="J33" t="n">
-        <v>76.72</v>
+        <v>71.81999999999999</v>
       </c>
       <c r="K33" t="n">
-        <v>45.48</v>
+        <v>42.57</v>
       </c>
       <c r="L33" t="n">
-        <v>89.18000000000001</v>
+        <v>83.48999999999999</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>26</v>
       </c>
       <c r="J34" t="n">
-        <v>-49.9</v>
+        <v>-47.82</v>
       </c>
       <c r="K34" t="n">
-        <v>-30.73</v>
+        <v>-29.45</v>
       </c>
       <c r="L34" t="n">
-        <v>58.6</v>
+        <v>56.16</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>87.78</v>
+        <v>89.5</v>
       </c>
       <c r="K35" t="n">
-        <v>-82.8</v>
+        <v>-84.43000000000001</v>
       </c>
       <c r="L35" t="n">
-        <v>120.67</v>
+        <v>123.04</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>23</v>
       </c>
       <c r="J36" t="n">
-        <v>-77.31999999999999</v>
+        <v>-78.84</v>
       </c>
       <c r="K36" t="n">
-        <v>20.3</v>
+        <v>20.7</v>
       </c>
       <c r="L36" t="n">
-        <v>79.94</v>
+        <v>81.51000000000001</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>19.81</v>
+        <v>19.4</v>
       </c>
       <c r="K37" t="n">
-        <v>-115.7</v>
+        <v>-113.34</v>
       </c>
       <c r="L37" t="n">
-        <v>117.38</v>
+        <v>114.99</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>27</v>
       </c>
       <c r="J38" t="n">
-        <v>100.47</v>
+        <v>94.06</v>
       </c>
       <c r="K38" t="n">
-        <v>-131.06</v>
+        <v>-122.69</v>
       </c>
       <c r="L38" t="n">
-        <v>165.14</v>
+        <v>154.6</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>27</v>
       </c>
       <c r="J39" t="n">
-        <v>31.11</v>
+        <v>29.12</v>
       </c>
       <c r="K39" t="n">
-        <v>-156.56</v>
+        <v>-146.56</v>
       </c>
       <c r="L39" t="n">
-        <v>159.62</v>
+        <v>149.43</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>28</v>
       </c>
       <c r="J40" t="n">
-        <v>-36.04</v>
+        <v>-32.9</v>
       </c>
       <c r="K40" t="n">
-        <v>83.8</v>
+        <v>76.51000000000001</v>
       </c>
       <c r="L40" t="n">
-        <v>91.22</v>
+        <v>83.28</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>22</v>
       </c>
       <c r="J41" t="n">
-        <v>-169.72</v>
+        <v>-176.25</v>
       </c>
       <c r="K41" t="n">
-        <v>190.75</v>
+        <v>198.09</v>
       </c>
       <c r="L41" t="n">
-        <v>255.33</v>
+        <v>265.15</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>27</v>
       </c>
       <c r="J42" t="n">
-        <v>-133.39</v>
+        <v>-124.88</v>
       </c>
       <c r="K42" t="n">
-        <v>-20.49</v>
+        <v>-19.18</v>
       </c>
       <c r="L42" t="n">
-        <v>134.95</v>
+        <v>126.34</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>28</v>
       </c>
       <c r="J43" t="n">
-        <v>-82.69</v>
+        <v>-75.5</v>
       </c>
       <c r="K43" t="n">
-        <v>106.29</v>
+        <v>97.04000000000001</v>
       </c>
       <c r="L43" t="n">
-        <v>134.66</v>
+        <v>122.95</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>28</v>
       </c>
       <c r="J44" t="n">
-        <v>5.21</v>
+        <v>4.76</v>
       </c>
       <c r="K44" t="n">
-        <v>49.1</v>
+        <v>44.83</v>
       </c>
       <c r="L44" t="n">
-        <v>49.38</v>
+        <v>45.08</v>
       </c>
     </row>
     <row r="45">
@@ -1984,13 +1984,13 @@
         <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>37.01</v>
+        <v>38.43</v>
       </c>
       <c r="K46" t="n">
-        <v>-33.69</v>
+        <v>-34.98</v>
       </c>
       <c r="L46" t="n">
-        <v>50.05</v>
+        <v>51.97</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>28</v>
       </c>
       <c r="J47" t="n">
-        <v>-49.78</v>
+        <v>-45.45</v>
       </c>
       <c r="K47" t="n">
-        <v>-67.92</v>
+        <v>-62.01</v>
       </c>
       <c r="L47" t="n">
-        <v>84.20999999999999</v>
+        <v>76.89</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>23</v>
       </c>
       <c r="J48" t="n">
-        <v>21.37</v>
+        <v>21.79</v>
       </c>
       <c r="K48" t="n">
-        <v>-103.17</v>
+        <v>-105.19</v>
       </c>
       <c r="L48" t="n">
-        <v>105.36</v>
+        <v>107.43</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>22</v>
       </c>
       <c r="J49" t="n">
-        <v>-37.08</v>
+        <v>-38.51</v>
       </c>
       <c r="K49" t="n">
-        <v>-43.8</v>
+        <v>-45.49</v>
       </c>
       <c r="L49" t="n">
-        <v>57.39</v>
+        <v>59.6</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>26</v>
       </c>
       <c r="J50" t="n">
-        <v>81.90000000000001</v>
+        <v>78.48999999999999</v>
       </c>
       <c r="K50" t="n">
-        <v>-5.36</v>
+        <v>-5.14</v>
       </c>
       <c r="L50" t="n">
-        <v>82.08</v>
+        <v>78.66</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>25</v>
       </c>
       <c r="J51" t="n">
-        <v>-68.66</v>
+        <v>-67.26000000000001</v>
       </c>
       <c r="K51" t="n">
-        <v>-36.67</v>
+        <v>-35.92</v>
       </c>
       <c r="L51" t="n">
-        <v>77.84</v>
+        <v>76.25</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>-95.95999999999999</v>
+        <v>-97.84</v>
       </c>
       <c r="K52" t="n">
-        <v>-95.13</v>
+        <v>-97</v>
       </c>
       <c r="L52" t="n">
-        <v>135.12</v>
+        <v>137.77</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>27</v>
       </c>
       <c r="J53" t="n">
-        <v>-86.69</v>
+        <v>-81.16</v>
       </c>
       <c r="K53" t="n">
-        <v>-85.65000000000001</v>
+        <v>-80.18000000000001</v>
       </c>
       <c r="L53" t="n">
-        <v>121.86</v>
+        <v>114.09</v>
       </c>
     </row>
     <row r="54">
@@ -2362,13 +2362,13 @@
         <v>28</v>
       </c>
       <c r="J55" t="n">
-        <v>45.9</v>
+        <v>41.91</v>
       </c>
       <c r="K55" t="n">
-        <v>115.13</v>
+        <v>105.12</v>
       </c>
       <c r="L55" t="n">
-        <v>123.94</v>
+        <v>113.16</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>26</v>
       </c>
       <c r="J56" t="n">
-        <v>-93.14</v>
+        <v>-89.26000000000001</v>
       </c>
       <c r="K56" t="n">
-        <v>-166.74</v>
+        <v>-159.79</v>
       </c>
       <c r="L56" t="n">
-        <v>190.99</v>
+        <v>183.04</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>25</v>
       </c>
       <c r="J57" t="n">
-        <v>-193.38</v>
+        <v>-189.43</v>
       </c>
       <c r="K57" t="n">
-        <v>-117.22</v>
+        <v>-114.83</v>
       </c>
       <c r="L57" t="n">
-        <v>226.13</v>
+        <v>221.52</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>23</v>
       </c>
       <c r="J58" t="n">
-        <v>-26.63</v>
+        <v>-27.15</v>
       </c>
       <c r="K58" t="n">
-        <v>225.09</v>
+        <v>229.51</v>
       </c>
       <c r="L58" t="n">
-        <v>226.66</v>
+        <v>231.11</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>28</v>
       </c>
       <c r="J59" t="n">
-        <v>52.15</v>
+        <v>47.62</v>
       </c>
       <c r="K59" t="n">
-        <v>1.03</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L59" t="n">
-        <v>52.16</v>
+        <v>47.63</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>25</v>
       </c>
       <c r="J60" t="n">
-        <v>-48.59</v>
+        <v>-47.6</v>
       </c>
       <c r="K60" t="n">
-        <v>-1.76</v>
+        <v>-1.73</v>
       </c>
       <c r="L60" t="n">
-        <v>48.63</v>
+        <v>47.63</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>28</v>
       </c>
       <c r="J61" t="n">
-        <v>-49.06</v>
+        <v>-44.8</v>
       </c>
       <c r="K61" t="n">
-        <v>11.57</v>
+        <v>10.56</v>
       </c>
       <c r="L61" t="n">
-        <v>50.41</v>
+        <v>46.03</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>27</v>
       </c>
       <c r="J62" t="n">
-        <v>18.69</v>
+        <v>17.49</v>
       </c>
       <c r="K62" t="n">
-        <v>76.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="L62" t="n">
-        <v>79.04000000000001</v>
+        <v>73.98999999999999</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>27</v>
       </c>
       <c r="J63" t="n">
-        <v>5.3</v>
+        <v>4.96</v>
       </c>
       <c r="K63" t="n">
-        <v>73.93000000000001</v>
+        <v>69.20999999999999</v>
       </c>
       <c r="L63" t="n">
-        <v>74.12</v>
+        <v>69.39</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>28</v>
       </c>
       <c r="J64" t="n">
-        <v>-29.8</v>
+        <v>-27.21</v>
       </c>
       <c r="K64" t="n">
-        <v>-44.59</v>
+        <v>-40.72</v>
       </c>
       <c r="L64" t="n">
-        <v>53.64</v>
+        <v>48.97</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>120.22</v>
+        <v>124.84</v>
       </c>
       <c r="K65" t="n">
-        <v>23.45</v>
+        <v>24.36</v>
       </c>
       <c r="L65" t="n">
-        <v>122.48</v>
+        <v>127.19</v>
       </c>
     </row>
     <row r="66">
@@ -2908,13 +2908,13 @@
         <v>25</v>
       </c>
       <c r="J68" t="n">
-        <v>-7.06</v>
+        <v>-6.92</v>
       </c>
       <c r="K68" t="n">
-        <v>-95.65000000000001</v>
+        <v>-93.7</v>
       </c>
       <c r="L68" t="n">
-        <v>95.91</v>
+        <v>93.95</v>
       </c>
     </row>
     <row r="69">
@@ -2992,13 +2992,13 @@
         <v>26</v>
       </c>
       <c r="J70" t="n">
-        <v>137.21</v>
+        <v>131.49</v>
       </c>
       <c r="K70" t="n">
-        <v>-132.4</v>
+        <v>-126.89</v>
       </c>
       <c r="L70" t="n">
-        <v>190.67</v>
+        <v>182.73</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>-161.81</v>
+        <v>-168.03</v>
       </c>
       <c r="K71" t="n">
-        <v>207.17</v>
+        <v>215.14</v>
       </c>
       <c r="L71" t="n">
-        <v>262.87</v>
+        <v>272.98</v>
       </c>
     </row>
     <row r="72">
@@ -3118,13 +3118,13 @@
         <v>26</v>
       </c>
       <c r="J73" t="n">
-        <v>-56.53</v>
+        <v>-54.17</v>
       </c>
       <c r="K73" t="n">
-        <v>-186.49</v>
+        <v>-178.72</v>
       </c>
       <c r="L73" t="n">
-        <v>194.87</v>
+        <v>186.75</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>27</v>
       </c>
       <c r="J74" t="n">
-        <v>-46.75</v>
+        <v>-43.77</v>
       </c>
       <c r="K74" t="n">
-        <v>-15.48</v>
+        <v>-14.5</v>
       </c>
       <c r="L74" t="n">
-        <v>49.25</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>28</v>
       </c>
       <c r="J75" t="n">
-        <v>-8.31</v>
+        <v>-7.58</v>
       </c>
       <c r="K75" t="n">
-        <v>-50.69</v>
+        <v>-46.28</v>
       </c>
       <c r="L75" t="n">
-        <v>51.37</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>27</v>
       </c>
       <c r="J76" t="n">
-        <v>32.82</v>
+        <v>30.73</v>
       </c>
       <c r="K76" t="n">
-        <v>-68.69</v>
+        <v>-64.31</v>
       </c>
       <c r="L76" t="n">
-        <v>76.13</v>
+        <v>71.27</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>27</v>
       </c>
       <c r="J77" t="n">
-        <v>-20.75</v>
+        <v>-19.43</v>
       </c>
       <c r="K77" t="n">
-        <v>51.83</v>
+        <v>48.53</v>
       </c>
       <c r="L77" t="n">
-        <v>55.83</v>
+        <v>52.27</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>28</v>
       </c>
       <c r="J78" t="n">
-        <v>13.13</v>
+        <v>11.98</v>
       </c>
       <c r="K78" t="n">
-        <v>-63.36</v>
+        <v>-57.85</v>
       </c>
       <c r="L78" t="n">
-        <v>64.70999999999999</v>
+        <v>59.08</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>28</v>
       </c>
       <c r="J79" t="n">
-        <v>-61.24</v>
+        <v>-55.92</v>
       </c>
       <c r="K79" t="n">
-        <v>-20.8</v>
+        <v>-18.99</v>
       </c>
       <c r="L79" t="n">
-        <v>64.68000000000001</v>
+        <v>59.05</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>-145.64</v>
+        <v>-148.49</v>
       </c>
       <c r="K80" t="n">
-        <v>-7.69</v>
+        <v>-7.84</v>
       </c>
       <c r="L80" t="n">
-        <v>145.84</v>
+        <v>148.7</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>27</v>
       </c>
       <c r="J81" t="n">
-        <v>66.33</v>
+        <v>62.1</v>
       </c>
       <c r="K81" t="n">
-        <v>78.94</v>
+        <v>73.91</v>
       </c>
       <c r="L81" t="n">
-        <v>103.11</v>
+        <v>96.53</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>-63.41</v>
+        <v>-62.12</v>
       </c>
       <c r="K82" t="n">
-        <v>78.47</v>
+        <v>76.87</v>
       </c>
       <c r="L82" t="n">
-        <v>100.89</v>
+        <v>98.83</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>23</v>
       </c>
       <c r="J83" t="n">
-        <v>108.78</v>
+        <v>110.91</v>
       </c>
       <c r="K83" t="n">
-        <v>-72.15000000000001</v>
+        <v>-73.56</v>
       </c>
       <c r="L83" t="n">
-        <v>130.53</v>
+        <v>133.09</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>23</v>
       </c>
       <c r="J84" t="n">
-        <v>-116.06</v>
+        <v>-118.33</v>
       </c>
       <c r="K84" t="n">
-        <v>-110.57</v>
+        <v>-112.74</v>
       </c>
       <c r="L84" t="n">
-        <v>160.3</v>
+        <v>163.44</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>26</v>
       </c>
       <c r="J85" t="n">
-        <v>-191.66</v>
+        <v>-183.67</v>
       </c>
       <c r="K85" t="n">
-        <v>3.92</v>
+        <v>3.76</v>
       </c>
       <c r="L85" t="n">
-        <v>191.7</v>
+        <v>183.71</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>40.35</v>
+        <v>39.53</v>
       </c>
       <c r="K86" t="n">
-        <v>-278.16</v>
+        <v>-272.48</v>
       </c>
       <c r="L86" t="n">
-        <v>281.07</v>
+        <v>275.33</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>28</v>
       </c>
       <c r="J87" t="n">
-        <v>-80.26000000000001</v>
+        <v>-73.28</v>
       </c>
       <c r="K87" t="n">
-        <v>-79.79000000000001</v>
+        <v>-72.84999999999999</v>
       </c>
       <c r="L87" t="n">
-        <v>113.17</v>
+        <v>103.33</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>24</v>
       </c>
       <c r="J88" t="n">
-        <v>-285.12</v>
+        <v>-285.59</v>
       </c>
       <c r="K88" t="n">
-        <v>-185.24</v>
+        <v>-185.55</v>
       </c>
       <c r="L88" t="n">
-        <v>340.02</v>
+        <v>340.58</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-05-25.xlsx
+++ b/output/2024-05-25.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2.16</v>
+        <v>2.6</v>
       </c>
       <c r="F14" t="n">
-        <v>4.16</v>
+        <v>6.81</v>
       </c>
       <c r="G14" t="n">
-        <v>233.9</v>
+        <v>242.3</v>
       </c>
       <c r="H14" t="n">
-        <v>15.3</v>
+        <v>43.1</v>
       </c>
       <c r="I14" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>41.2</v>
+        <v>-15.03</v>
       </c>
       <c r="K14" t="n">
-        <v>-5.59</v>
+        <v>-49.2</v>
       </c>
       <c r="L14" t="n">
-        <v>41.58</v>
+        <v>51.44</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:47:33</t>
+          <t>04:47:12</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2.52</v>
+        <v>2.05</v>
       </c>
       <c r="F15" t="n">
-        <v>6.04</v>
+        <v>5.7</v>
       </c>
       <c r="G15" t="n">
-        <v>222</v>
+        <v>248</v>
       </c>
       <c r="H15" t="n">
-        <v>21.2</v>
+        <v>50.8</v>
       </c>
       <c r="I15" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>54.2</v>
+        <v>28.54</v>
       </c>
       <c r="K15" t="n">
-        <v>-30.56</v>
+        <v>-13.56</v>
       </c>
       <c r="L15" t="n">
-        <v>62.23</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:49:05</t>
+          <t>04:48:46</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="F16" t="n">
-        <v>6.47</v>
+        <v>4.66</v>
       </c>
       <c r="G16" t="n">
-        <v>241.3</v>
+        <v>234.8</v>
       </c>
       <c r="H16" t="n">
-        <v>19.8</v>
+        <v>45.3</v>
       </c>
       <c r="I16" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J16" t="n">
-        <v>-23.3</v>
+        <v>-37.62</v>
       </c>
       <c r="K16" t="n">
-        <v>-45.62</v>
+        <v>25.5</v>
       </c>
       <c r="L16" t="n">
-        <v>51.22</v>
+        <v>45.45</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04:53:51</t>
+          <t>04:54:03</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -754,31 +754,31 @@
         <v>2.25</v>
       </c>
       <c r="F17" t="n">
-        <v>7.02</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>241.7</v>
+        <v>243.1</v>
       </c>
       <c r="H17" t="n">
-        <v>10.8</v>
+        <v>51</v>
       </c>
       <c r="I17" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>43.88</v>
+        <v>-51.45</v>
       </c>
       <c r="K17" t="n">
-        <v>-30.74</v>
+        <v>-53.7</v>
       </c>
       <c r="L17" t="n">
-        <v>53.57</v>
+        <v>74.37</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:55:39</t>
+          <t>04:55:29</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="F18" t="n">
-        <v>7.39</v>
+        <v>4.49</v>
       </c>
       <c r="G18" t="n">
-        <v>239.1</v>
+        <v>245.4</v>
       </c>
       <c r="H18" t="n">
-        <v>16</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J18" t="n">
-        <v>2.56</v>
+        <v>48.14</v>
       </c>
       <c r="K18" t="n">
-        <v>-80.13</v>
+        <v>60.61</v>
       </c>
       <c r="L18" t="n">
-        <v>80.18000000000001</v>
+        <v>77.40000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04:57:38</t>
+          <t>04:57:07</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>2.56</v>
+        <v>3.08</v>
       </c>
       <c r="F19" t="n">
-        <v>8.43</v>
+        <v>7.15</v>
       </c>
       <c r="G19" t="n">
-        <v>230.4</v>
+        <v>244.5</v>
       </c>
       <c r="H19" t="n">
-        <v>10.4</v>
+        <v>76.3</v>
       </c>
       <c r="I19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J19" t="n">
-        <v>-25.36</v>
+        <v>-42.87</v>
       </c>
       <c r="K19" t="n">
-        <v>64.43000000000001</v>
+        <v>-81.81</v>
       </c>
       <c r="L19" t="n">
-        <v>69.23999999999999</v>
+        <v>92.36</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>05:03:49</t>
+          <t>05:00:35</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>2.29</v>
+        <v>2.66</v>
       </c>
       <c r="F20" t="n">
-        <v>7.06</v>
+        <v>6.22</v>
       </c>
       <c r="G20" t="n">
-        <v>234.7</v>
+        <v>224.3</v>
       </c>
       <c r="H20" t="n">
-        <v>14.7</v>
+        <v>42.2</v>
       </c>
       <c r="I20" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J20" t="n">
-        <v>89</v>
+        <v>-52.24</v>
       </c>
       <c r="K20" t="n">
-        <v>-11.2</v>
+        <v>-43.84</v>
       </c>
       <c r="L20" t="n">
-        <v>89.70999999999999</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>05:05:11</t>
+          <t>05:02:49</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>3.33</v>
+        <v>2.53</v>
       </c>
       <c r="F21" t="n">
-        <v>8.74</v>
+        <v>7.92</v>
       </c>
       <c r="G21" t="n">
-        <v>239.4</v>
+        <v>240.1</v>
       </c>
       <c r="H21" t="n">
-        <v>13.8</v>
+        <v>50.9</v>
       </c>
       <c r="I21" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J21" t="n">
-        <v>-76.77</v>
+        <v>56.61</v>
       </c>
       <c r="K21" t="n">
-        <v>45.07</v>
+        <v>-94.36</v>
       </c>
       <c r="L21" t="n">
-        <v>89.02</v>
+        <v>110.04</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05:07:19</t>
+          <t>05:04:17</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>2.55</v>
+        <v>2.14</v>
       </c>
       <c r="F22" t="n">
-        <v>5.09</v>
+        <v>8.74</v>
       </c>
       <c r="G22" t="n">
-        <v>237</v>
+        <v>232.2</v>
       </c>
       <c r="H22" t="n">
-        <v>17.4</v>
+        <v>63</v>
       </c>
       <c r="I22" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J22" t="n">
-        <v>70.93000000000001</v>
+        <v>93.69</v>
       </c>
       <c r="K22" t="n">
-        <v>81.12</v>
+        <v>20.74</v>
       </c>
       <c r="L22" t="n">
-        <v>107.76</v>
+        <v>95.95999999999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05:13:02</t>
+          <t>05:08:59</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="F23" t="n">
-        <v>8.07</v>
+        <v>6.65</v>
       </c>
       <c r="G23" t="n">
-        <v>227.1</v>
+        <v>237.8</v>
       </c>
       <c r="H23" t="n">
-        <v>16.4</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J23" t="n">
-        <v>91.09</v>
+        <v>-123.58</v>
       </c>
       <c r="K23" t="n">
-        <v>-70.45</v>
+        <v>83.23999999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>115.16</v>
+        <v>148.99</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:15:24</t>
+          <t>05:10:44</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="F24" t="n">
-        <v>5.37</v>
+        <v>5.01</v>
       </c>
       <c r="G24" t="n">
-        <v>243.6</v>
+        <v>249.8</v>
       </c>
       <c r="H24" t="n">
-        <v>14.8</v>
+        <v>55.2</v>
       </c>
       <c r="I24" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="J24" t="n">
-        <v>-106.27</v>
+        <v>29.01</v>
       </c>
       <c r="K24" t="n">
-        <v>23.31</v>
+        <v>136.18</v>
       </c>
       <c r="L24" t="n">
-        <v>108.8</v>
+        <v>139.23</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:17:16</t>
+          <t>05:12:39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="F25" t="n">
-        <v>3.86</v>
+        <v>4.3</v>
       </c>
       <c r="G25" t="n">
-        <v>242.5</v>
+        <v>233.4</v>
       </c>
       <c r="H25" t="n">
-        <v>16.4</v>
+        <v>63.5</v>
       </c>
       <c r="I25" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J25" t="n">
-        <v>-128.84</v>
+        <v>-131.82</v>
       </c>
       <c r="K25" t="n">
-        <v>-8.619999999999999</v>
+        <v>-45.82</v>
       </c>
       <c r="L25" t="n">
-        <v>129.13</v>
+        <v>139.56</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:22:01</t>
+          <t>05:15:47</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>2.51</v>
+        <v>2.61</v>
       </c>
       <c r="F26" t="n">
-        <v>6.1</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="G26" t="n">
-        <v>249.7</v>
+        <v>241.9</v>
       </c>
       <c r="H26" t="n">
-        <v>14.7</v>
+        <v>44.1</v>
       </c>
       <c r="I26" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J26" t="n">
-        <v>-193.05</v>
+        <v>-164.1</v>
       </c>
       <c r="K26" t="n">
-        <v>6.91</v>
+        <v>107.69</v>
       </c>
       <c r="L26" t="n">
-        <v>193.18</v>
+        <v>196.28</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:23:16</t>
+          <t>05:17:18</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2.88</v>
+        <v>2.13</v>
       </c>
       <c r="F27" t="n">
-        <v>8.1</v>
+        <v>5.16</v>
       </c>
       <c r="G27" t="n">
-        <v>239.3</v>
+        <v>228.7</v>
       </c>
       <c r="H27" t="n">
-        <v>13.9</v>
+        <v>38.4</v>
       </c>
       <c r="I27" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J27" t="n">
-        <v>-44.95</v>
+        <v>36.19</v>
       </c>
       <c r="K27" t="n">
-        <v>186.1</v>
+        <v>83.5</v>
       </c>
       <c r="L27" t="n">
-        <v>191.45</v>
+        <v>91.01000000000001</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:25:41</t>
+          <t>05:18:36</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>3.35</v>
+        <v>2.13</v>
       </c>
       <c r="F28" t="n">
-        <v>6.16</v>
+        <v>3.34</v>
       </c>
       <c r="G28" t="n">
-        <v>254.1</v>
+        <v>228.1</v>
       </c>
       <c r="H28" t="n">
         <v>14.6</v>
       </c>
       <c r="I28" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>68.54000000000001</v>
+        <v>3.23</v>
       </c>
       <c r="K28" t="n">
-        <v>-118.59</v>
+        <v>177.5</v>
       </c>
       <c r="L28" t="n">
-        <v>136.97</v>
+        <v>177.53</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:33:54</t>
+          <t>05:29:45</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>2.34</v>
+        <v>2.13</v>
       </c>
       <c r="F29" t="n">
-        <v>8.74</v>
+        <v>3.32</v>
       </c>
       <c r="G29" t="n">
-        <v>238</v>
+        <v>222.7</v>
       </c>
       <c r="H29" t="n">
-        <v>16.7</v>
+        <v>34.1</v>
       </c>
       <c r="I29" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J29" t="n">
-        <v>-30.25</v>
+        <v>-25.21</v>
       </c>
       <c r="K29" t="n">
-        <v>-56.86</v>
+        <v>38.96</v>
       </c>
       <c r="L29" t="n">
-        <v>64.40000000000001</v>
+        <v>46.41</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:35:53</t>
+          <t>05:30:35</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="F30" t="n">
-        <v>5.48</v>
+        <v>7.04</v>
       </c>
       <c r="G30" t="n">
-        <v>237.4</v>
+        <v>240.6</v>
       </c>
       <c r="H30" t="n">
-        <v>7.6</v>
+        <v>43.2</v>
       </c>
       <c r="I30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J30" t="n">
-        <v>-44.22</v>
+        <v>3.32</v>
       </c>
       <c r="K30" t="n">
-        <v>-14.23</v>
+        <v>34.56</v>
       </c>
       <c r="L30" t="n">
-        <v>46.45</v>
+        <v>34.72</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:37:05</t>
+          <t>05:32:27</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>3.34</v>
+        <v>2.49</v>
       </c>
       <c r="F31" t="n">
-        <v>6.05</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="G31" t="n">
-        <v>238.5</v>
+        <v>239</v>
       </c>
       <c r="H31" t="n">
-        <v>13.5</v>
+        <v>40.2</v>
       </c>
       <c r="I31" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>-26.68</v>
+        <v>32.2</v>
       </c>
       <c r="K31" t="n">
-        <v>-43.59</v>
+        <v>4.73</v>
       </c>
       <c r="L31" t="n">
-        <v>51.1</v>
+        <v>32.54</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:41:54</t>
+          <t>05:38:17</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="F32" t="n">
-        <v>8.74</v>
+        <v>4.28</v>
       </c>
       <c r="G32" t="n">
-        <v>237.3</v>
+        <v>217.4</v>
       </c>
       <c r="H32" t="n">
-        <v>12.2</v>
+        <v>61.3</v>
       </c>
       <c r="I32" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J32" t="n">
-        <v>-22.28</v>
+        <v>58.25</v>
       </c>
       <c r="K32" t="n">
-        <v>47.47</v>
+        <v>25.52</v>
       </c>
       <c r="L32" t="n">
-        <v>52.44</v>
+        <v>63.59</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:43:15</t>
+          <t>05:40:04</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>2.58</v>
+        <v>2.44</v>
       </c>
       <c r="F33" t="n">
-        <v>7.81</v>
+        <v>8.74</v>
       </c>
       <c r="G33" t="n">
-        <v>233.1</v>
+        <v>230.3</v>
       </c>
       <c r="H33" t="n">
-        <v>13.9</v>
+        <v>33.2</v>
       </c>
       <c r="I33" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>71.81999999999999</v>
+        <v>59.8</v>
       </c>
       <c r="K33" t="n">
-        <v>42.57</v>
+        <v>25.92</v>
       </c>
       <c r="L33" t="n">
-        <v>83.48999999999999</v>
+        <v>65.18000000000001</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:44:34</t>
+          <t>05:42:10</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="F34" t="n">
-        <v>5.54</v>
+        <v>6.07</v>
       </c>
       <c r="G34" t="n">
-        <v>245.3</v>
+        <v>231.6</v>
       </c>
       <c r="H34" t="n">
-        <v>12.5</v>
+        <v>33.7</v>
       </c>
       <c r="I34" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J34" t="n">
-        <v>-47.82</v>
+        <v>1.45</v>
       </c>
       <c r="K34" t="n">
-        <v>-29.45</v>
+        <v>-57.14</v>
       </c>
       <c r="L34" t="n">
-        <v>56.16</v>
+        <v>57.16</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:49:57</t>
+          <t>05:48:25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>2.97</v>
+        <v>2.18</v>
       </c>
       <c r="F35" t="n">
-        <v>8.74</v>
+        <v>4.31</v>
       </c>
       <c r="G35" t="n">
-        <v>235.3</v>
+        <v>239.6</v>
       </c>
       <c r="H35" t="n">
-        <v>14.5</v>
+        <v>32.9</v>
       </c>
       <c r="I35" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J35" t="n">
-        <v>89.5</v>
+        <v>-22.15</v>
       </c>
       <c r="K35" t="n">
-        <v>-84.43000000000001</v>
+        <v>95.84999999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>123.04</v>
+        <v>98.37</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:51:29</t>
+          <t>05:49:13</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2.36</v>
+        <v>2.23</v>
       </c>
       <c r="F36" t="n">
-        <v>6.48</v>
+        <v>5.29</v>
       </c>
       <c r="G36" t="n">
-        <v>245.8</v>
+        <v>229</v>
       </c>
       <c r="H36" t="n">
-        <v>11.5</v>
+        <v>31.3</v>
       </c>
       <c r="I36" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J36" t="n">
-        <v>-78.84</v>
+        <v>47.67</v>
       </c>
       <c r="K36" t="n">
-        <v>20.7</v>
+        <v>-31.77</v>
       </c>
       <c r="L36" t="n">
-        <v>81.51000000000001</v>
+        <v>57.29</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:53:34</t>
+          <t>05:51:18</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>2.15</v>
+        <v>2.64</v>
       </c>
       <c r="F37" t="n">
-        <v>6.34</v>
+        <v>6.25</v>
       </c>
       <c r="G37" t="n">
-        <v>232</v>
+        <v>249.6</v>
       </c>
       <c r="H37" t="n">
-        <v>9.6</v>
+        <v>36.2</v>
       </c>
       <c r="I37" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J37" t="n">
-        <v>19.4</v>
+        <v>48.34</v>
       </c>
       <c r="K37" t="n">
-        <v>-113.34</v>
+        <v>67.59</v>
       </c>
       <c r="L37" t="n">
-        <v>114.99</v>
+        <v>83.09999999999999</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05:58:22</t>
+          <t>05:56:30</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2.21</v>
+        <v>2.77</v>
       </c>
       <c r="F38" t="n">
-        <v>7.05</v>
+        <v>8.74</v>
       </c>
       <c r="G38" t="n">
-        <v>238</v>
+        <v>235.6</v>
       </c>
       <c r="H38" t="n">
-        <v>6.3</v>
+        <v>39.4</v>
       </c>
       <c r="I38" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J38" t="n">
-        <v>94.06</v>
+        <v>32.8</v>
       </c>
       <c r="K38" t="n">
-        <v>-122.69</v>
+        <v>-148.12</v>
       </c>
       <c r="L38" t="n">
-        <v>154.6</v>
+        <v>151.7</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06:00:10</t>
+          <t>05:58:41</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="F39" t="n">
-        <v>5.15</v>
+        <v>7.53</v>
       </c>
       <c r="G39" t="n">
-        <v>242.5</v>
+        <v>254.1</v>
       </c>
       <c r="H39" t="n">
-        <v>18.4</v>
+        <v>64.7</v>
       </c>
       <c r="I39" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J39" t="n">
-        <v>29.12</v>
+        <v>-77.25</v>
       </c>
       <c r="K39" t="n">
-        <v>-146.56</v>
+        <v>17.37</v>
       </c>
       <c r="L39" t="n">
-        <v>149.43</v>
+        <v>79.18000000000001</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06:00:49</t>
+          <t>05:59:53</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>2.28</v>
+        <v>2.14</v>
       </c>
       <c r="F40" t="n">
-        <v>6.66</v>
+        <v>7.6</v>
       </c>
       <c r="G40" t="n">
-        <v>236.6</v>
+        <v>234.8</v>
       </c>
       <c r="H40" t="n">
-        <v>12.7</v>
+        <v>3.7</v>
       </c>
       <c r="I40" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J40" t="n">
-        <v>-32.9</v>
+        <v>33.75</v>
       </c>
       <c r="K40" t="n">
-        <v>76.51000000000001</v>
+        <v>-133.42</v>
       </c>
       <c r="L40" t="n">
-        <v>83.28</v>
+        <v>137.62</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06:05:11</t>
+          <t>06:04:25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>2.51</v>
+        <v>2.65</v>
       </c>
       <c r="F41" t="n">
-        <v>7.9</v>
+        <v>7.12</v>
       </c>
       <c r="G41" t="n">
-        <v>237.2</v>
+        <v>224</v>
       </c>
       <c r="H41" t="n">
-        <v>11.3</v>
+        <v>30.1</v>
       </c>
       <c r="I41" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J41" t="n">
-        <v>-176.25</v>
+        <v>-80.20999999999999</v>
       </c>
       <c r="K41" t="n">
-        <v>198.09</v>
+        <v>-160.37</v>
       </c>
       <c r="L41" t="n">
-        <v>265.15</v>
+        <v>179.31</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06:07:14</t>
+          <t>06:06:53</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>2.15</v>
+        <v>2.48</v>
       </c>
       <c r="F42" t="n">
-        <v>4.49</v>
+        <v>6.06</v>
       </c>
       <c r="G42" t="n">
-        <v>233.7</v>
+        <v>237.8</v>
       </c>
       <c r="H42" t="n">
-        <v>22.3</v>
+        <v>35.7</v>
       </c>
       <c r="I42" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J42" t="n">
-        <v>-124.88</v>
+        <v>-35.66</v>
       </c>
       <c r="K42" t="n">
-        <v>-19.18</v>
+        <v>205.1</v>
       </c>
       <c r="L42" t="n">
-        <v>126.34</v>
+        <v>208.17</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06:08:46</t>
+          <t>06:08:51</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="F43" t="n">
-        <v>2.7</v>
+        <v>6.68</v>
       </c>
       <c r="G43" t="n">
-        <v>246</v>
+        <v>234.7</v>
       </c>
       <c r="H43" t="n">
-        <v>13.6</v>
+        <v>0.7</v>
       </c>
       <c r="I43" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="J43" t="n">
-        <v>-75.5</v>
+        <v>133.77</v>
       </c>
       <c r="K43" t="n">
-        <v>97.04000000000001</v>
+        <v>139.05</v>
       </c>
       <c r="L43" t="n">
-        <v>122.95</v>
+        <v>192.95</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:19:49</t>
+          <t>06:19:20</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>2.24</v>
+        <v>2.8</v>
       </c>
       <c r="F44" t="n">
-        <v>5.46</v>
+        <v>8.74</v>
       </c>
       <c r="G44" t="n">
-        <v>236.2</v>
+        <v>239.9</v>
       </c>
       <c r="H44" t="n">
-        <v>8.800000000000001</v>
+        <v>55.5</v>
       </c>
       <c r="I44" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J44" t="n">
-        <v>4.76</v>
+        <v>-56.04</v>
       </c>
       <c r="K44" t="n">
-        <v>44.83</v>
+        <v>-22.69</v>
       </c>
       <c r="L44" t="n">
-        <v>45.08</v>
+        <v>60.46</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:21:35</t>
+          <t>06:21:15</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>2.33</v>
+        <v>2.52</v>
       </c>
       <c r="F45" t="n">
-        <v>5.59</v>
+        <v>8.74</v>
       </c>
       <c r="G45" t="n">
-        <v>243</v>
+        <v>231.4</v>
       </c>
       <c r="H45" t="n">
-        <v>14.4</v>
+        <v>55.6</v>
       </c>
       <c r="I45" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>-33.28</v>
+        <v>-23.39</v>
       </c>
       <c r="K45" t="n">
-        <v>37.66</v>
+        <v>-20.12</v>
       </c>
       <c r="L45" t="n">
-        <v>50.25</v>
+        <v>30.85</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:24:00</t>
+          <t>06:23:10</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="F46" t="n">
-        <v>5.27</v>
+        <v>8.74</v>
       </c>
       <c r="G46" t="n">
-        <v>235.1</v>
+        <v>240.5</v>
       </c>
       <c r="H46" t="n">
-        <v>15.5</v>
+        <v>36.2</v>
       </c>
       <c r="I46" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J46" t="n">
-        <v>38.43</v>
+        <v>28.63</v>
       </c>
       <c r="K46" t="n">
-        <v>-34.98</v>
+        <v>-44.1</v>
       </c>
       <c r="L46" t="n">
-        <v>51.97</v>
+        <v>52.58</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:29:37</t>
+          <t>06:26:52</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>2.46</v>
+        <v>2.73</v>
       </c>
       <c r="F47" t="n">
         <v>8.74</v>
       </c>
       <c r="G47" t="n">
-        <v>228.1</v>
+        <v>250.5</v>
       </c>
       <c r="H47" t="n">
-        <v>8.6</v>
+        <v>28.1</v>
       </c>
       <c r="I47" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J47" t="n">
-        <v>-45.45</v>
+        <v>15.63</v>
       </c>
       <c r="K47" t="n">
-        <v>-62.01</v>
+        <v>71.88</v>
       </c>
       <c r="L47" t="n">
-        <v>76.89</v>
+        <v>73.56</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:31:09</t>
+          <t>06:28:06</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>2.69</v>
+        <v>2.19</v>
       </c>
       <c r="F48" t="n">
-        <v>7.17</v>
+        <v>8.74</v>
       </c>
       <c r="G48" t="n">
-        <v>239.2</v>
+        <v>235.8</v>
       </c>
       <c r="H48" t="n">
-        <v>14.7</v>
+        <v>57.9</v>
       </c>
       <c r="I48" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>21.79</v>
+        <v>-70.39</v>
       </c>
       <c r="K48" t="n">
-        <v>-105.19</v>
+        <v>-35.94</v>
       </c>
       <c r="L48" t="n">
-        <v>107.43</v>
+        <v>79.04000000000001</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:32:54</t>
+          <t>06:29:41</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>3.04</v>
+        <v>2.78</v>
       </c>
       <c r="F49" t="n">
-        <v>8.74</v>
+        <v>8.17</v>
       </c>
       <c r="G49" t="n">
-        <v>249.8</v>
+        <v>242.7</v>
       </c>
       <c r="H49" t="n">
-        <v>13.8</v>
+        <v>41.4</v>
       </c>
       <c r="I49" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J49" t="n">
-        <v>-38.51</v>
+        <v>67.86</v>
       </c>
       <c r="K49" t="n">
-        <v>-45.49</v>
+        <v>-22.89</v>
       </c>
       <c r="L49" t="n">
-        <v>59.6</v>
+        <v>71.61</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:37:22</t>
+          <t>06:35:26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>1.85</v>
+        <v>3</v>
       </c>
       <c r="F50" t="n">
-        <v>3.01</v>
+        <v>8.74</v>
       </c>
       <c r="G50" t="n">
-        <v>238.9</v>
+        <v>242.8</v>
       </c>
       <c r="H50" t="n">
-        <v>14.4</v>
+        <v>21.3</v>
       </c>
       <c r="I50" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J50" t="n">
-        <v>78.48999999999999</v>
+        <v>-98.56</v>
       </c>
       <c r="K50" t="n">
-        <v>-5.14</v>
+        <v>-64.55</v>
       </c>
       <c r="L50" t="n">
-        <v>78.66</v>
+        <v>117.82</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:38:30</t>
+          <t>06:37:42</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="F51" t="n">
-        <v>6.74</v>
+        <v>8.74</v>
       </c>
       <c r="G51" t="n">
-        <v>242.4</v>
+        <v>239.9</v>
       </c>
       <c r="H51" t="n">
-        <v>12</v>
+        <v>28.2</v>
       </c>
       <c r="I51" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J51" t="n">
-        <v>-67.26000000000001</v>
+        <v>63.46</v>
       </c>
       <c r="K51" t="n">
-        <v>-35.92</v>
+        <v>-72.53</v>
       </c>
       <c r="L51" t="n">
-        <v>76.25</v>
+        <v>96.37</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:39:55</t>
+          <t>06:38:59</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>2.44</v>
+        <v>2.62</v>
       </c>
       <c r="F52" t="n">
-        <v>8.27</v>
+        <v>8.74</v>
       </c>
       <c r="G52" t="n">
-        <v>235.1</v>
+        <v>233.1</v>
       </c>
       <c r="H52" t="n">
-        <v>18.2</v>
+        <v>23.7</v>
       </c>
       <c r="I52" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J52" t="n">
-        <v>-97.84</v>
+        <v>2.48</v>
       </c>
       <c r="K52" t="n">
-        <v>-97</v>
+        <v>-102.01</v>
       </c>
       <c r="L52" t="n">
-        <v>137.77</v>
+        <v>102.04</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:44:59</t>
+          <t>06:45:04</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>2.27</v>
+        <v>2.83</v>
       </c>
       <c r="F53" t="n">
-        <v>8.74</v>
+        <v>6.75</v>
       </c>
       <c r="G53" t="n">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="H53" t="n">
-        <v>11.6</v>
+        <v>58</v>
       </c>
       <c r="I53" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>-81.16</v>
+        <v>186.11</v>
       </c>
       <c r="K53" t="n">
-        <v>-80.18000000000001</v>
+        <v>-22.67</v>
       </c>
       <c r="L53" t="n">
-        <v>114.09</v>
+        <v>187.48</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:47:03</t>
+          <t>06:46:44</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>2.24</v>
+        <v>2.76</v>
       </c>
       <c r="F54" t="n">
-        <v>8.66</v>
+        <v>6.79</v>
       </c>
       <c r="G54" t="n">
-        <v>231.8</v>
+        <v>237.8</v>
       </c>
       <c r="H54" t="n">
-        <v>13.9</v>
+        <v>69.5</v>
       </c>
       <c r="I54" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J54" t="n">
-        <v>-78.65000000000001</v>
+        <v>48.45</v>
       </c>
       <c r="K54" t="n">
-        <v>130.5</v>
+        <v>143.69</v>
       </c>
       <c r="L54" t="n">
-        <v>152.36</v>
+        <v>151.64</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:48:34</t>
+          <t>06:48:24</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>2.91</v>
+        <v>2.53</v>
       </c>
       <c r="F55" t="n">
-        <v>5.9</v>
+        <v>7.81</v>
       </c>
       <c r="G55" t="n">
-        <v>235.1</v>
+        <v>226.5</v>
       </c>
       <c r="H55" t="n">
-        <v>15</v>
+        <v>46.3</v>
       </c>
       <c r="I55" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>41.91</v>
+        <v>-50.95</v>
       </c>
       <c r="K55" t="n">
-        <v>105.12</v>
+        <v>-157.44</v>
       </c>
       <c r="L55" t="n">
-        <v>113.16</v>
+        <v>165.48</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:53:52</t>
+          <t>06:53:46</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>3.1</v>
+        <v>2.77</v>
       </c>
       <c r="F56" t="n">
         <v>8.74</v>
       </c>
       <c r="G56" t="n">
-        <v>239.9</v>
+        <v>237.2</v>
       </c>
       <c r="H56" t="n">
-        <v>13.4</v>
+        <v>19.4</v>
       </c>
       <c r="I56" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J56" t="n">
-        <v>-89.26000000000001</v>
+        <v>-54.29</v>
       </c>
       <c r="K56" t="n">
-        <v>-159.79</v>
+        <v>164.85</v>
       </c>
       <c r="L56" t="n">
-        <v>183.04</v>
+        <v>173.56</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06:55:53</t>
+          <t>06:54:40</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>2.78</v>
+        <v>3.09</v>
       </c>
       <c r="F57" t="n">
-        <v>7.21</v>
+        <v>8.74</v>
       </c>
       <c r="G57" t="n">
-        <v>237.8</v>
+        <v>250</v>
       </c>
       <c r="H57" t="n">
-        <v>15.2</v>
+        <v>34.7</v>
       </c>
       <c r="I57" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J57" t="n">
-        <v>-189.43</v>
+        <v>-196.08</v>
       </c>
       <c r="K57" t="n">
-        <v>-114.83</v>
+        <v>215.68</v>
       </c>
       <c r="L57" t="n">
-        <v>221.52</v>
+        <v>291.49</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06:58:23</t>
+          <t>06:56:38</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>2.07</v>
+        <v>2.7</v>
       </c>
       <c r="F58" t="n">
-        <v>6.76</v>
+        <v>7.22</v>
       </c>
       <c r="G58" t="n">
-        <v>220.2</v>
+        <v>239.9</v>
       </c>
       <c r="H58" t="n">
-        <v>13.4</v>
+        <v>16.3</v>
       </c>
       <c r="I58" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J58" t="n">
-        <v>-27.15</v>
+        <v>-170.26</v>
       </c>
       <c r="K58" t="n">
-        <v>229.51</v>
+        <v>158.57</v>
       </c>
       <c r="L58" t="n">
-        <v>231.11</v>
+        <v>232.66</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07:08:44</t>
+          <t>07:07:06</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="F59" t="n">
-        <v>6.4</v>
+        <v>6.76</v>
       </c>
       <c r="G59" t="n">
-        <v>234.9</v>
+        <v>233.4</v>
       </c>
       <c r="H59" t="n">
-        <v>18.4</v>
+        <v>9.4</v>
       </c>
       <c r="I59" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="J59" t="n">
-        <v>47.62</v>
+        <v>-29.33</v>
       </c>
       <c r="K59" t="n">
-        <v>0.9399999999999999</v>
+        <v>-35.2</v>
       </c>
       <c r="L59" t="n">
-        <v>47.63</v>
+        <v>45.82</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07:10:23</t>
+          <t>07:08:31</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>2.88</v>
+        <v>2.57</v>
       </c>
       <c r="F60" t="n">
-        <v>8.74</v>
+        <v>7.66</v>
       </c>
       <c r="G60" t="n">
-        <v>241.2</v>
+        <v>244.3</v>
       </c>
       <c r="H60" t="n">
-        <v>14.6</v>
+        <v>52.6</v>
       </c>
       <c r="I60" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>-47.6</v>
+        <v>-30.25</v>
       </c>
       <c r="K60" t="n">
-        <v>-1.73</v>
+        <v>-32.83</v>
       </c>
       <c r="L60" t="n">
-        <v>47.63</v>
+        <v>44.64</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07:11:41</t>
+          <t>07:10:26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>2.51</v>
+        <v>2.41</v>
       </c>
       <c r="F61" t="n">
-        <v>7.1</v>
+        <v>5.96</v>
       </c>
       <c r="G61" t="n">
-        <v>223.9</v>
+        <v>226.4</v>
       </c>
       <c r="H61" t="n">
-        <v>6.8</v>
+        <v>51.3</v>
       </c>
       <c r="I61" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>-44.8</v>
+        <v>9.92</v>
       </c>
       <c r="K61" t="n">
-        <v>10.56</v>
+        <v>-31.51</v>
       </c>
       <c r="L61" t="n">
-        <v>46.03</v>
+        <v>33.04</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:15:01</t>
+          <t>07:15:37</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="F62" t="n">
-        <v>8.699999999999999</v>
+        <v>6.37</v>
       </c>
       <c r="G62" t="n">
-        <v>216</v>
+        <v>241.4</v>
       </c>
       <c r="H62" t="n">
-        <v>14.1</v>
+        <v>36</v>
       </c>
       <c r="I62" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J62" t="n">
-        <v>17.49</v>
+        <v>-44.52</v>
       </c>
       <c r="K62" t="n">
-        <v>71.90000000000001</v>
+        <v>24.62</v>
       </c>
       <c r="L62" t="n">
-        <v>73.98999999999999</v>
+        <v>50.87</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:17:13</t>
+          <t>07:17:18</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="F63" t="n">
-        <v>8.449999999999999</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="G63" t="n">
-        <v>245.8</v>
+        <v>234.8</v>
       </c>
       <c r="H63" t="n">
-        <v>19.6</v>
+        <v>49</v>
       </c>
       <c r="I63" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="J63" t="n">
-        <v>4.96</v>
+        <v>-1.94</v>
       </c>
       <c r="K63" t="n">
-        <v>69.20999999999999</v>
+        <v>-93.26000000000001</v>
       </c>
       <c r="L63" t="n">
-        <v>69.39</v>
+        <v>93.28</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:19:18</t>
+          <t>07:19:16</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>2.93</v>
+        <v>2.66</v>
       </c>
       <c r="F64" t="n">
-        <v>8.74</v>
+        <v>7.12</v>
       </c>
       <c r="G64" t="n">
-        <v>243.8</v>
+        <v>246.3</v>
       </c>
       <c r="H64" t="n">
-        <v>12.1</v>
+        <v>22.7</v>
       </c>
       <c r="I64" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>-27.21</v>
+        <v>-34.51</v>
       </c>
       <c r="K64" t="n">
-        <v>-40.72</v>
+        <v>36.9</v>
       </c>
       <c r="L64" t="n">
-        <v>48.97</v>
+        <v>50.52</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:23:31</t>
+          <t>07:23:59</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>2.92</v>
+        <v>3.18</v>
       </c>
       <c r="F65" t="n">
-        <v>7.41</v>
+        <v>8.74</v>
       </c>
       <c r="G65" t="n">
-        <v>241.6</v>
+        <v>247</v>
       </c>
       <c r="H65" t="n">
-        <v>14.9</v>
+        <v>22.6</v>
       </c>
       <c r="I65" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J65" t="n">
-        <v>124.84</v>
+        <v>84.66</v>
       </c>
       <c r="K65" t="n">
-        <v>24.36</v>
+        <v>-11.97</v>
       </c>
       <c r="L65" t="n">
-        <v>127.19</v>
+        <v>85.5</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:26:14</t>
+          <t>07:25:37</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>2.77</v>
+        <v>2.91</v>
       </c>
       <c r="F66" t="n">
-        <v>7.5</v>
+        <v>8.74</v>
       </c>
       <c r="G66" t="n">
-        <v>227.7</v>
+        <v>225.8</v>
       </c>
       <c r="H66" t="n">
-        <v>13.1</v>
+        <v>57.3</v>
       </c>
       <c r="I66" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>-108.71</v>
+        <v>-10.2</v>
       </c>
       <c r="K66" t="n">
-        <v>42.62</v>
+        <v>-110.57</v>
       </c>
       <c r="L66" t="n">
-        <v>116.76</v>
+        <v>111.04</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:27:23</t>
+          <t>07:26:56</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>2.75</v>
+        <v>2.43</v>
       </c>
       <c r="F67" t="n">
-        <v>8.06</v>
+        <v>6.76</v>
       </c>
       <c r="G67" t="n">
-        <v>239.3</v>
+        <v>242.1</v>
       </c>
       <c r="H67" t="n">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="I67" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J67" t="n">
-        <v>-121.1</v>
+        <v>-90.12</v>
       </c>
       <c r="K67" t="n">
-        <v>37.6</v>
+        <v>35.61</v>
       </c>
       <c r="L67" t="n">
-        <v>126.8</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:32:54</t>
+          <t>07:32:30</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="F68" t="n">
-        <v>4.71</v>
+        <v>7.03</v>
       </c>
       <c r="G68" t="n">
-        <v>228.4</v>
+        <v>237.3</v>
       </c>
       <c r="H68" t="n">
-        <v>19.2</v>
+        <v>29.7</v>
       </c>
       <c r="I68" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>-6.92</v>
+        <v>-136.95</v>
       </c>
       <c r="K68" t="n">
-        <v>-93.7</v>
+        <v>11.46</v>
       </c>
       <c r="L68" t="n">
-        <v>93.95</v>
+        <v>137.43</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:34:57</t>
+          <t>07:34:01</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>2.3</v>
+        <v>2.56</v>
       </c>
       <c r="F69" t="n">
-        <v>3.4</v>
+        <v>5.66</v>
       </c>
       <c r="G69" t="n">
-        <v>244.1</v>
+        <v>226.3</v>
       </c>
       <c r="H69" t="n">
-        <v>11.2</v>
+        <v>47</v>
       </c>
       <c r="I69" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J69" t="n">
-        <v>99.98</v>
+        <v>-116.35</v>
       </c>
       <c r="K69" t="n">
-        <v>-29.08</v>
+        <v>-99.84999999999999</v>
       </c>
       <c r="L69" t="n">
-        <v>104.12</v>
+        <v>153.32</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:35:52</t>
+          <t>07:35:42</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>3.11</v>
+        <v>2.59</v>
       </c>
       <c r="F70" t="n">
-        <v>8.74</v>
+        <v>5.08</v>
       </c>
       <c r="G70" t="n">
-        <v>228.2</v>
+        <v>251.9</v>
       </c>
       <c r="H70" t="n">
-        <v>15.4</v>
+        <v>76</v>
       </c>
       <c r="I70" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>131.49</v>
+        <v>127.68</v>
       </c>
       <c r="K70" t="n">
-        <v>-126.89</v>
+        <v>14.28</v>
       </c>
       <c r="L70" t="n">
-        <v>182.73</v>
+        <v>128.47</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:40:01</t>
+          <t>07:41:01</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>2.39</v>
+        <v>3.2</v>
       </c>
       <c r="F71" t="n">
-        <v>6.45</v>
+        <v>8.74</v>
       </c>
       <c r="G71" t="n">
-        <v>241.4</v>
+        <v>225.6</v>
       </c>
       <c r="H71" t="n">
-        <v>19.6</v>
+        <v>50.2</v>
       </c>
       <c r="I71" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J71" t="n">
-        <v>-168.03</v>
+        <v>-429.61</v>
       </c>
       <c r="K71" t="n">
-        <v>215.14</v>
+        <v>-105.98</v>
       </c>
       <c r="L71" t="n">
-        <v>272.98</v>
+        <v>442.49</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:42:29</t>
+          <t>07:43:06</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>2.67</v>
+        <v>2.59</v>
       </c>
       <c r="F72" t="n">
-        <v>8.74</v>
+        <v>6.85</v>
       </c>
       <c r="G72" t="n">
-        <v>233.6</v>
+        <v>223.1</v>
       </c>
       <c r="H72" t="n">
-        <v>11.4</v>
+        <v>21</v>
       </c>
       <c r="I72" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>127.8</v>
+        <v>-96.51000000000001</v>
       </c>
       <c r="K72" t="n">
-        <v>-236.91</v>
+        <v>-104.79</v>
       </c>
       <c r="L72" t="n">
-        <v>269.18</v>
+        <v>142.46</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:43:45</t>
+          <t>07:44:47</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>3.19</v>
+        <v>2.57</v>
       </c>
       <c r="F73" t="n">
         <v>8.74</v>
       </c>
       <c r="G73" t="n">
-        <v>231.3</v>
+        <v>231.2</v>
       </c>
       <c r="H73" t="n">
-        <v>11.6</v>
+        <v>42.1</v>
       </c>
       <c r="I73" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>-54.17</v>
+        <v>98.47</v>
       </c>
       <c r="K73" t="n">
-        <v>-178.72</v>
+        <v>-165.85</v>
       </c>
       <c r="L73" t="n">
-        <v>186.75</v>
+        <v>192.88</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:55:53</t>
+          <t>07:56:37</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>3.08</v>
+        <v>3.36</v>
       </c>
       <c r="F74" t="n">
         <v>8.74</v>
       </c>
       <c r="G74" t="n">
-        <v>233.3</v>
+        <v>239.8</v>
       </c>
       <c r="H74" t="n">
-        <v>12.9</v>
+        <v>30.8</v>
       </c>
       <c r="I74" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>-43.77</v>
+        <v>-46.04</v>
       </c>
       <c r="K74" t="n">
-        <v>-14.5</v>
+        <v>-34.72</v>
       </c>
       <c r="L74" t="n">
-        <v>46.11</v>
+        <v>57.66</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:57:41</t>
+          <t>07:58:19</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>2.88</v>
+        <v>2.15</v>
       </c>
       <c r="F75" t="n">
-        <v>8.74</v>
+        <v>5.8</v>
       </c>
       <c r="G75" t="n">
-        <v>244.8</v>
+        <v>232.3</v>
       </c>
       <c r="H75" t="n">
-        <v>18.6</v>
+        <v>58.8</v>
       </c>
       <c r="I75" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J75" t="n">
-        <v>-7.58</v>
+        <v>-44.19</v>
       </c>
       <c r="K75" t="n">
-        <v>-46.28</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="L75" t="n">
-        <v>46.9</v>
+        <v>45.29</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07:59:17</t>
+          <t>07:59:13</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>3.22</v>
+        <v>3.03</v>
       </c>
       <c r="F76" t="n">
-        <v>7.28</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="G76" t="n">
-        <v>250.7</v>
+        <v>229.9</v>
       </c>
       <c r="H76" t="n">
-        <v>15.8</v>
+        <v>38.3</v>
       </c>
       <c r="I76" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J76" t="n">
-        <v>30.73</v>
+        <v>-57.44</v>
       </c>
       <c r="K76" t="n">
-        <v>-64.31</v>
+        <v>16.22</v>
       </c>
       <c r="L76" t="n">
-        <v>71.27</v>
+        <v>59.69</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>08:03:24</t>
+          <t>08:05:25</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>2.59</v>
+        <v>3.18</v>
       </c>
       <c r="F77" t="n">
-        <v>8.74</v>
+        <v>7.58</v>
       </c>
       <c r="G77" t="n">
-        <v>241.8</v>
+        <v>239.5</v>
       </c>
       <c r="H77" t="n">
-        <v>8.4</v>
+        <v>67</v>
       </c>
       <c r="I77" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>-19.43</v>
+        <v>-10.52</v>
       </c>
       <c r="K77" t="n">
-        <v>48.53</v>
+        <v>63.22</v>
       </c>
       <c r="L77" t="n">
-        <v>52.27</v>
+        <v>64.09</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>08:05:49</t>
+          <t>08:07:41</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>2.85</v>
+        <v>2.82</v>
       </c>
       <c r="F78" t="n">
-        <v>6.76</v>
+        <v>6.41</v>
       </c>
       <c r="G78" t="n">
-        <v>242.6</v>
+        <v>234.7</v>
       </c>
       <c r="H78" t="n">
-        <v>15.8</v>
+        <v>50.2</v>
       </c>
       <c r="I78" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J78" t="n">
-        <v>11.98</v>
+        <v>57.56</v>
       </c>
       <c r="K78" t="n">
-        <v>-57.85</v>
+        <v>-60.04</v>
       </c>
       <c r="L78" t="n">
-        <v>59.08</v>
+        <v>83.17</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>08:07:07</t>
+          <t>08:09:28</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>2.89</v>
+        <v>2.77</v>
       </c>
       <c r="F79" t="n">
-        <v>7.97</v>
+        <v>8.24</v>
       </c>
       <c r="G79" t="n">
-        <v>244.8</v>
+        <v>235.1</v>
       </c>
       <c r="H79" t="n">
-        <v>10.7</v>
+        <v>9.5</v>
       </c>
       <c r="I79" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J79" t="n">
-        <v>-55.92</v>
+        <v>-54.43</v>
       </c>
       <c r="K79" t="n">
-        <v>-18.99</v>
+        <v>21.01</v>
       </c>
       <c r="L79" t="n">
-        <v>59.05</v>
+        <v>58.34</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>08:10:59</t>
+          <t>08:15:02</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>3.12</v>
+        <v>2.91</v>
       </c>
       <c r="F80" t="n">
-        <v>6.64</v>
+        <v>8.01</v>
       </c>
       <c r="G80" t="n">
-        <v>248.5</v>
+        <v>232.4</v>
       </c>
       <c r="H80" t="n">
-        <v>18.9</v>
+        <v>42.5</v>
       </c>
       <c r="I80" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J80" t="n">
-        <v>-148.49</v>
+        <v>-110.95</v>
       </c>
       <c r="K80" t="n">
-        <v>-7.84</v>
+        <v>-45.13</v>
       </c>
       <c r="L80" t="n">
-        <v>148.7</v>
+        <v>119.78</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08:12:09</t>
+          <t>08:15:43</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="F81" t="n">
-        <v>7.64</v>
+        <v>7.29</v>
       </c>
       <c r="G81" t="n">
-        <v>234.8</v>
+        <v>237.5</v>
       </c>
       <c r="H81" t="n">
-        <v>4.6</v>
+        <v>23.3</v>
       </c>
       <c r="I81" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>62.1</v>
+        <v>94.2</v>
       </c>
       <c r="K81" t="n">
-        <v>73.91</v>
+        <v>-38.79</v>
       </c>
       <c r="L81" t="n">
-        <v>96.53</v>
+        <v>101.87</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:14:15</t>
+          <t>08:17:27</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>2.97</v>
+        <v>2.87</v>
       </c>
       <c r="F82" t="n">
-        <v>8.74</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="G82" t="n">
-        <v>224.3</v>
+        <v>230.1</v>
       </c>
       <c r="H82" t="n">
-        <v>15.5</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="I82" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J82" t="n">
-        <v>-62.12</v>
+        <v>114.38</v>
       </c>
       <c r="K82" t="n">
-        <v>76.87</v>
+        <v>-12.7</v>
       </c>
       <c r="L82" t="n">
-        <v>98.83</v>
+        <v>115.08</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:19:41</t>
+          <t>08:22:29</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>2.7</v>
+        <v>2.27</v>
       </c>
       <c r="F83" t="n">
-        <v>7.92</v>
+        <v>7.91</v>
       </c>
       <c r="G83" t="n">
-        <v>225.3</v>
+        <v>225.9</v>
       </c>
       <c r="H83" t="n">
-        <v>13.2</v>
+        <v>42.8</v>
       </c>
       <c r="I83" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>110.91</v>
+        <v>-19.5</v>
       </c>
       <c r="K83" t="n">
-        <v>-73.56</v>
+        <v>129.01</v>
       </c>
       <c r="L83" t="n">
-        <v>133.09</v>
+        <v>130.48</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:21:41</t>
+          <t>08:23:47</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>2.67</v>
+        <v>2.52</v>
       </c>
       <c r="F84" t="n">
-        <v>6.21</v>
+        <v>8.74</v>
       </c>
       <c r="G84" t="n">
-        <v>227.1</v>
+        <v>220.1</v>
       </c>
       <c r="H84" t="n">
-        <v>14.8</v>
+        <v>33.7</v>
       </c>
       <c r="I84" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J84" t="n">
-        <v>-118.33</v>
+        <v>-122.14</v>
       </c>
       <c r="K84" t="n">
-        <v>-112.74</v>
+        <v>-7.5</v>
       </c>
       <c r="L84" t="n">
-        <v>163.44</v>
+        <v>122.37</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:23:42</t>
+          <t>08:26:15</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>3.15</v>
+        <v>3.01</v>
       </c>
       <c r="F85" t="n">
-        <v>8.74</v>
+        <v>6.84</v>
       </c>
       <c r="G85" t="n">
-        <v>241.4</v>
+        <v>231.3</v>
       </c>
       <c r="H85" t="n">
-        <v>11.1</v>
+        <v>64.3</v>
       </c>
       <c r="I85" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J85" t="n">
-        <v>-183.67</v>
+        <v>129.64</v>
       </c>
       <c r="K85" t="n">
-        <v>3.76</v>
+        <v>98.04000000000001</v>
       </c>
       <c r="L85" t="n">
-        <v>183.71</v>
+        <v>162.54</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:28:06</t>
+          <t>08:30:49</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>2.85</v>
+        <v>2.82</v>
       </c>
       <c r="F86" t="n">
-        <v>7.62</v>
+        <v>8.74</v>
       </c>
       <c r="G86" t="n">
-        <v>229.7</v>
+        <v>230.3</v>
       </c>
       <c r="H86" t="n">
-        <v>4.5</v>
+        <v>31.1</v>
       </c>
       <c r="I86" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J86" t="n">
-        <v>39.53</v>
+        <v>33.17</v>
       </c>
       <c r="K86" t="n">
-        <v>-272.48</v>
+        <v>-226.55</v>
       </c>
       <c r="L86" t="n">
-        <v>275.33</v>
+        <v>228.96</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:29:30</t>
+          <t>08:31:30</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>2.65</v>
+        <v>3.36</v>
       </c>
       <c r="F87" t="n">
-        <v>8.18</v>
+        <v>8.49</v>
       </c>
       <c r="G87" t="n">
-        <v>224.9</v>
+        <v>224.2</v>
       </c>
       <c r="H87" t="n">
-        <v>6.9</v>
+        <v>42.6</v>
       </c>
       <c r="I87" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>-73.28</v>
+        <v>196.72</v>
       </c>
       <c r="K87" t="n">
-        <v>-72.84999999999999</v>
+        <v>7.77</v>
       </c>
       <c r="L87" t="n">
-        <v>103.33</v>
+        <v>196.88</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:30:32</t>
+          <t>08:33:54</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>3.44</v>
+        <v>3.15</v>
       </c>
       <c r="F88" t="n">
-        <v>8.74</v>
+        <v>8.23</v>
       </c>
       <c r="G88" t="n">
-        <v>241.6</v>
+        <v>226.9</v>
       </c>
       <c r="H88" t="n">
-        <v>24.4</v>
+        <v>71.5</v>
       </c>
       <c r="I88" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>-285.59</v>
+        <v>-69.23</v>
       </c>
       <c r="K88" t="n">
-        <v>-185.55</v>
+        <v>170.11</v>
       </c>
       <c r="L88" t="n">
-        <v>340.58</v>
+        <v>183.66</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-05-25.xlsx
+++ b/output/2024-05-25.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2.6</v>
+        <v>2.42</v>
       </c>
       <c r="F14" t="n">
-        <v>6.81</v>
+        <v>7.14</v>
       </c>
       <c r="G14" t="n">
-        <v>242.3</v>
+        <v>235.1</v>
       </c>
       <c r="H14" t="n">
-        <v>43.1</v>
+        <v>31.6</v>
       </c>
       <c r="I14" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J14" t="n">
-        <v>-15.03</v>
+        <v>-16.86</v>
       </c>
       <c r="K14" t="n">
-        <v>-49.2</v>
+        <v>40.03</v>
       </c>
       <c r="L14" t="n">
-        <v>51.44</v>
+        <v>43.43</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:47:12</t>
+          <t>04:46:56</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2.05</v>
+        <v>3.19</v>
       </c>
       <c r="F15" t="n">
-        <v>5.7</v>
+        <v>8.74</v>
       </c>
       <c r="G15" t="n">
-        <v>248</v>
+        <v>248.8</v>
       </c>
       <c r="H15" t="n">
-        <v>50.8</v>
+        <v>63.4</v>
       </c>
       <c r="I15" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J15" t="n">
-        <v>28.54</v>
+        <v>65.36</v>
       </c>
       <c r="K15" t="n">
-        <v>-13.56</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>31.6</v>
+        <v>66.06</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:48:46</t>
+          <t>04:48:36</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>2.44</v>
+        <v>2.18</v>
       </c>
       <c r="F16" t="n">
-        <v>4.66</v>
+        <v>5.65</v>
       </c>
       <c r="G16" t="n">
-        <v>234.8</v>
+        <v>223</v>
       </c>
       <c r="H16" t="n">
-        <v>45.3</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>-37.62</v>
+        <v>-0.45</v>
       </c>
       <c r="K16" t="n">
-        <v>25.5</v>
+        <v>-40.39</v>
       </c>
       <c r="L16" t="n">
-        <v>45.45</v>
+        <v>40.4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04:54:03</t>
+          <t>04:53:54</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
       <c r="F17" t="n">
-        <v>8.529999999999999</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>243.1</v>
+        <v>241.7</v>
       </c>
       <c r="H17" t="n">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="I17" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J17" t="n">
-        <v>-51.45</v>
+        <v>56.48</v>
       </c>
       <c r="K17" t="n">
-        <v>-53.7</v>
+        <v>-8.039999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>74.37</v>
+        <v>57.05</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:55:29</t>
+          <t>04:56:02</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.58</v>
+        <v>2.03</v>
       </c>
       <c r="F18" t="n">
-        <v>4.49</v>
+        <v>5.84</v>
       </c>
       <c r="G18" t="n">
-        <v>245.4</v>
+        <v>240.7</v>
       </c>
       <c r="H18" t="n">
-        <v>73.59999999999999</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>48.14</v>
+        <v>-73.79000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>60.61</v>
+        <v>-7</v>
       </c>
       <c r="L18" t="n">
-        <v>77.40000000000001</v>
+        <v>74.12</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04:57:07</t>
+          <t>04:57:17</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>3.08</v>
+        <v>2.07</v>
       </c>
       <c r="F19" t="n">
-        <v>7.15</v>
+        <v>4.97</v>
       </c>
       <c r="G19" t="n">
-        <v>244.5</v>
+        <v>238.8</v>
       </c>
       <c r="H19" t="n">
-        <v>76.3</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J19" t="n">
-        <v>-42.87</v>
+        <v>76.36</v>
       </c>
       <c r="K19" t="n">
-        <v>-81.81</v>
+        <v>-30.12</v>
       </c>
       <c r="L19" t="n">
-        <v>92.36</v>
+        <v>82.09</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>05:00:35</t>
+          <t>05:02:07</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>2.66</v>
+        <v>2.16</v>
       </c>
       <c r="F20" t="n">
-        <v>6.22</v>
+        <v>3.66</v>
       </c>
       <c r="G20" t="n">
-        <v>224.3</v>
+        <v>241.8</v>
       </c>
       <c r="H20" t="n">
-        <v>42.2</v>
+        <v>38.7</v>
       </c>
       <c r="I20" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J20" t="n">
-        <v>-52.24</v>
+        <v>-112.44</v>
       </c>
       <c r="K20" t="n">
-        <v>-43.84</v>
+        <v>43.2</v>
       </c>
       <c r="L20" t="n">
-        <v>68.2</v>
+        <v>120.45</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>05:02:49</t>
+          <t>05:03:36</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>2.53</v>
+        <v>2.1</v>
       </c>
       <c r="F21" t="n">
-        <v>7.92</v>
+        <v>3.45</v>
       </c>
       <c r="G21" t="n">
-        <v>240.1</v>
+        <v>244</v>
       </c>
       <c r="H21" t="n">
-        <v>50.9</v>
+        <v>46.4</v>
       </c>
       <c r="I21" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>56.61</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>-94.36</v>
+        <v>74.22</v>
       </c>
       <c r="L21" t="n">
-        <v>110.04</v>
+        <v>117.56</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05:04:17</t>
+          <t>05:05:30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="F22" t="n">
-        <v>8.74</v>
+        <v>4.81</v>
       </c>
       <c r="G22" t="n">
-        <v>232.2</v>
+        <v>219.1</v>
       </c>
       <c r="H22" t="n">
-        <v>63</v>
+        <v>57.2</v>
       </c>
       <c r="I22" t="n">
         <v>21</v>
       </c>
       <c r="J22" t="n">
-        <v>93.69</v>
+        <v>99.88</v>
       </c>
       <c r="K22" t="n">
-        <v>20.74</v>
+        <v>90.28</v>
       </c>
       <c r="L22" t="n">
-        <v>95.95999999999999</v>
+        <v>134.63</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05:08:59</t>
+          <t>05:10:06</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>2.45</v>
+        <v>2.17</v>
       </c>
       <c r="F23" t="n">
-        <v>6.65</v>
+        <v>6.26</v>
       </c>
       <c r="G23" t="n">
-        <v>237.8</v>
+        <v>247.9</v>
       </c>
       <c r="H23" t="n">
-        <v>80.59999999999999</v>
+        <v>31.8</v>
       </c>
       <c r="I23" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J23" t="n">
-        <v>-123.58</v>
+        <v>-49.58</v>
       </c>
       <c r="K23" t="n">
-        <v>83.23999999999999</v>
+        <v>-155.94</v>
       </c>
       <c r="L23" t="n">
-        <v>148.99</v>
+        <v>163.64</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:10:44</t>
+          <t>05:12:40</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>2.2</v>
+        <v>2.73</v>
       </c>
       <c r="F24" t="n">
-        <v>5.01</v>
+        <v>8.74</v>
       </c>
       <c r="G24" t="n">
-        <v>249.8</v>
+        <v>229.5</v>
       </c>
       <c r="H24" t="n">
-        <v>55.2</v>
+        <v>24</v>
       </c>
       <c r="I24" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J24" t="n">
-        <v>29.01</v>
+        <v>20.67</v>
       </c>
       <c r="K24" t="n">
-        <v>136.18</v>
+        <v>135.85</v>
       </c>
       <c r="L24" t="n">
-        <v>139.23</v>
+        <v>137.42</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:12:39</t>
+          <t>05:13:44</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="F25" t="n">
-        <v>4.3</v>
+        <v>6.61</v>
       </c>
       <c r="G25" t="n">
-        <v>233.4</v>
+        <v>242.5</v>
       </c>
       <c r="H25" t="n">
-        <v>63.5</v>
+        <v>49.7</v>
       </c>
       <c r="I25" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J25" t="n">
-        <v>-131.82</v>
+        <v>-160.96</v>
       </c>
       <c r="K25" t="n">
-        <v>-45.82</v>
+        <v>46.5</v>
       </c>
       <c r="L25" t="n">
-        <v>139.56</v>
+        <v>167.54</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:15:47</t>
+          <t>05:19:43</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1132,31 +1132,31 @@
         <v>2.61</v>
       </c>
       <c r="F26" t="n">
-        <v>8.289999999999999</v>
+        <v>8.02</v>
       </c>
       <c r="G26" t="n">
-        <v>241.9</v>
+        <v>235.7</v>
       </c>
       <c r="H26" t="n">
-        <v>44.1</v>
+        <v>38.7</v>
       </c>
       <c r="I26" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J26" t="n">
-        <v>-164.1</v>
+        <v>-194.74</v>
       </c>
       <c r="K26" t="n">
-        <v>107.69</v>
+        <v>-108.8</v>
       </c>
       <c r="L26" t="n">
-        <v>196.28</v>
+        <v>223.07</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:17:18</t>
+          <t>05:21:39</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="F27" t="n">
-        <v>5.16</v>
+        <v>6.51</v>
       </c>
       <c r="G27" t="n">
-        <v>228.7</v>
+        <v>246.4</v>
       </c>
       <c r="H27" t="n">
-        <v>38.4</v>
+        <v>38.3</v>
       </c>
       <c r="I27" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="J27" t="n">
-        <v>36.19</v>
+        <v>-56.54</v>
       </c>
       <c r="K27" t="n">
-        <v>83.5</v>
+        <v>-258.74</v>
       </c>
       <c r="L27" t="n">
-        <v>91.01000000000001</v>
+        <v>264.84</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:18:36</t>
+          <t>05:22:43</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.13</v>
+        <v>2.63</v>
       </c>
       <c r="F28" t="n">
-        <v>3.34</v>
+        <v>4.77</v>
       </c>
       <c r="G28" t="n">
-        <v>228.1</v>
+        <v>262.7</v>
       </c>
       <c r="H28" t="n">
-        <v>14.6</v>
+        <v>36.2</v>
       </c>
       <c r="I28" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="J28" t="n">
-        <v>3.23</v>
+        <v>-219.52</v>
       </c>
       <c r="K28" t="n">
-        <v>177.5</v>
+        <v>328.9</v>
       </c>
       <c r="L28" t="n">
-        <v>177.53</v>
+        <v>395.43</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:29:45</t>
+          <t>05:33:41</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>2.13</v>
+        <v>2.61</v>
       </c>
       <c r="F29" t="n">
-        <v>3.32</v>
+        <v>7.78</v>
       </c>
       <c r="G29" t="n">
-        <v>222.7</v>
+        <v>239</v>
       </c>
       <c r="H29" t="n">
-        <v>34.1</v>
+        <v>23.9</v>
       </c>
       <c r="I29" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="J29" t="n">
-        <v>-25.21</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>38.96</v>
+        <v>-51.05</v>
       </c>
       <c r="L29" t="n">
-        <v>46.41</v>
+        <v>51.83</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:30:35</t>
+          <t>05:36:11</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2.16</v>
+        <v>1.84</v>
       </c>
       <c r="F30" t="n">
-        <v>7.04</v>
+        <v>4.52</v>
       </c>
       <c r="G30" t="n">
-        <v>240.6</v>
+        <v>244.3</v>
       </c>
       <c r="H30" t="n">
-        <v>43.2</v>
+        <v>35.6</v>
       </c>
       <c r="I30" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J30" t="n">
-        <v>3.32</v>
+        <v>-2.91</v>
       </c>
       <c r="K30" t="n">
-        <v>34.56</v>
+        <v>51.35</v>
       </c>
       <c r="L30" t="n">
-        <v>34.72</v>
+        <v>51.43</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:32:27</t>
+          <t>05:37:48</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.49</v>
+        <v>2.1</v>
       </c>
       <c r="F31" t="n">
-        <v>8.210000000000001</v>
+        <v>2.4</v>
       </c>
       <c r="G31" t="n">
-        <v>239</v>
+        <v>231.4</v>
       </c>
       <c r="H31" t="n">
-        <v>40.2</v>
+        <v>41.3</v>
       </c>
       <c r="I31" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="J31" t="n">
-        <v>32.2</v>
+        <v>-49.39</v>
       </c>
       <c r="K31" t="n">
-        <v>4.73</v>
+        <v>7.8</v>
       </c>
       <c r="L31" t="n">
-        <v>32.54</v>
+        <v>50.01</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:38:17</t>
+          <t>05:43:04</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="F32" t="n">
-        <v>4.28</v>
+        <v>3.88</v>
       </c>
       <c r="G32" t="n">
-        <v>217.4</v>
+        <v>241.2</v>
       </c>
       <c r="H32" t="n">
-        <v>61.3</v>
+        <v>42.9</v>
       </c>
       <c r="I32" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="J32" t="n">
-        <v>58.25</v>
+        <v>-73.88</v>
       </c>
       <c r="K32" t="n">
-        <v>25.52</v>
+        <v>-12.62</v>
       </c>
       <c r="L32" t="n">
-        <v>63.59</v>
+        <v>74.95</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:40:04</t>
+          <t>05:45:04</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="F33" t="n">
-        <v>8.74</v>
+        <v>5.93</v>
       </c>
       <c r="G33" t="n">
-        <v>230.3</v>
+        <v>234</v>
       </c>
       <c r="H33" t="n">
-        <v>33.2</v>
+        <v>11.8</v>
       </c>
       <c r="I33" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J33" t="n">
-        <v>59.8</v>
+        <v>89.04000000000001</v>
       </c>
       <c r="K33" t="n">
-        <v>25.92</v>
+        <v>-2.23</v>
       </c>
       <c r="L33" t="n">
-        <v>65.18000000000001</v>
+        <v>89.06999999999999</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:42:10</t>
+          <t>05:46:10</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>2.31</v>
+        <v>2.43</v>
       </c>
       <c r="F34" t="n">
-        <v>6.07</v>
+        <v>7.82</v>
       </c>
       <c r="G34" t="n">
-        <v>231.6</v>
+        <v>243.7</v>
       </c>
       <c r="H34" t="n">
-        <v>33.7</v>
+        <v>43.2</v>
       </c>
       <c r="I34" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J34" t="n">
-        <v>1.45</v>
+        <v>18.26</v>
       </c>
       <c r="K34" t="n">
-        <v>-57.14</v>
+        <v>-61.88</v>
       </c>
       <c r="L34" t="n">
-        <v>57.16</v>
+        <v>64.51000000000001</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:48:25</t>
+          <t>05:51:20</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>2.18</v>
+        <v>2.31</v>
       </c>
       <c r="F35" t="n">
-        <v>4.31</v>
+        <v>5.37</v>
       </c>
       <c r="G35" t="n">
-        <v>239.6</v>
+        <v>239.1</v>
       </c>
       <c r="H35" t="n">
-        <v>32.9</v>
+        <v>39.5</v>
       </c>
       <c r="I35" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="J35" t="n">
-        <v>-22.15</v>
+        <v>-55.86</v>
       </c>
       <c r="K35" t="n">
-        <v>95.84999999999999</v>
+        <v>97.93000000000001</v>
       </c>
       <c r="L35" t="n">
-        <v>98.37</v>
+        <v>112.75</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:49:13</t>
+          <t>05:52:55</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2.23</v>
+        <v>2.56</v>
       </c>
       <c r="F36" t="n">
-        <v>5.29</v>
+        <v>7.94</v>
       </c>
       <c r="G36" t="n">
-        <v>229</v>
+        <v>246.9</v>
       </c>
       <c r="H36" t="n">
-        <v>31.3</v>
+        <v>56.7</v>
       </c>
       <c r="I36" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J36" t="n">
-        <v>47.67</v>
+        <v>-41.4</v>
       </c>
       <c r="K36" t="n">
-        <v>-31.77</v>
+        <v>-91.78</v>
       </c>
       <c r="L36" t="n">
-        <v>57.29</v>
+        <v>100.69</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:51:18</t>
+          <t>05:54:59</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>2.64</v>
+        <v>2.18</v>
       </c>
       <c r="F37" t="n">
-        <v>6.25</v>
+        <v>2.5</v>
       </c>
       <c r="G37" t="n">
-        <v>249.6</v>
+        <v>236.6</v>
       </c>
       <c r="H37" t="n">
-        <v>36.2</v>
+        <v>37.5</v>
       </c>
       <c r="I37" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J37" t="n">
-        <v>48.34</v>
+        <v>-87.98999999999999</v>
       </c>
       <c r="K37" t="n">
-        <v>67.59</v>
+        <v>-7.26</v>
       </c>
       <c r="L37" t="n">
-        <v>83.09999999999999</v>
+        <v>88.29000000000001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05:56:30</t>
+          <t>05:59:41</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2.77</v>
+        <v>2.17</v>
       </c>
       <c r="F38" t="n">
-        <v>8.74</v>
+        <v>5.88</v>
       </c>
       <c r="G38" t="n">
-        <v>235.6</v>
+        <v>243</v>
       </c>
       <c r="H38" t="n">
-        <v>39.4</v>
+        <v>45.9</v>
       </c>
       <c r="I38" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J38" t="n">
-        <v>32.8</v>
+        <v>25.06</v>
       </c>
       <c r="K38" t="n">
-        <v>-148.12</v>
+        <v>130.59</v>
       </c>
       <c r="L38" t="n">
-        <v>151.7</v>
+        <v>132.97</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>05:58:41</t>
+          <t>06:00:45</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="F39" t="n">
-        <v>7.53</v>
+        <v>6.69</v>
       </c>
       <c r="G39" t="n">
-        <v>254.1</v>
+        <v>233.1</v>
       </c>
       <c r="H39" t="n">
-        <v>64.7</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="I39" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="J39" t="n">
-        <v>-77.25</v>
+        <v>75.61</v>
       </c>
       <c r="K39" t="n">
-        <v>17.37</v>
+        <v>-122.67</v>
       </c>
       <c r="L39" t="n">
-        <v>79.18000000000001</v>
+        <v>144.1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>05:59:53</t>
+          <t>06:02:25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>2.14</v>
+        <v>2.56</v>
       </c>
       <c r="F40" t="n">
-        <v>7.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G40" t="n">
-        <v>234.8</v>
+        <v>240.5</v>
       </c>
       <c r="H40" t="n">
-        <v>3.7</v>
+        <v>31.2</v>
       </c>
       <c r="I40" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J40" t="n">
-        <v>33.75</v>
+        <v>75.66</v>
       </c>
       <c r="K40" t="n">
-        <v>-133.42</v>
+        <v>167.34</v>
       </c>
       <c r="L40" t="n">
-        <v>137.62</v>
+        <v>183.65</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06:04:25</t>
+          <t>06:07:24</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>2.65</v>
+        <v>2.47</v>
       </c>
       <c r="F41" t="n">
-        <v>7.12</v>
+        <v>8.73</v>
       </c>
       <c r="G41" t="n">
-        <v>224</v>
+        <v>241.6</v>
       </c>
       <c r="H41" t="n">
-        <v>30.1</v>
+        <v>14.2</v>
       </c>
       <c r="I41" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J41" t="n">
-        <v>-80.20999999999999</v>
+        <v>240.08</v>
       </c>
       <c r="K41" t="n">
-        <v>-160.37</v>
+        <v>-13.54</v>
       </c>
       <c r="L41" t="n">
-        <v>179.31</v>
+        <v>240.46</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06:06:53</t>
+          <t>06:08:56</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>2.48</v>
+        <v>1.87</v>
       </c>
       <c r="F42" t="n">
-        <v>6.06</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G42" t="n">
-        <v>237.8</v>
+        <v>238.4</v>
       </c>
       <c r="H42" t="n">
-        <v>35.7</v>
+        <v>34.3</v>
       </c>
       <c r="I42" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J42" t="n">
-        <v>-35.66</v>
+        <v>-195.95</v>
       </c>
       <c r="K42" t="n">
-        <v>205.1</v>
+        <v>-34.94</v>
       </c>
       <c r="L42" t="n">
-        <v>208.17</v>
+        <v>199.04</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06:08:51</t>
+          <t>06:11:36</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="F43" t="n">
-        <v>6.68</v>
+        <v>5.08</v>
       </c>
       <c r="G43" t="n">
-        <v>234.7</v>
+        <v>233.3</v>
       </c>
       <c r="H43" t="n">
-        <v>0.7</v>
+        <v>41.4</v>
       </c>
       <c r="I43" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>133.77</v>
+        <v>-60.57</v>
       </c>
       <c r="K43" t="n">
-        <v>139.05</v>
+        <v>-197.17</v>
       </c>
       <c r="L43" t="n">
-        <v>192.95</v>
+        <v>206.26</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:19:20</t>
+          <t>06:24:20</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>2.8</v>
+        <v>2.33</v>
       </c>
       <c r="F44" t="n">
-        <v>8.74</v>
+        <v>7.18</v>
       </c>
       <c r="G44" t="n">
-        <v>239.9</v>
+        <v>236.5</v>
       </c>
       <c r="H44" t="n">
-        <v>55.5</v>
+        <v>29.7</v>
       </c>
       <c r="I44" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J44" t="n">
-        <v>-56.04</v>
+        <v>-2.83</v>
       </c>
       <c r="K44" t="n">
-        <v>-22.69</v>
+        <v>-37.78</v>
       </c>
       <c r="L44" t="n">
-        <v>60.46</v>
+        <v>37.88</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:21:15</t>
+          <t>06:25:20</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>2.52</v>
+        <v>2.42</v>
       </c>
       <c r="F45" t="n">
         <v>8.74</v>
       </c>
       <c r="G45" t="n">
-        <v>231.4</v>
+        <v>241.9</v>
       </c>
       <c r="H45" t="n">
-        <v>55.6</v>
+        <v>55</v>
       </c>
       <c r="I45" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J45" t="n">
-        <v>-23.39</v>
+        <v>35.35</v>
       </c>
       <c r="K45" t="n">
-        <v>-20.12</v>
+        <v>19.1</v>
       </c>
       <c r="L45" t="n">
-        <v>30.85</v>
+        <v>40.18</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:23:10</t>
+          <t>06:28:00</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>3</v>
+        <v>2.26</v>
       </c>
       <c r="F46" t="n">
-        <v>8.74</v>
+        <v>5.81</v>
       </c>
       <c r="G46" t="n">
-        <v>240.5</v>
+        <v>235.8</v>
       </c>
       <c r="H46" t="n">
-        <v>36.2</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="J46" t="n">
-        <v>28.63</v>
+        <v>23.63</v>
       </c>
       <c r="K46" t="n">
-        <v>-44.1</v>
+        <v>12.07</v>
       </c>
       <c r="L46" t="n">
-        <v>52.58</v>
+        <v>26.53</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:26:52</t>
+          <t>06:32:09</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>2.73</v>
+        <v>2.36</v>
       </c>
       <c r="F47" t="n">
-        <v>8.74</v>
+        <v>6.45</v>
       </c>
       <c r="G47" t="n">
-        <v>250.5</v>
+        <v>231.9</v>
       </c>
       <c r="H47" t="n">
-        <v>28.1</v>
+        <v>24.4</v>
       </c>
       <c r="I47" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="J47" t="n">
-        <v>15.63</v>
+        <v>75.81999999999999</v>
       </c>
       <c r="K47" t="n">
-        <v>71.88</v>
+        <v>-4.04</v>
       </c>
       <c r="L47" t="n">
-        <v>73.56</v>
+        <v>75.93000000000001</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:28:06</t>
+          <t>06:34:25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>2.19</v>
+        <v>3.12</v>
       </c>
       <c r="F48" t="n">
-        <v>8.74</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="G48" t="n">
-        <v>235.8</v>
+        <v>243.3</v>
       </c>
       <c r="H48" t="n">
-        <v>57.9</v>
+        <v>14.9</v>
       </c>
       <c r="I48" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J48" t="n">
-        <v>-70.39</v>
+        <v>-82.44</v>
       </c>
       <c r="K48" t="n">
-        <v>-35.94</v>
+        <v>46.26</v>
       </c>
       <c r="L48" t="n">
-        <v>79.04000000000001</v>
+        <v>94.53</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:29:41</t>
+          <t>06:36:21</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>2.78</v>
+        <v>2.58</v>
       </c>
       <c r="F49" t="n">
-        <v>8.17</v>
+        <v>8.74</v>
       </c>
       <c r="G49" t="n">
-        <v>242.7</v>
+        <v>243.5</v>
       </c>
       <c r="H49" t="n">
-        <v>41.4</v>
+        <v>18.7</v>
       </c>
       <c r="I49" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J49" t="n">
-        <v>67.86</v>
+        <v>53.33</v>
       </c>
       <c r="K49" t="n">
-        <v>-22.89</v>
+        <v>-16.43</v>
       </c>
       <c r="L49" t="n">
-        <v>71.61</v>
+        <v>55.8</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:35:26</t>
+          <t>06:41:20</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>3</v>
+        <v>2.76</v>
       </c>
       <c r="F50" t="n">
-        <v>8.74</v>
+        <v>7.44</v>
       </c>
       <c r="G50" t="n">
-        <v>242.8</v>
+        <v>250.3</v>
       </c>
       <c r="H50" t="n">
-        <v>21.3</v>
+        <v>30.6</v>
       </c>
       <c r="I50" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J50" t="n">
-        <v>-98.56</v>
+        <v>-94.05</v>
       </c>
       <c r="K50" t="n">
-        <v>-64.55</v>
+        <v>57.25</v>
       </c>
       <c r="L50" t="n">
-        <v>117.82</v>
+        <v>110.11</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:37:42</t>
+          <t>06:43:13</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>3.04</v>
+        <v>2.49</v>
       </c>
       <c r="F51" t="n">
-        <v>8.74</v>
+        <v>6.34</v>
       </c>
       <c r="G51" t="n">
-        <v>239.9</v>
+        <v>248.8</v>
       </c>
       <c r="H51" t="n">
-        <v>28.2</v>
+        <v>27.3</v>
       </c>
       <c r="I51" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J51" t="n">
-        <v>63.46</v>
+        <v>-61.15</v>
       </c>
       <c r="K51" t="n">
-        <v>-72.53</v>
+        <v>-95.06999999999999</v>
       </c>
       <c r="L51" t="n">
-        <v>96.37</v>
+        <v>113.04</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:38:59</t>
+          <t>06:45:00</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>2.62</v>
+        <v>2.42</v>
       </c>
       <c r="F52" t="n">
-        <v>8.74</v>
+        <v>7.12</v>
       </c>
       <c r="G52" t="n">
-        <v>233.1</v>
+        <v>236.1</v>
       </c>
       <c r="H52" t="n">
-        <v>23.7</v>
+        <v>25.4</v>
       </c>
       <c r="I52" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J52" t="n">
-        <v>2.48</v>
+        <v>72.93000000000001</v>
       </c>
       <c r="K52" t="n">
-        <v>-102.01</v>
+        <v>81.48999999999999</v>
       </c>
       <c r="L52" t="n">
-        <v>102.04</v>
+        <v>109.36</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:45:04</t>
+          <t>06:49:41</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>2.83</v>
+        <v>2.59</v>
       </c>
       <c r="F53" t="n">
-        <v>6.75</v>
+        <v>4.06</v>
       </c>
       <c r="G53" t="n">
-        <v>234</v>
+        <v>251.7</v>
       </c>
       <c r="H53" t="n">
-        <v>58</v>
+        <v>48.3</v>
       </c>
       <c r="I53" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J53" t="n">
-        <v>186.11</v>
+        <v>-62.19</v>
       </c>
       <c r="K53" t="n">
-        <v>-22.67</v>
+        <v>128.57</v>
       </c>
       <c r="L53" t="n">
-        <v>187.48</v>
+        <v>142.82</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:46:44</t>
+          <t>06:50:36</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>2.76</v>
+        <v>2.81</v>
       </c>
       <c r="F54" t="n">
-        <v>6.79</v>
+        <v>8.74</v>
       </c>
       <c r="G54" t="n">
-        <v>237.8</v>
+        <v>229.8</v>
       </c>
       <c r="H54" t="n">
-        <v>69.5</v>
+        <v>34.3</v>
       </c>
       <c r="I54" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J54" t="n">
-        <v>48.45</v>
+        <v>31.14</v>
       </c>
       <c r="K54" t="n">
-        <v>143.69</v>
+        <v>-78.3</v>
       </c>
       <c r="L54" t="n">
-        <v>151.64</v>
+        <v>84.27</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:48:24</t>
+          <t>06:53:08</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="F55" t="n">
-        <v>7.81</v>
+        <v>8.74</v>
       </c>
       <c r="G55" t="n">
-        <v>226.5</v>
+        <v>231.4</v>
       </c>
       <c r="H55" t="n">
-        <v>46.3</v>
+        <v>55.6</v>
       </c>
       <c r="I55" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J55" t="n">
-        <v>-50.95</v>
+        <v>-97.89</v>
       </c>
       <c r="K55" t="n">
-        <v>-157.44</v>
+        <v>-85.59999999999999</v>
       </c>
       <c r="L55" t="n">
-        <v>165.48</v>
+        <v>130.04</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:53:46</t>
+          <t>06:57:01</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>2.77</v>
+        <v>3.07</v>
       </c>
       <c r="F56" t="n">
         <v>8.74</v>
       </c>
       <c r="G56" t="n">
-        <v>237.2</v>
+        <v>240.5</v>
       </c>
       <c r="H56" t="n">
-        <v>19.4</v>
+        <v>36.2</v>
       </c>
       <c r="I56" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J56" t="n">
-        <v>-54.29</v>
+        <v>181.54</v>
       </c>
       <c r="K56" t="n">
-        <v>164.85</v>
+        <v>-176.29</v>
       </c>
       <c r="L56" t="n">
-        <v>173.56</v>
+        <v>253.05</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06:54:40</t>
+          <t>06:58:44</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>3.09</v>
+        <v>2.8</v>
       </c>
       <c r="F57" t="n">
         <v>8.74</v>
       </c>
       <c r="G57" t="n">
-        <v>250</v>
+        <v>250.5</v>
       </c>
       <c r="H57" t="n">
-        <v>34.7</v>
+        <v>28.1</v>
       </c>
       <c r="I57" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J57" t="n">
-        <v>-196.08</v>
+        <v>90.36</v>
       </c>
       <c r="K57" t="n">
-        <v>215.68</v>
+        <v>223.44</v>
       </c>
       <c r="L57" t="n">
-        <v>291.49</v>
+        <v>241.02</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06:56:38</t>
+          <t>06:59:51</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>2.7</v>
+        <v>2.26</v>
       </c>
       <c r="F58" t="n">
-        <v>7.22</v>
+        <v>8.74</v>
       </c>
       <c r="G58" t="n">
-        <v>239.9</v>
+        <v>235.8</v>
       </c>
       <c r="H58" t="n">
-        <v>16.3</v>
+        <v>57.9</v>
       </c>
       <c r="I58" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J58" t="n">
-        <v>-170.26</v>
+        <v>-249.07</v>
       </c>
       <c r="K58" t="n">
-        <v>158.57</v>
+        <v>-119.63</v>
       </c>
       <c r="L58" t="n">
-        <v>232.66</v>
+        <v>276.31</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07:07:06</t>
+          <t>07:09:55</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>2.5</v>
+        <v>2.87</v>
       </c>
       <c r="F59" t="n">
-        <v>6.76</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G59" t="n">
-        <v>233.4</v>
+        <v>242.7</v>
       </c>
       <c r="H59" t="n">
-        <v>9.4</v>
+        <v>41.4</v>
       </c>
       <c r="I59" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="J59" t="n">
-        <v>-29.33</v>
+        <v>52.86</v>
       </c>
       <c r="K59" t="n">
-        <v>-35.2</v>
+        <v>-9.76</v>
       </c>
       <c r="L59" t="n">
-        <v>45.82</v>
+        <v>53.75</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07:08:31</t>
+          <t>07:12:11</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>2.57</v>
+        <v>3.07</v>
       </c>
       <c r="F60" t="n">
-        <v>7.66</v>
+        <v>8.74</v>
       </c>
       <c r="G60" t="n">
-        <v>244.3</v>
+        <v>242.8</v>
       </c>
       <c r="H60" t="n">
-        <v>52.6</v>
+        <v>21.3</v>
       </c>
       <c r="I60" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="J60" t="n">
-        <v>-30.25</v>
+        <v>-52.83</v>
       </c>
       <c r="K60" t="n">
-        <v>-32.83</v>
+        <v>-36.67</v>
       </c>
       <c r="L60" t="n">
-        <v>44.64</v>
+        <v>64.31</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07:10:26</t>
+          <t>07:14:34</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>2.41</v>
+        <v>3.12</v>
       </c>
       <c r="F61" t="n">
-        <v>5.96</v>
+        <v>8.74</v>
       </c>
       <c r="G61" t="n">
-        <v>226.4</v>
+        <v>239.9</v>
       </c>
       <c r="H61" t="n">
-        <v>51.3</v>
+        <v>28.2</v>
       </c>
       <c r="I61" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="J61" t="n">
-        <v>9.92</v>
+        <v>42.99</v>
       </c>
       <c r="K61" t="n">
-        <v>-31.51</v>
+        <v>-31.55</v>
       </c>
       <c r="L61" t="n">
-        <v>33.04</v>
+        <v>53.33</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:15:37</t>
+          <t>07:19:01</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>2.64</v>
+        <v>2.71</v>
       </c>
       <c r="F62" t="n">
-        <v>6.37</v>
+        <v>8.74</v>
       </c>
       <c r="G62" t="n">
-        <v>241.4</v>
+        <v>233.1</v>
       </c>
       <c r="H62" t="n">
-        <v>36</v>
+        <v>23.7</v>
       </c>
       <c r="I62" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J62" t="n">
-        <v>-44.52</v>
+        <v>16.1</v>
       </c>
       <c r="K62" t="n">
-        <v>24.62</v>
+        <v>-79.22</v>
       </c>
       <c r="L62" t="n">
-        <v>50.87</v>
+        <v>80.84</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:17:18</t>
+          <t>07:20:00</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>3.03</v>
+        <v>2.9</v>
       </c>
       <c r="F63" t="n">
-        <v>8.539999999999999</v>
+        <v>7.12</v>
       </c>
       <c r="G63" t="n">
-        <v>234.8</v>
+        <v>234</v>
       </c>
       <c r="H63" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="I63" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="J63" t="n">
-        <v>-1.94</v>
+        <v>103.82</v>
       </c>
       <c r="K63" t="n">
-        <v>-93.26000000000001</v>
+        <v>1.66</v>
       </c>
       <c r="L63" t="n">
-        <v>93.28</v>
+        <v>103.84</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:19:16</t>
+          <t>07:22:09</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>2.66</v>
+        <v>2.83</v>
       </c>
       <c r="F64" t="n">
-        <v>7.12</v>
+        <v>7.15</v>
       </c>
       <c r="G64" t="n">
-        <v>246.3</v>
+        <v>237.8</v>
       </c>
       <c r="H64" t="n">
-        <v>22.7</v>
+        <v>69.5</v>
       </c>
       <c r="I64" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J64" t="n">
-        <v>-34.51</v>
+        <v>69.01000000000001</v>
       </c>
       <c r="K64" t="n">
-        <v>36.9</v>
+        <v>48.07</v>
       </c>
       <c r="L64" t="n">
-        <v>50.52</v>
+        <v>84.09999999999999</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:23:59</t>
+          <t>07:26:35</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>3.18</v>
+        <v>2.7</v>
       </c>
       <c r="F65" t="n">
-        <v>8.74</v>
+        <v>7.83</v>
       </c>
       <c r="G65" t="n">
-        <v>247</v>
+        <v>246.6</v>
       </c>
       <c r="H65" t="n">
-        <v>22.6</v>
+        <v>45.2</v>
       </c>
       <c r="I65" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J65" t="n">
-        <v>84.66</v>
+        <v>-67.53</v>
       </c>
       <c r="K65" t="n">
-        <v>-11.97</v>
+        <v>-81.84</v>
       </c>
       <c r="L65" t="n">
-        <v>85.5</v>
+        <v>106.1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:25:37</t>
+          <t>07:28:03</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>2.91</v>
+        <v>3.99</v>
       </c>
       <c r="F66" t="n">
         <v>8.74</v>
       </c>
       <c r="G66" t="n">
-        <v>225.8</v>
+        <v>229.1</v>
       </c>
       <c r="H66" t="n">
-        <v>57.3</v>
+        <v>49.5</v>
       </c>
       <c r="I66" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J66" t="n">
-        <v>-10.2</v>
+        <v>3.19</v>
       </c>
       <c r="K66" t="n">
-        <v>-110.57</v>
+        <v>-172.28</v>
       </c>
       <c r="L66" t="n">
-        <v>111.04</v>
+        <v>172.31</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:26:56</t>
+          <t>07:30:01</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="F67" t="n">
-        <v>6.76</v>
+        <v>8.74</v>
       </c>
       <c r="G67" t="n">
-        <v>242.1</v>
+        <v>235.2</v>
       </c>
       <c r="H67" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="I67" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J67" t="n">
-        <v>-90.12</v>
+        <v>-276.79</v>
       </c>
       <c r="K67" t="n">
-        <v>35.61</v>
+        <v>201.73</v>
       </c>
       <c r="L67" t="n">
-        <v>96.90000000000001</v>
+        <v>342.5</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:32:30</t>
+          <t>07:34:02</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="F68" t="n">
-        <v>7.03</v>
+        <v>8.74</v>
       </c>
       <c r="G68" t="n">
-        <v>237.3</v>
+        <v>243.7</v>
       </c>
       <c r="H68" t="n">
-        <v>29.7</v>
+        <v>50.2</v>
       </c>
       <c r="I68" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J68" t="n">
-        <v>-136.95</v>
+        <v>164.93</v>
       </c>
       <c r="K68" t="n">
-        <v>11.46</v>
+        <v>-89.45</v>
       </c>
       <c r="L68" t="n">
-        <v>137.43</v>
+        <v>187.63</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:34:01</t>
+          <t>07:36:34</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>2.56</v>
+        <v>2.96</v>
       </c>
       <c r="F69" t="n">
-        <v>5.66</v>
+        <v>8.19</v>
       </c>
       <c r="G69" t="n">
-        <v>226.3</v>
+        <v>225.1</v>
       </c>
       <c r="H69" t="n">
-        <v>47</v>
+        <v>39.6</v>
       </c>
       <c r="I69" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="J69" t="n">
-        <v>-116.35</v>
+        <v>-195.28</v>
       </c>
       <c r="K69" t="n">
-        <v>-99.84999999999999</v>
+        <v>-50.21</v>
       </c>
       <c r="L69" t="n">
-        <v>153.32</v>
+        <v>201.63</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:35:42</t>
+          <t>07:37:41</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>2.59</v>
+        <v>2.89</v>
       </c>
       <c r="F70" t="n">
-        <v>5.08</v>
+        <v>7.6</v>
       </c>
       <c r="G70" t="n">
-        <v>251.9</v>
+        <v>242.4</v>
       </c>
       <c r="H70" t="n">
-        <v>76</v>
+        <v>41.2</v>
       </c>
       <c r="I70" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J70" t="n">
-        <v>127.68</v>
+        <v>185.09</v>
       </c>
       <c r="K70" t="n">
-        <v>14.28</v>
+        <v>-39.4</v>
       </c>
       <c r="L70" t="n">
-        <v>128.47</v>
+        <v>189.23</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:41:01</t>
+          <t>07:40:51</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="F71" t="n">
-        <v>8.74</v>
+        <v>6.54</v>
       </c>
       <c r="G71" t="n">
-        <v>225.6</v>
+        <v>241.9</v>
       </c>
       <c r="H71" t="n">
-        <v>50.2</v>
+        <v>46</v>
       </c>
       <c r="I71" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J71" t="n">
-        <v>-429.61</v>
+        <v>-238.57</v>
       </c>
       <c r="K71" t="n">
-        <v>-105.98</v>
+        <v>6.77</v>
       </c>
       <c r="L71" t="n">
-        <v>442.49</v>
+        <v>238.67</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:43:06</t>
+          <t>07:41:52</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="F72" t="n">
-        <v>6.85</v>
+        <v>8.24</v>
       </c>
       <c r="G72" t="n">
-        <v>223.1</v>
+        <v>235.8</v>
       </c>
       <c r="H72" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="I72" t="n">
         <v>21</v>
       </c>
-      <c r="I72" t="n">
-        <v>16</v>
-      </c>
       <c r="J72" t="n">
-        <v>-96.51000000000001</v>
+        <v>-14.69</v>
       </c>
       <c r="K72" t="n">
-        <v>-104.79</v>
+        <v>167.06</v>
       </c>
       <c r="L72" t="n">
-        <v>142.46</v>
+        <v>167.7</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:44:47</t>
+          <t>07:44:05</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="F73" t="n">
-        <v>8.74</v>
+        <v>5.39</v>
       </c>
       <c r="G73" t="n">
-        <v>231.2</v>
+        <v>241</v>
       </c>
       <c r="H73" t="n">
-        <v>42.1</v>
+        <v>83.5</v>
       </c>
       <c r="I73" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J73" t="n">
-        <v>98.47</v>
+        <v>-70.93000000000001</v>
       </c>
       <c r="K73" t="n">
-        <v>-165.85</v>
+        <v>231.51</v>
       </c>
       <c r="L73" t="n">
-        <v>192.88</v>
+        <v>242.13</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:56:37</t>
+          <t>07:56:11</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>3.36</v>
+        <v>2.37</v>
       </c>
       <c r="F74" t="n">
-        <v>8.74</v>
+        <v>4.72</v>
       </c>
       <c r="G74" t="n">
-        <v>239.8</v>
+        <v>230.4</v>
       </c>
       <c r="H74" t="n">
-        <v>30.8</v>
+        <v>31.6</v>
       </c>
       <c r="I74" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J74" t="n">
-        <v>-46.04</v>
+        <v>-0.71</v>
       </c>
       <c r="K74" t="n">
-        <v>-34.72</v>
+        <v>48.95</v>
       </c>
       <c r="L74" t="n">
-        <v>57.66</v>
+        <v>48.96</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:58:19</t>
+          <t>07:58:04</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>2.15</v>
+        <v>2.41</v>
       </c>
       <c r="F75" t="n">
-        <v>5.8</v>
+        <v>8.74</v>
       </c>
       <c r="G75" t="n">
-        <v>232.3</v>
+        <v>263.3</v>
       </c>
       <c r="H75" t="n">
-        <v>58.8</v>
+        <v>38.3</v>
       </c>
       <c r="I75" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="J75" t="n">
-        <v>-44.19</v>
+        <v>-33.98</v>
       </c>
       <c r="K75" t="n">
-        <v>9.949999999999999</v>
+        <v>11.13</v>
       </c>
       <c r="L75" t="n">
-        <v>45.29</v>
+        <v>35.76</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07:59:13</t>
+          <t>07:59:49</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>3.03</v>
+        <v>3.66</v>
       </c>
       <c r="F76" t="n">
-        <v>8.529999999999999</v>
+        <v>8.74</v>
       </c>
       <c r="G76" t="n">
-        <v>229.9</v>
+        <v>244.3</v>
       </c>
       <c r="H76" t="n">
-        <v>38.3</v>
+        <v>47.4</v>
       </c>
       <c r="I76" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>-57.44</v>
+        <v>76.37</v>
       </c>
       <c r="K76" t="n">
-        <v>16.22</v>
+        <v>-10.34</v>
       </c>
       <c r="L76" t="n">
-        <v>59.69</v>
+        <v>77.06999999999999</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>08:05:25</t>
+          <t>08:05:50</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>3.18</v>
+        <v>2.64</v>
       </c>
       <c r="F77" t="n">
-        <v>7.58</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="G77" t="n">
-        <v>239.5</v>
+        <v>236.9</v>
       </c>
       <c r="H77" t="n">
-        <v>67</v>
+        <v>35.4</v>
       </c>
       <c r="I77" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J77" t="n">
-        <v>-10.52</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="K77" t="n">
-        <v>63.22</v>
+        <v>29.72</v>
       </c>
       <c r="L77" t="n">
-        <v>64.09</v>
+        <v>71.03</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>08:07:41</t>
+          <t>08:07:40</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>2.82</v>
+        <v>2.44</v>
       </c>
       <c r="F78" t="n">
-        <v>6.41</v>
+        <v>6.67</v>
       </c>
       <c r="G78" t="n">
-        <v>234.7</v>
+        <v>237.3</v>
       </c>
       <c r="H78" t="n">
-        <v>50.2</v>
+        <v>29.7</v>
       </c>
       <c r="I78" t="n">
         <v>21</v>
       </c>
       <c r="J78" t="n">
-        <v>57.56</v>
+        <v>-75.23</v>
       </c>
       <c r="K78" t="n">
-        <v>-60.04</v>
+        <v>17.46</v>
       </c>
       <c r="L78" t="n">
-        <v>83.17</v>
+        <v>77.23</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>08:09:28</t>
+          <t>08:10:04</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="F79" t="n">
-        <v>8.24</v>
+        <v>5.97</v>
       </c>
       <c r="G79" t="n">
-        <v>235.1</v>
+        <v>226.3</v>
       </c>
       <c r="H79" t="n">
-        <v>9.5</v>
+        <v>47</v>
       </c>
       <c r="I79" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>-54.43</v>
+        <v>-70.26000000000001</v>
       </c>
       <c r="K79" t="n">
-        <v>21.01</v>
+        <v>-58.85</v>
       </c>
       <c r="L79" t="n">
-        <v>58.34</v>
+        <v>91.65000000000001</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>08:15:02</t>
+          <t>08:15:40</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>2.91</v>
+        <v>2.66</v>
       </c>
       <c r="F80" t="n">
-        <v>8.01</v>
+        <v>5.44</v>
       </c>
       <c r="G80" t="n">
-        <v>232.4</v>
+        <v>251.9</v>
       </c>
       <c r="H80" t="n">
-        <v>42.5</v>
+        <v>76</v>
       </c>
       <c r="I80" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J80" t="n">
-        <v>-110.95</v>
+        <v>110.62</v>
       </c>
       <c r="K80" t="n">
-        <v>-45.13</v>
+        <v>16.6</v>
       </c>
       <c r="L80" t="n">
-        <v>119.78</v>
+        <v>111.86</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08:15:43</t>
+          <t>08:16:57</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>2.5</v>
+        <v>3.27</v>
       </c>
       <c r="F81" t="n">
-        <v>7.29</v>
+        <v>8.74</v>
       </c>
       <c r="G81" t="n">
-        <v>237.5</v>
+        <v>225.6</v>
       </c>
       <c r="H81" t="n">
-        <v>23.3</v>
+        <v>50.2</v>
       </c>
       <c r="I81" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="J81" t="n">
-        <v>94.2</v>
+        <v>-256.8</v>
       </c>
       <c r="K81" t="n">
-        <v>-38.79</v>
+        <v>-47.15</v>
       </c>
       <c r="L81" t="n">
-        <v>101.87</v>
+        <v>261.1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:17:27</t>
+          <t>08:18:30</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>2.87</v>
+        <v>2.65</v>
       </c>
       <c r="F82" t="n">
-        <v>8.289999999999999</v>
+        <v>7.16</v>
       </c>
       <c r="G82" t="n">
-        <v>230.1</v>
+        <v>223.1</v>
       </c>
       <c r="H82" t="n">
-        <v>78.90000000000001</v>
+        <v>21</v>
       </c>
       <c r="I82" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J82" t="n">
-        <v>114.38</v>
+        <v>-63</v>
       </c>
       <c r="K82" t="n">
-        <v>-12.7</v>
+        <v>-68.66</v>
       </c>
       <c r="L82" t="n">
-        <v>115.08</v>
+        <v>93.18000000000001</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:22:29</t>
+          <t>08:22:23</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>2.27</v>
+        <v>2.64</v>
       </c>
       <c r="F83" t="n">
-        <v>7.91</v>
+        <v>8.74</v>
       </c>
       <c r="G83" t="n">
-        <v>225.9</v>
+        <v>231.2</v>
       </c>
       <c r="H83" t="n">
-        <v>42.8</v>
+        <v>42.1</v>
       </c>
       <c r="I83" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J83" t="n">
-        <v>-19.5</v>
+        <v>130.92</v>
       </c>
       <c r="K83" t="n">
-        <v>129.01</v>
+        <v>-143.89</v>
       </c>
       <c r="L83" t="n">
-        <v>130.48</v>
+        <v>194.54</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:23:47</t>
+          <t>08:24:48</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>2.52</v>
+        <v>3.41</v>
       </c>
       <c r="F84" t="n">
         <v>8.74</v>
       </c>
       <c r="G84" t="n">
-        <v>220.1</v>
+        <v>239.8</v>
       </c>
       <c r="H84" t="n">
-        <v>33.7</v>
+        <v>30.8</v>
       </c>
       <c r="I84" t="n">
         <v>22</v>
       </c>
       <c r="J84" t="n">
-        <v>-122.14</v>
+        <v>-177.33</v>
       </c>
       <c r="K84" t="n">
-        <v>-7.5</v>
+        <v>-143.29</v>
       </c>
       <c r="L84" t="n">
-        <v>122.37</v>
+        <v>227.99</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:26:15</t>
+          <t>08:26:41</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>3.01</v>
+        <v>2.2</v>
       </c>
       <c r="F85" t="n">
-        <v>6.84</v>
+        <v>6.03</v>
       </c>
       <c r="G85" t="n">
-        <v>231.3</v>
+        <v>232.3</v>
       </c>
       <c r="H85" t="n">
-        <v>64.3</v>
+        <v>58.8</v>
       </c>
       <c r="I85" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J85" t="n">
-        <v>129.64</v>
+        <v>-182.51</v>
       </c>
       <c r="K85" t="n">
-        <v>98.04000000000001</v>
+        <v>69.76000000000001</v>
       </c>
       <c r="L85" t="n">
-        <v>162.54</v>
+        <v>195.38</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:30:49</t>
+          <t>08:30:59</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>2.82</v>
+        <v>3.09</v>
       </c>
       <c r="F86" t="n">
         <v>8.74</v>
       </c>
       <c r="G86" t="n">
-        <v>230.3</v>
+        <v>229.9</v>
       </c>
       <c r="H86" t="n">
-        <v>31.1</v>
+        <v>38.3</v>
       </c>
       <c r="I86" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="J86" t="n">
-        <v>33.17</v>
+        <v>-262.28</v>
       </c>
       <c r="K86" t="n">
-        <v>-226.55</v>
+        <v>135.71</v>
       </c>
       <c r="L86" t="n">
-        <v>228.96</v>
+        <v>295.31</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:31:30</t>
+          <t>08:33:09</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>3.36</v>
+        <v>3.23</v>
       </c>
       <c r="F87" t="n">
-        <v>8.49</v>
+        <v>7.85</v>
       </c>
       <c r="G87" t="n">
-        <v>224.2</v>
+        <v>239.5</v>
       </c>
       <c r="H87" t="n">
-        <v>42.6</v>
+        <v>67</v>
       </c>
       <c r="I87" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="J87" t="n">
-        <v>196.72</v>
+        <v>9.93</v>
       </c>
       <c r="K87" t="n">
-        <v>7.77</v>
+        <v>209.51</v>
       </c>
       <c r="L87" t="n">
-        <v>196.88</v>
+        <v>209.74</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:33:54</t>
+          <t>08:34:44</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>3.15</v>
+        <v>2.86</v>
       </c>
       <c r="F88" t="n">
-        <v>8.23</v>
+        <v>6.63</v>
       </c>
       <c r="G88" t="n">
-        <v>226.9</v>
+        <v>234.7</v>
       </c>
       <c r="H88" t="n">
-        <v>71.5</v>
+        <v>50.2</v>
       </c>
       <c r="I88" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J88" t="n">
-        <v>-69.23</v>
+        <v>231.43</v>
       </c>
       <c r="K88" t="n">
-        <v>170.11</v>
+        <v>-156.39</v>
       </c>
       <c r="L88" t="n">
-        <v>183.66</v>
+        <v>279.31</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-05-25.xlsx
+++ b/output/2024-05-25.xlsx
@@ -640,13 +640,13 @@
         <v>31</v>
       </c>
       <c r="J14" t="n">
-        <v>-24.53</v>
+        <v>-24.37</v>
       </c>
       <c r="K14" t="n">
-        <v>-22.59</v>
+        <v>-22.44</v>
       </c>
       <c r="L14" t="n">
-        <v>33.35</v>
+        <v>33.13</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>26</v>
       </c>
       <c r="J15" t="n">
-        <v>26.64</v>
+        <v>24.66</v>
       </c>
       <c r="K15" t="n">
-        <v>-53.03</v>
+        <v>-49.08</v>
       </c>
       <c r="L15" t="n">
-        <v>59.35</v>
+        <v>54.93</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>28</v>
       </c>
       <c r="J16" t="n">
-        <v>-23.44</v>
+        <v>-25.67</v>
       </c>
       <c r="K16" t="n">
-        <v>32.09</v>
+        <v>35.14</v>
       </c>
       <c r="L16" t="n">
-        <v>39.74</v>
+        <v>43.51</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>27</v>
       </c>
       <c r="J17" t="n">
-        <v>-56.74</v>
+        <v>-57.41</v>
       </c>
       <c r="K17" t="n">
-        <v>22.4</v>
+        <v>22.66</v>
       </c>
       <c r="L17" t="n">
-        <v>61</v>
+        <v>61.72</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>28</v>
       </c>
       <c r="J18" t="n">
-        <v>53.8</v>
+        <v>54.15</v>
       </c>
       <c r="K18" t="n">
-        <v>-19.41</v>
+        <v>-19.54</v>
       </c>
       <c r="L18" t="n">
-        <v>57.2</v>
+        <v>57.57</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>43.41</v>
+        <v>44.8</v>
       </c>
       <c r="K19" t="n">
-        <v>37.77</v>
+        <v>38.99</v>
       </c>
       <c r="L19" t="n">
-        <v>57.54</v>
+        <v>59.39</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>30</v>
       </c>
       <c r="J20" t="n">
-        <v>67.90000000000001</v>
+        <v>72.03</v>
       </c>
       <c r="K20" t="n">
-        <v>27.25</v>
+        <v>28.9</v>
       </c>
       <c r="L20" t="n">
-        <v>73.16</v>
+        <v>77.61</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>26</v>
       </c>
       <c r="J21" t="n">
-        <v>5.01</v>
+        <v>5.16</v>
       </c>
       <c r="K21" t="n">
-        <v>113.19</v>
+        <v>116.52</v>
       </c>
       <c r="L21" t="n">
-        <v>113.3</v>
+        <v>116.63</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>27</v>
       </c>
       <c r="J22" t="n">
-        <v>61.71</v>
+        <v>66.33</v>
       </c>
       <c r="K22" t="n">
-        <v>54.76</v>
+        <v>58.85</v>
       </c>
       <c r="L22" t="n">
-        <v>82.5</v>
+        <v>88.67</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>31</v>
       </c>
       <c r="J23" t="n">
-        <v>58.56</v>
+        <v>62.9</v>
       </c>
       <c r="K23" t="n">
-        <v>67.91</v>
+        <v>72.95</v>
       </c>
       <c r="L23" t="n">
-        <v>89.67</v>
+        <v>96.31999999999999</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>27</v>
       </c>
       <c r="J24" t="n">
-        <v>-109.07</v>
+        <v>-118.2</v>
       </c>
       <c r="K24" t="n">
-        <v>46.25</v>
+        <v>50.13</v>
       </c>
       <c r="L24" t="n">
-        <v>118.47</v>
+        <v>128.39</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>31</v>
       </c>
       <c r="J25" t="n">
-        <v>6.35</v>
+        <v>6.65</v>
       </c>
       <c r="K25" t="n">
-        <v>-107.74</v>
+        <v>-112.88</v>
       </c>
       <c r="L25" t="n">
-        <v>107.93</v>
+        <v>113.07</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>31</v>
       </c>
       <c r="J26" t="n">
-        <v>94.53</v>
+        <v>113.13</v>
       </c>
       <c r="K26" t="n">
-        <v>66.92</v>
+        <v>80.08</v>
       </c>
       <c r="L26" t="n">
-        <v>115.82</v>
+        <v>138.6</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>29</v>
       </c>
       <c r="J27" t="n">
-        <v>-161.37</v>
+        <v>-179.34</v>
       </c>
       <c r="K27" t="n">
-        <v>-5.81</v>
+        <v>-6.46</v>
       </c>
       <c r="L27" t="n">
-        <v>161.48</v>
+        <v>179.46</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>29</v>
       </c>
       <c r="J28" t="n">
-        <v>-56.3</v>
+        <v>-68.70999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>-99.77</v>
+        <v>-121.76</v>
       </c>
       <c r="L28" t="n">
-        <v>114.56</v>
+        <v>139.81</v>
       </c>
     </row>
     <row r="29">
@@ -1312,13 +1312,13 @@
         <v>26</v>
       </c>
       <c r="J30" t="n">
-        <v>-47.99</v>
+        <v>-46.36</v>
       </c>
       <c r="K30" t="n">
-        <v>-37.25</v>
+        <v>-35.98</v>
       </c>
       <c r="L30" t="n">
-        <v>60.75</v>
+        <v>58.69</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>-17.58</v>
+        <v>-18.16</v>
       </c>
       <c r="K31" t="n">
-        <v>-32.82</v>
+        <v>-33.91</v>
       </c>
       <c r="L31" t="n">
-        <v>37.23</v>
+        <v>38.46</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>30</v>
       </c>
       <c r="J32" t="n">
-        <v>-26.18</v>
+        <v>-26.38</v>
       </c>
       <c r="K32" t="n">
-        <v>-43.23</v>
+        <v>-43.55</v>
       </c>
       <c r="L32" t="n">
-        <v>50.54</v>
+        <v>50.92</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>25</v>
       </c>
       <c r="J33" t="n">
-        <v>32.2</v>
+        <v>33.83</v>
       </c>
       <c r="K33" t="n">
-        <v>38.21</v>
+        <v>40.14</v>
       </c>
       <c r="L33" t="n">
-        <v>49.96</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>26</v>
       </c>
       <c r="J34" t="n">
-        <v>68.61</v>
+        <v>65.27</v>
       </c>
       <c r="K34" t="n">
-        <v>40.93</v>
+        <v>38.94</v>
       </c>
       <c r="L34" t="n">
-        <v>79.89</v>
+        <v>76</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>30</v>
       </c>
       <c r="J35" t="n">
-        <v>-24.06</v>
+        <v>-23.68</v>
       </c>
       <c r="K35" t="n">
-        <v>96.09</v>
+        <v>94.59</v>
       </c>
       <c r="L35" t="n">
-        <v>99.06</v>
+        <v>97.51000000000001</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>30</v>
       </c>
       <c r="J36" t="n">
-        <v>66.2</v>
+        <v>67.25</v>
       </c>
       <c r="K36" t="n">
-        <v>-54.05</v>
+        <v>-54.9</v>
       </c>
       <c r="L36" t="n">
-        <v>85.47</v>
+        <v>86.81</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>30</v>
       </c>
       <c r="J37" t="n">
-        <v>9.390000000000001</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="K37" t="n">
-        <v>-72.62</v>
+        <v>-75.67</v>
       </c>
       <c r="L37" t="n">
-        <v>73.23</v>
+        <v>76.3</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>27</v>
       </c>
       <c r="J38" t="n">
-        <v>24.92</v>
+        <v>25.36</v>
       </c>
       <c r="K38" t="n">
-        <v>-128.56</v>
+        <v>-130.83</v>
       </c>
       <c r="L38" t="n">
-        <v>130.95</v>
+        <v>133.27</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>27</v>
       </c>
       <c r="J39" t="n">
-        <v>-122.32</v>
+        <v>-124.21</v>
       </c>
       <c r="K39" t="n">
-        <v>16.63</v>
+        <v>16.89</v>
       </c>
       <c r="L39" t="n">
-        <v>123.45</v>
+        <v>125.35</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>38.37</v>
+        <v>38.52</v>
       </c>
       <c r="K40" t="n">
-        <v>-138.82</v>
+        <v>-139.35</v>
       </c>
       <c r="L40" t="n">
-        <v>144.02</v>
+        <v>144.58</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>27</v>
       </c>
       <c r="J41" t="n">
-        <v>107.78</v>
+        <v>131.77</v>
       </c>
       <c r="K41" t="n">
-        <v>21.09</v>
+        <v>25.78</v>
       </c>
       <c r="L41" t="n">
-        <v>109.82</v>
+        <v>134.27</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>25</v>
       </c>
       <c r="J42" t="n">
-        <v>172.65</v>
+        <v>187.7</v>
       </c>
       <c r="K42" t="n">
-        <v>-148.42</v>
+        <v>-161.36</v>
       </c>
       <c r="L42" t="n">
-        <v>227.68</v>
+        <v>247.53</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>28</v>
       </c>
       <c r="J43" t="n">
-        <v>-98.20999999999999</v>
+        <v>-119.56</v>
       </c>
       <c r="K43" t="n">
-        <v>-47.02</v>
+        <v>-57.24</v>
       </c>
       <c r="L43" t="n">
-        <v>108.88</v>
+        <v>132.56</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>31</v>
       </c>
       <c r="J44" t="n">
-        <v>21.72</v>
+        <v>20.87</v>
       </c>
       <c r="K44" t="n">
-        <v>-29.86</v>
+        <v>-28.68</v>
       </c>
       <c r="L44" t="n">
-        <v>36.92</v>
+        <v>35.47</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>29</v>
       </c>
       <c r="J45" t="n">
-        <v>-29.28</v>
+        <v>-28.74</v>
       </c>
       <c r="K45" t="n">
-        <v>39.7</v>
+        <v>38.98</v>
       </c>
       <c r="L45" t="n">
-        <v>49.33</v>
+        <v>48.44</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>28</v>
       </c>
       <c r="J46" t="n">
-        <v>25.06</v>
+        <v>23.29</v>
       </c>
       <c r="K46" t="n">
-        <v>49.94</v>
+        <v>46.42</v>
       </c>
       <c r="L46" t="n">
-        <v>55.88</v>
+        <v>51.93</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>-39.32</v>
+        <v>-43.91</v>
       </c>
       <c r="K47" t="n">
-        <v>-15.58</v>
+        <v>-17.4</v>
       </c>
       <c r="L47" t="n">
-        <v>42.29</v>
+        <v>47.23</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>27</v>
       </c>
       <c r="J48" t="n">
-        <v>-68.86</v>
+        <v>-67.45999999999999</v>
       </c>
       <c r="K48" t="n">
-        <v>26.52</v>
+        <v>25.97</v>
       </c>
       <c r="L48" t="n">
-        <v>73.79000000000001</v>
+        <v>72.28</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>30</v>
       </c>
       <c r="J49" t="n">
-        <v>-17.4</v>
+        <v>-19.55</v>
       </c>
       <c r="K49" t="n">
-        <v>-35.93</v>
+        <v>-40.35</v>
       </c>
       <c r="L49" t="n">
-        <v>39.92</v>
+        <v>44.84</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>27</v>
       </c>
       <c r="J50" t="n">
-        <v>82.38</v>
+        <v>88.43000000000001</v>
       </c>
       <c r="K50" t="n">
-        <v>-11.39</v>
+        <v>-12.23</v>
       </c>
       <c r="L50" t="n">
-        <v>83.17</v>
+        <v>89.27</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>30</v>
       </c>
       <c r="J51" t="n">
-        <v>38.06</v>
+        <v>39.03</v>
       </c>
       <c r="K51" t="n">
-        <v>79.2</v>
+        <v>81.23</v>
       </c>
       <c r="L51" t="n">
-        <v>87.87</v>
+        <v>90.12</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>26</v>
       </c>
       <c r="J52" t="n">
-        <v>41.32</v>
+        <v>44.21</v>
       </c>
       <c r="K52" t="n">
-        <v>-74.90000000000001</v>
+        <v>-80.14</v>
       </c>
       <c r="L52" t="n">
-        <v>85.54000000000001</v>
+        <v>91.52</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>26</v>
       </c>
       <c r="J53" t="n">
-        <v>88.42</v>
+        <v>92.73999999999999</v>
       </c>
       <c r="K53" t="n">
-        <v>-110.92</v>
+        <v>-116.35</v>
       </c>
       <c r="L53" t="n">
-        <v>141.85</v>
+        <v>148.79</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>30</v>
       </c>
       <c r="J54" t="n">
-        <v>-39.07</v>
+        <v>-44.24</v>
       </c>
       <c r="K54" t="n">
-        <v>72.39</v>
+        <v>81.98</v>
       </c>
       <c r="L54" t="n">
-        <v>82.26000000000001</v>
+        <v>93.16</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>31</v>
       </c>
       <c r="J55" t="n">
-        <v>94.97</v>
+        <v>100.79</v>
       </c>
       <c r="K55" t="n">
-        <v>-51.11</v>
+        <v>-54.24</v>
       </c>
       <c r="L55" t="n">
-        <v>107.85</v>
+        <v>114.46</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>30</v>
       </c>
       <c r="J56" t="n">
-        <v>-64.22</v>
+        <v>-74.48999999999999</v>
       </c>
       <c r="K56" t="n">
-        <v>128.61</v>
+        <v>149.17</v>
       </c>
       <c r="L56" t="n">
-        <v>143.75</v>
+        <v>166.74</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>31</v>
       </c>
       <c r="J57" t="n">
-        <v>131.65</v>
+        <v>153.32</v>
       </c>
       <c r="K57" t="n">
-        <v>29.35</v>
+        <v>34.18</v>
       </c>
       <c r="L57" t="n">
-        <v>134.88</v>
+        <v>157.08</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>26</v>
       </c>
       <c r="J58" t="n">
-        <v>99.27</v>
+        <v>119.72</v>
       </c>
       <c r="K58" t="n">
-        <v>84.95</v>
+        <v>102.46</v>
       </c>
       <c r="L58" t="n">
-        <v>130.65</v>
+        <v>157.58</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>-1.3</v>
+        <v>-1.2</v>
       </c>
       <c r="K59" t="n">
-        <v>-67.23</v>
+        <v>-62.39</v>
       </c>
       <c r="L59" t="n">
-        <v>67.23999999999999</v>
+        <v>62.4</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>31</v>
       </c>
       <c r="J60" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="K60" t="n">
-        <v>40.31</v>
+        <v>38.95</v>
       </c>
       <c r="L60" t="n">
-        <v>40.33</v>
+        <v>38.98</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>28</v>
       </c>
       <c r="J61" t="n">
-        <v>18.43</v>
+        <v>19.53</v>
       </c>
       <c r="K61" t="n">
-        <v>30.71</v>
+        <v>32.53</v>
       </c>
       <c r="L61" t="n">
-        <v>35.82</v>
+        <v>37.94</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>31</v>
       </c>
       <c r="J62" t="n">
-        <v>-51.83</v>
+        <v>-48.81</v>
       </c>
       <c r="K62" t="n">
-        <v>-57.8</v>
+        <v>-54.44</v>
       </c>
       <c r="L62" t="n">
-        <v>77.63</v>
+        <v>73.12</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>31</v>
       </c>
       <c r="J63" t="n">
-        <v>4.03</v>
+        <v>3.69</v>
       </c>
       <c r="K63" t="n">
-        <v>-81.33</v>
+        <v>-74.48</v>
       </c>
       <c r="L63" t="n">
-        <v>81.43000000000001</v>
+        <v>74.56999999999999</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>31</v>
       </c>
       <c r="J64" t="n">
-        <v>-55.03</v>
+        <v>-52.4</v>
       </c>
       <c r="K64" t="n">
-        <v>52.06</v>
+        <v>49.57</v>
       </c>
       <c r="L64" t="n">
-        <v>75.75</v>
+        <v>72.13</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>30</v>
       </c>
       <c r="J65" t="n">
-        <v>54.51</v>
+        <v>59.14</v>
       </c>
       <c r="K65" t="n">
-        <v>61.62</v>
+        <v>66.86</v>
       </c>
       <c r="L65" t="n">
-        <v>82.27</v>
+        <v>89.27</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>29</v>
       </c>
       <c r="J66" t="n">
-        <v>34.36</v>
+        <v>39.02</v>
       </c>
       <c r="K66" t="n">
-        <v>55.1</v>
+        <v>62.58</v>
       </c>
       <c r="L66" t="n">
-        <v>64.94</v>
+        <v>73.75</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>29</v>
       </c>
       <c r="J67" t="n">
-        <v>-85.15000000000001</v>
+        <v>-89.14</v>
       </c>
       <c r="K67" t="n">
-        <v>-12.44</v>
+        <v>-13.02</v>
       </c>
       <c r="L67" t="n">
-        <v>86.05</v>
+        <v>90.08</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>31</v>
       </c>
       <c r="J68" t="n">
-        <v>-102.21</v>
+        <v>-109.29</v>
       </c>
       <c r="K68" t="n">
-        <v>13.23</v>
+        <v>14.15</v>
       </c>
       <c r="L68" t="n">
-        <v>103.07</v>
+        <v>110.2</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>-93.43000000000001</v>
+        <v>-95.88</v>
       </c>
       <c r="K69" t="n">
-        <v>-128.18</v>
+        <v>-131.53</v>
       </c>
       <c r="L69" t="n">
-        <v>158.62</v>
+        <v>162.77</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>-76.11</v>
+        <v>-84.37</v>
       </c>
       <c r="K70" t="n">
-        <v>86.68000000000001</v>
+        <v>96.08</v>
       </c>
       <c r="L70" t="n">
-        <v>115.36</v>
+        <v>127.86</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>28</v>
       </c>
       <c r="J71" t="n">
-        <v>43.31</v>
+        <v>48.34</v>
       </c>
       <c r="K71" t="n">
-        <v>-163.32</v>
+        <v>-182.31</v>
       </c>
       <c r="L71" t="n">
-        <v>168.96</v>
+        <v>188.61</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>29</v>
       </c>
       <c r="J72" t="n">
-        <v>-128.66</v>
+        <v>-137.34</v>
       </c>
       <c r="K72" t="n">
-        <v>145.7</v>
+        <v>155.53</v>
       </c>
       <c r="L72" t="n">
-        <v>194.37</v>
+        <v>207.49</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>-114.65</v>
+        <v>-136.95</v>
       </c>
       <c r="K73" t="n">
-        <v>-105.65</v>
+        <v>-126.2</v>
       </c>
       <c r="L73" t="n">
-        <v>155.9</v>
+        <v>186.23</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>29</v>
       </c>
       <c r="J74" t="n">
-        <v>9.26</v>
+        <v>9.08</v>
       </c>
       <c r="K74" t="n">
-        <v>-52.07</v>
+        <v>-51.06</v>
       </c>
       <c r="L74" t="n">
-        <v>52.89</v>
+        <v>51.86</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>31</v>
       </c>
       <c r="J75" t="n">
-        <v>51.31</v>
+        <v>48.22</v>
       </c>
       <c r="K75" t="n">
-        <v>-4.97</v>
+        <v>-4.67</v>
       </c>
       <c r="L75" t="n">
-        <v>51.55</v>
+        <v>48.44</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>29</v>
       </c>
       <c r="J76" t="n">
-        <v>30.89</v>
+        <v>31.12</v>
       </c>
       <c r="K76" t="n">
-        <v>25.44</v>
+        <v>25.63</v>
       </c>
       <c r="L76" t="n">
-        <v>40.01</v>
+        <v>40.32</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>27</v>
       </c>
       <c r="J77" t="n">
-        <v>-65.37</v>
+        <v>-65.23999999999999</v>
       </c>
       <c r="K77" t="n">
-        <v>24.33</v>
+        <v>24.28</v>
       </c>
       <c r="L77" t="n">
-        <v>69.75</v>
+        <v>69.62</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>30</v>
       </c>
       <c r="J78" t="n">
-        <v>30.41</v>
+        <v>29.99</v>
       </c>
       <c r="K78" t="n">
-        <v>-63.47</v>
+        <v>-62.61</v>
       </c>
       <c r="L78" t="n">
-        <v>70.38</v>
+        <v>69.42</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>28</v>
       </c>
       <c r="J79" t="n">
-        <v>-51.43</v>
+        <v>-51.65</v>
       </c>
       <c r="K79" t="n">
-        <v>25.28</v>
+        <v>25.39</v>
       </c>
       <c r="L79" t="n">
-        <v>57.31</v>
+        <v>57.56</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>31</v>
       </c>
       <c r="J80" t="n">
-        <v>-53.42</v>
+        <v>-59.73</v>
       </c>
       <c r="K80" t="n">
-        <v>-34.07</v>
+        <v>-38.1</v>
       </c>
       <c r="L80" t="n">
-        <v>63.36</v>
+        <v>70.84999999999999</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>29</v>
       </c>
       <c r="J81" t="n">
-        <v>-82.33</v>
+        <v>-81.29000000000001</v>
       </c>
       <c r="K81" t="n">
-        <v>63.98</v>
+        <v>63.17</v>
       </c>
       <c r="L81" t="n">
-        <v>104.26</v>
+        <v>102.95</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>26</v>
       </c>
       <c r="J82" t="n">
-        <v>-52.78</v>
+        <v>-53</v>
       </c>
       <c r="K82" t="n">
-        <v>96.69</v>
+        <v>97.09</v>
       </c>
       <c r="L82" t="n">
-        <v>110.15</v>
+        <v>110.61</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>26</v>
       </c>
       <c r="J83" t="n">
-        <v>83.88</v>
+        <v>93.23999999999999</v>
       </c>
       <c r="K83" t="n">
-        <v>51.01</v>
+        <v>56.7</v>
       </c>
       <c r="L83" t="n">
-        <v>98.17</v>
+        <v>109.12</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>27</v>
       </c>
       <c r="J84" t="n">
-        <v>-52.39</v>
+        <v>-61.21</v>
       </c>
       <c r="K84" t="n">
-        <v>60.02</v>
+        <v>70.12</v>
       </c>
       <c r="L84" t="n">
-        <v>79.67</v>
+        <v>93.08</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>25</v>
       </c>
       <c r="J85" t="n">
-        <v>-119.92</v>
+        <v>-132.24</v>
       </c>
       <c r="K85" t="n">
-        <v>26.2</v>
+        <v>28.89</v>
       </c>
       <c r="L85" t="n">
-        <v>122.75</v>
+        <v>135.36</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>28</v>
       </c>
       <c r="J86" t="n">
-        <v>11.11</v>
+        <v>11.78</v>
       </c>
       <c r="K86" t="n">
-        <v>-197.85</v>
+        <v>-209.72</v>
       </c>
       <c r="L86" t="n">
-        <v>198.16</v>
+        <v>210.05</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>29</v>
       </c>
       <c r="J87" t="n">
-        <v>-66.91</v>
+        <v>-69.44</v>
       </c>
       <c r="K87" t="n">
-        <v>-201.6</v>
+        <v>-209.23</v>
       </c>
       <c r="L87" t="n">
-        <v>212.41</v>
+        <v>220.45</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>-11.45</v>
+        <v>-13.58</v>
       </c>
       <c r="K88" t="n">
-        <v>138.71</v>
+        <v>164.54</v>
       </c>
       <c r="L88" t="n">
-        <v>139.18</v>
+        <v>165.09</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-05-25.xlsx
+++ b/output/2024-05-25.xlsx
@@ -724,13 +724,13 @@
         <v>28</v>
       </c>
       <c r="J16" t="n">
-        <v>-25.67</v>
+        <v>-26.57</v>
       </c>
       <c r="K16" t="n">
-        <v>35.14</v>
+        <v>36.38</v>
       </c>
       <c r="L16" t="n">
-        <v>43.51</v>
+        <v>45.05</v>
       </c>
     </row>
     <row r="17">
@@ -3160,13 +3160,13 @@
         <v>29</v>
       </c>
       <c r="J74" t="n">
-        <v>9.08</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="K74" t="n">
-        <v>-51.06</v>
+        <v>-51.34</v>
       </c>
       <c r="L74" t="n">
-        <v>51.86</v>
+        <v>52.15</v>
       </c>
     </row>
     <row r="75">
@@ -3286,13 +3286,13 @@
         <v>27</v>
       </c>
       <c r="J77" t="n">
-        <v>-65.23999999999999</v>
+        <v>-65.33</v>
       </c>
       <c r="K77" t="n">
-        <v>24.28</v>
+        <v>24.31</v>
       </c>
       <c r="L77" t="n">
-        <v>69.62</v>
+        <v>69.70999999999999</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>30</v>
       </c>
       <c r="J78" t="n">
-        <v>29.99</v>
+        <v>30.31</v>
       </c>
       <c r="K78" t="n">
-        <v>-62.61</v>
+        <v>-63.26</v>
       </c>
       <c r="L78" t="n">
-        <v>69.42</v>
+        <v>70.14</v>
       </c>
     </row>
     <row r="79">
